--- a/KPH-AI-GLOBAL.xlsx
+++ b/KPH-AI-GLOBAL.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="1497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="1509">
   <si>
     <t>Namirnica</t>
   </si>
@@ -4505,13 +4505,52 @@
   </si>
   <si>
     <t>Guarana-Energy-Drink – Warnhinweis zu Koffein und Zucker</t>
+  </si>
+  <si>
+    <t>Hleb sa marmeladom namaz snita</t>
+  </si>
+  <si>
+    <t>Hleb sa medom namaz snita</t>
+  </si>
+  <si>
+    <t>Kiflice sa dzemom</t>
+  </si>
+  <si>
+    <t>Bread with marmalade spread</t>
+  </si>
+  <si>
+    <t>Pan untado con mermelada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brot mit Marmeladenaufstrich
+</t>
+  </si>
+  <si>
+    <t>Brot mit Honigaufstrich, in Scheiben geschnitten</t>
+  </si>
+  <si>
+    <t>Pan untado con miel, en rebanadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bread with honey spread, sliced
+</t>
+  </si>
+  <si>
+    <t>Rolls with jam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rollitos con mermelada
+</t>
+  </si>
+  <si>
+    <t>Brötchen mit Marmelade</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4524,6 +4563,14 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4546,10 +4593,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4845,13 +4901,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G386"/>
+  <dimension ref="A1:G389"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.796875" customWidth="1"/>
     <col min="3" max="3" width="25.296875" customWidth="1"/>
-    <col min="4" max="4" width="27.19921875" customWidth="1"/>
+    <col min="4" max="4" width="57.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -13131,601 +13187,670 @@
         <v>635</v>
       </c>
     </row>
-    <row r="361" spans="1:7">
-      <c r="A361" t="s">
-        <v>1366</v>
-      </c>
-      <c r="B361" t="s">
-        <v>1367</v>
-      </c>
-      <c r="C361" t="s">
-        <v>1368</v>
-      </c>
-      <c r="D361" t="s">
-        <v>1369</v>
-      </c>
-      <c r="E361">
-        <v>1</v>
-      </c>
-      <c r="F361">
-        <v>1</v>
-      </c>
-      <c r="G361">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="362" spans="1:7">
-      <c r="A362" t="s">
-        <v>1370</v>
-      </c>
-      <c r="B362" t="s">
-        <v>1371</v>
-      </c>
-      <c r="C362" t="s">
-        <v>1372</v>
-      </c>
-      <c r="D362" t="s">
-        <v>1373</v>
-      </c>
-      <c r="E362">
-        <v>0</v>
-      </c>
-      <c r="F362">
-        <v>0</v>
-      </c>
-      <c r="G362">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="363" spans="1:7" ht="15">
-      <c r="A363" t="s">
-        <v>1493</v>
-      </c>
-      <c r="B363" s="1" t="s">
-        <v>1494</v>
-      </c>
-      <c r="C363" s="1" t="s">
-        <v>1495</v>
-      </c>
-      <c r="D363" s="1" t="s">
-        <v>1496</v>
-      </c>
-      <c r="E363">
-        <v>1</v>
-      </c>
-      <c r="F363">
-        <v>0</v>
-      </c>
-      <c r="G363">
-        <v>4</v>
+    <row r="361" spans="1:7" s="2" customFormat="1" ht="17.850000000000001" customHeight="1">
+      <c r="A361" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D361" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E361" s="2">
+        <v>42</v>
+      </c>
+      <c r="F361" s="2">
+        <v>14</v>
+      </c>
+      <c r="G361" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" s="2" customFormat="1" ht="16.7" customHeight="1">
+      <c r="A362" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B362" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E362" s="2">
+        <v>53</v>
+      </c>
+      <c r="F362" s="2">
+        <v>9</v>
+      </c>
+      <c r="G362" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" s="2" customFormat="1" ht="19.05" customHeight="1">
+      <c r="A363" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C363" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D363" s="4" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E363" s="2">
+        <v>77</v>
+      </c>
+      <c r="F363" s="2">
+        <v>47</v>
+      </c>
+      <c r="G363" s="2">
+        <v>223</v>
       </c>
     </row>
     <row r="364" spans="1:7">
       <c r="A364" t="s">
-        <v>1374</v>
+        <v>1366</v>
       </c>
       <c r="B364" t="s">
-        <v>1375</v>
+        <v>1367</v>
       </c>
       <c r="C364" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="D364" t="s">
-        <v>1377</v>
+        <v>1369</v>
       </c>
       <c r="E364">
         <v>1</v>
       </c>
       <c r="F364">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G364">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="365" spans="1:7">
       <c r="A365" t="s">
-        <v>1378</v>
+        <v>1370</v>
       </c>
       <c r="B365" t="s">
-        <v>1379</v>
+        <v>1371</v>
       </c>
       <c r="C365" t="s">
-        <v>1380</v>
+        <v>1372</v>
       </c>
       <c r="D365" t="s">
-        <v>1381</v>
+        <v>1373</v>
       </c>
       <c r="E365">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="F365">
+        <v>0</v>
+      </c>
+      <c r="G365">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" ht="15">
+      <c r="A366" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B366" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E366">
         <v>1</v>
-      </c>
-      <c r="G365">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="366" spans="1:7">
-      <c r="A366" t="s">
-        <v>1382</v>
-      </c>
-      <c r="B366" t="s">
-        <v>1383</v>
-      </c>
-      <c r="C366" t="s">
-        <v>1384</v>
-      </c>
-      <c r="D366" t="s">
-        <v>1385</v>
-      </c>
-      <c r="E366">
-        <v>0</v>
       </c>
       <c r="F366">
         <v>0</v>
       </c>
       <c r="G366">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="367" spans="1:7">
       <c r="A367" t="s">
-        <v>1386</v>
+        <v>1374</v>
       </c>
       <c r="B367" t="s">
-        <v>1387</v>
+        <v>1375</v>
       </c>
       <c r="C367" t="s">
-        <v>1388</v>
+        <v>1376</v>
       </c>
       <c r="D367" t="s">
-        <v>1389</v>
+        <v>1377</v>
       </c>
       <c r="E367">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F367">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G367">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="368" spans="1:7">
       <c r="A368" t="s">
-        <v>1482</v>
+        <v>1378</v>
       </c>
       <c r="B368" t="s">
-        <v>1483</v>
+        <v>1379</v>
       </c>
       <c r="C368" t="s">
-        <v>1484</v>
+        <v>1380</v>
       </c>
       <c r="D368" t="s">
-        <v>1485</v>
+        <v>1381</v>
       </c>
       <c r="E368">
-        <v>50</v>
+        <v>10.8</v>
       </c>
       <c r="F368">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G368">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="369" spans="1:7">
       <c r="A369" t="s">
-        <v>1390</v>
+        <v>1382</v>
       </c>
       <c r="B369" t="s">
-        <v>1391</v>
+        <v>1383</v>
       </c>
       <c r="C369" t="s">
-        <v>1392</v>
+        <v>1384</v>
       </c>
       <c r="D369" t="s">
-        <v>1393</v>
+        <v>1385</v>
       </c>
       <c r="E369">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F369">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G369">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="370" spans="1:7">
       <c r="A370" t="s">
-        <v>1394</v>
+        <v>1386</v>
       </c>
       <c r="B370" t="s">
-        <v>1395</v>
+        <v>1387</v>
       </c>
       <c r="C370" t="s">
-        <v>1396</v>
+        <v>1388</v>
       </c>
       <c r="D370" t="s">
-        <v>1397</v>
+        <v>1389</v>
       </c>
       <c r="E370">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F370">
+        <v>2</v>
+      </c>
+      <c r="G370">
         <v>1</v>
-      </c>
-      <c r="G370">
-        <v>3</v>
       </c>
     </row>
     <row r="371" spans="1:7">
       <c r="A371" t="s">
-        <v>1398</v>
+        <v>1482</v>
       </c>
       <c r="B371" t="s">
-        <v>1399</v>
+        <v>1483</v>
       </c>
       <c r="C371" t="s">
-        <v>1400</v>
+        <v>1484</v>
       </c>
       <c r="D371" t="s">
-        <v>1401</v>
+        <v>1485</v>
       </c>
       <c r="E371">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="F371">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G371">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="372" spans="1:7">
       <c r="A372" t="s">
-        <v>1402</v>
+        <v>1390</v>
       </c>
       <c r="B372" t="s">
-        <v>1403</v>
+        <v>1391</v>
       </c>
       <c r="C372" t="s">
-        <v>1404</v>
+        <v>1392</v>
       </c>
       <c r="D372" t="s">
-        <v>1405</v>
+        <v>1393</v>
       </c>
       <c r="E372">
-        <v>549</v>
+        <v>10</v>
       </c>
       <c r="F372">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="G372">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="373" spans="1:7">
       <c r="A373" t="s">
-        <v>1479</v>
+        <v>1394</v>
       </c>
       <c r="B373" t="s">
-        <v>1406</v>
+        <v>1395</v>
       </c>
       <c r="C373" t="s">
-        <v>1481</v>
+        <v>1396</v>
       </c>
       <c r="D373" t="s">
-        <v>1480</v>
+        <v>1397</v>
       </c>
       <c r="E373">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F373">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G373">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="374" spans="1:7">
       <c r="A374" t="s">
-        <v>1407</v>
+        <v>1398</v>
       </c>
       <c r="B374" t="s">
-        <v>1408</v>
+        <v>1399</v>
       </c>
       <c r="C374" t="s">
-        <v>1409</v>
+        <v>1400</v>
       </c>
       <c r="D374" t="s">
-        <v>1410</v>
+        <v>1401</v>
       </c>
       <c r="E374">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="F374">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G374">
-        <v>150</v>
+        <v>10</v>
       </c>
     </row>
     <row r="375" spans="1:7">
       <c r="A375" t="s">
-        <v>1411</v>
+        <v>1402</v>
       </c>
       <c r="B375" t="s">
-        <v>1412</v>
+        <v>1403</v>
       </c>
       <c r="C375" t="s">
-        <v>1413</v>
+        <v>1404</v>
       </c>
       <c r="D375" t="s">
-        <v>1414</v>
+        <v>1405</v>
       </c>
       <c r="E375">
-        <v>49</v>
+        <v>549</v>
       </c>
       <c r="F375">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="G375">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
-        <v>1415</v>
+        <v>1479</v>
       </c>
       <c r="B376" t="s">
-        <v>1416</v>
+        <v>1406</v>
       </c>
       <c r="C376" t="s">
-        <v>1417</v>
+        <v>1481</v>
       </c>
       <c r="D376" t="s">
-        <v>1418</v>
+        <v>1480</v>
       </c>
       <c r="E376">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="F376">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="G376">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="377" spans="1:7">
       <c r="A377" t="s">
-        <v>1419</v>
+        <v>1407</v>
       </c>
       <c r="B377" t="s">
-        <v>1420</v>
+        <v>1408</v>
       </c>
       <c r="C377" t="s">
-        <v>1421</v>
+        <v>1409</v>
       </c>
       <c r="D377" t="s">
-        <v>1422</v>
+        <v>1410</v>
       </c>
       <c r="E377">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="F377">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G377">
-        <v>39</v>
+        <v>150</v>
       </c>
     </row>
     <row r="378" spans="1:7">
       <c r="A378" t="s">
-        <v>1423</v>
+        <v>1411</v>
       </c>
       <c r="B378" t="s">
-        <v>1424</v>
+        <v>1412</v>
       </c>
       <c r="C378" t="s">
-        <v>1425</v>
+        <v>1413</v>
       </c>
       <c r="D378" t="s">
-        <v>1426</v>
+        <v>1414</v>
       </c>
       <c r="E378">
+        <v>49</v>
+      </c>
+      <c r="F378">
         <v>3</v>
       </c>
-      <c r="F378">
-        <v>0</v>
-      </c>
       <c r="G378">
-        <v>91</v>
+        <v>2</v>
       </c>
     </row>
     <row r="379" spans="1:7">
       <c r="A379" t="s">
-        <v>1427</v>
+        <v>1415</v>
       </c>
       <c r="B379" t="s">
-        <v>1428</v>
+        <v>1416</v>
       </c>
       <c r="C379" t="s">
-        <v>1429</v>
+        <v>1417</v>
       </c>
       <c r="D379" t="s">
-        <v>1430</v>
+        <v>1418</v>
       </c>
       <c r="E379">
-        <v>1.9</v>
+        <v>80</v>
       </c>
       <c r="F379">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G379">
-        <v>219</v>
+        <v>4</v>
       </c>
     </row>
     <row r="380" spans="1:7">
       <c r="A380" t="s">
-        <v>1431</v>
+        <v>1419</v>
       </c>
       <c r="B380" t="s">
-        <v>1432</v>
+        <v>1420</v>
       </c>
       <c r="C380" t="s">
-        <v>1433</v>
+        <v>1421</v>
       </c>
       <c r="D380" t="s">
-        <v>1434</v>
+        <v>1422</v>
       </c>
       <c r="E380">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F380">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G380">
-        <v>119</v>
+        <v>39</v>
       </c>
     </row>
     <row r="381" spans="1:7">
       <c r="A381" t="s">
-        <v>1435</v>
+        <v>1423</v>
       </c>
       <c r="B381" t="s">
-        <v>1436</v>
+        <v>1424</v>
       </c>
       <c r="C381" t="s">
-        <v>1437</v>
+        <v>1425</v>
       </c>
       <c r="D381" t="s">
-        <v>1438</v>
+        <v>1426</v>
       </c>
       <c r="E381">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F381">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G381">
-        <v>14</v>
+        <v>91</v>
       </c>
     </row>
     <row r="382" spans="1:7">
       <c r="A382" t="s">
-        <v>1439</v>
+        <v>1427</v>
       </c>
       <c r="B382" t="s">
-        <v>1440</v>
+        <v>1428</v>
       </c>
       <c r="C382" t="s">
-        <v>1441</v>
+        <v>1429</v>
       </c>
       <c r="D382" t="s">
-        <v>1442</v>
+        <v>1430</v>
       </c>
       <c r="E382">
-        <v>27</v>
+        <v>1.9</v>
       </c>
       <c r="F382">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G382">
-        <v>10</v>
+        <v>219</v>
       </c>
     </row>
     <row r="383" spans="1:7">
       <c r="A383" t="s">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="B383" t="s">
-        <v>1444</v>
+        <v>1432</v>
       </c>
       <c r="C383" t="s">
-        <v>1445</v>
+        <v>1433</v>
       </c>
       <c r="D383" t="s">
-        <v>1446</v>
+        <v>1434</v>
       </c>
       <c r="E383">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F383">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G383">
-        <v>5</v>
+        <v>119</v>
       </c>
     </row>
     <row r="384" spans="1:7">
       <c r="A384" t="s">
-        <v>1447</v>
+        <v>1435</v>
       </c>
       <c r="B384" t="s">
-        <v>1448</v>
+        <v>1436</v>
       </c>
       <c r="C384" t="s">
-        <v>1449</v>
+        <v>1437</v>
       </c>
       <c r="D384" t="s">
-        <v>1450</v>
+        <v>1438</v>
       </c>
       <c r="E384">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="F384">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G384">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="385" spans="1:7">
       <c r="A385" t="s">
-        <v>1451</v>
+        <v>1439</v>
       </c>
       <c r="B385" t="s">
-        <v>1452</v>
+        <v>1440</v>
       </c>
       <c r="C385" t="s">
-        <v>1453</v>
+        <v>1441</v>
       </c>
       <c r="D385" t="s">
-        <v>1454</v>
+        <v>1442</v>
       </c>
       <c r="E385">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="F385">
+        <v>20</v>
+      </c>
+      <c r="G385">
         <v>10</v>
-      </c>
-      <c r="G385">
-        <v>3</v>
       </c>
     </row>
     <row r="386" spans="1:7">
       <c r="A386" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B386" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C386" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D386" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E386">
+        <v>27</v>
+      </c>
+      <c r="F386">
+        <v>13</v>
+      </c>
+      <c r="G386">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7">
+      <c r="A387" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B387" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C387" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D387" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E387">
+        <v>82</v>
+      </c>
+      <c r="F387">
+        <v>15</v>
+      </c>
+      <c r="G387">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7">
+      <c r="A388" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B388" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C388" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D388" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E388">
+        <v>102</v>
+      </c>
+      <c r="F388">
+        <v>10</v>
+      </c>
+      <c r="G388">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7">
+      <c r="A389" t="s">
         <v>1455</v>
       </c>
-      <c r="B386" t="s">
+      <c r="B389" t="s">
         <v>1456</v>
       </c>
-      <c r="C386" t="s">
+      <c r="C389" t="s">
         <v>1457</v>
       </c>
-      <c r="D386" t="s">
+      <c r="D389" t="s">
         <v>1458</v>
       </c>
-      <c r="E386">
+      <c r="E389">
         <v>0</v>
       </c>
-      <c r="F386">
+      <c r="F389">
         <v>0</v>
       </c>
-      <c r="G386">
+      <c r="G389">
         <v>0</v>
       </c>
     </row>

--- a/KPH-AI-GLOBAL.xlsx
+++ b/KPH-AI-GLOBAL.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="1509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="1513">
   <si>
     <t>Namirnica</t>
   </si>
@@ -4544,6 +4544,18 @@
   </si>
   <si>
     <t>Brötchen mit Marmelade</t>
+  </si>
+  <si>
+    <t>Trapist sir</t>
+  </si>
+  <si>
+    <t>Trapist cheese</t>
+  </si>
+  <si>
+    <t>Queso Trapist</t>
+  </si>
+  <si>
+    <t>Trapist-Käse</t>
   </si>
 </sst>
 </file>
@@ -4901,7 +4913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G389"/>
+  <dimension ref="A1:G390"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -8201,249 +8213,249 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>555</v>
+        <v>1509</v>
       </c>
       <c r="B144" t="s">
-        <v>556</v>
+        <v>1510</v>
       </c>
       <c r="C144" t="s">
-        <v>557</v>
+        <v>1511</v>
       </c>
       <c r="D144" t="s">
-        <v>558</v>
+        <v>1512</v>
       </c>
       <c r="E144">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="F144">
-        <v>443</v>
+        <v>550</v>
       </c>
       <c r="G144">
-        <v>869</v>
+        <v>700</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B145" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C145" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="D145" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E145">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="F145">
-        <v>356</v>
+        <v>443</v>
       </c>
       <c r="G145">
-        <v>398</v>
+        <v>869</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B146" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C146" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D146" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E146">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="F146">
-        <v>605</v>
+        <v>356</v>
       </c>
       <c r="G146">
-        <v>336</v>
+        <v>398</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B147" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C147" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="D147" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="E147">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="F147">
-        <v>256</v>
+        <v>605</v>
       </c>
       <c r="G147">
-        <v>1300</v>
+        <v>336</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B148" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C148" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="D148" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="E148">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="F148">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="G148">
-        <v>137</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B149" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C149" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D149" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="E149">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F149">
-        <v>1200</v>
+        <v>239</v>
       </c>
       <c r="G149">
-        <v>1250</v>
+        <v>137</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B150" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C150" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="D150" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="E150">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="F150">
-        <v>160</v>
+        <v>1200</v>
       </c>
       <c r="G150">
-        <v>40</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B151" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C151" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="D151" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="E151">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="F151">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="G151">
-        <v>62</v>
+        <v>40</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B152" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C152" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="D152" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="E152">
         <v>190</v>
       </c>
       <c r="F152">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="G152">
-        <v>44</v>
+        <v>62</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B153" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C153" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D153" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E153">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="F153">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="G153">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B154" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C154" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="D154" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="E154">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F154">
         <v>86</v>
@@ -8454,223 +8466,223 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B155" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C155" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="D155" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E155">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="F155">
-        <v>202</v>
+        <v>86</v>
       </c>
       <c r="G155">
-        <v>133</v>
+        <v>62</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B156" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C156" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="D156" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="E156">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="F156">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G156">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B157" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C157" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="D157" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="E157">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="F157">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="G157">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B158" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C158" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="D158" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="E158">
-        <v>132</v>
+        <v>233</v>
       </c>
       <c r="F158">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="G158">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B159" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C159" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D159" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="E159">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F159">
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="G159">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B160" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C160" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="D160" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="E160">
-        <v>42</v>
+        <v>142</v>
       </c>
       <c r="F160">
-        <v>23</v>
+        <v>170</v>
       </c>
       <c r="G160">
-        <v>943</v>
+        <v>151</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B161" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C161" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="D161" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="E161">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F161">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G161">
-        <v>994</v>
+        <v>943</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B162" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C162" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="D162" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E162">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F162">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G162">
-        <v>827</v>
+        <v>994</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B163" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C163" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="D163" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>827</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B164" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C164" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="D164" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -8684,367 +8696,367 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B165" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C165" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="D165" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="E165">
         <v>0</v>
       </c>
       <c r="F165">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G165">
-        <v>568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B166" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C166" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="D166" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="E166">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="F166">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="G166">
-        <v>1252</v>
+        <v>568</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B167" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C167" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="D167" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="E167">
-        <v>570</v>
+        <v>130</v>
       </c>
       <c r="F167">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="G167">
-        <v>27</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B168" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C168" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D168" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="E168">
-        <v>310</v>
+        <v>570</v>
       </c>
       <c r="F168">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="G168">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B169" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C169" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="D169" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="E169">
-        <v>455</v>
+        <v>310</v>
       </c>
       <c r="F169">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G169">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170" spans="1:7">
       <c r="A170" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B170" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C170" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="D170" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="E170">
-        <v>350</v>
+        <v>455</v>
       </c>
       <c r="F170">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="G170">
-        <v>300</v>
+        <v>12</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B171" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C171" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D171" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="E171">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="F171">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G171">
-        <v>4</v>
+        <v>300</v>
       </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B172" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C172" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="D172" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="E172">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="F172">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G172">
-        <v>400</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B173" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C173" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="D173" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E173">
-        <v>1275</v>
+        <v>460</v>
       </c>
       <c r="F173">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="G173">
-        <v>594</v>
+        <v>400</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B174" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C174" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D174" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="E174">
-        <v>376</v>
+        <v>1275</v>
       </c>
       <c r="F174">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="G174">
-        <v>133</v>
+        <v>594</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B175" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C175" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D175" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="E175">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="F175">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="G175">
-        <v>16</v>
+        <v>133</v>
       </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B176" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C176" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="D176" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="E176">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="F176">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G176">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B177" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C177" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="D177" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="E177">
-        <v>550</v>
+        <v>340</v>
       </c>
       <c r="F177">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="G177">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B178" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C178" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="D178" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="E178">
-        <v>490</v>
+        <v>550</v>
       </c>
       <c r="F178">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="G178">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B179" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="C179" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="D179" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="E179">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="F179">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G179">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B180" t="s">
-        <v>696</v>
+        <v>683</v>
       </c>
       <c r="C180" t="s">
-        <v>697</v>
+        <v>684</v>
       </c>
       <c r="D180" t="s">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="E180">
-        <v>227</v>
+        <v>464</v>
       </c>
       <c r="F180">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="G180">
         <v>13</v>
@@ -9052,942 +9064,942 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B181" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="C181" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="D181" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="E181">
-        <v>266</v>
+        <v>227</v>
       </c>
       <c r="F181">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G181">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B182" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="C182" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="D182" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="E182">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="F182">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G182">
-        <v>355</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B183" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="C183" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="D183" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="E183">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="F183">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G183">
-        <v>15</v>
+        <v>355</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B184" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C184" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D184" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="E184">
-        <v>399</v>
+        <v>300</v>
       </c>
       <c r="F184">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G184">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B185" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C185" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="D185" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="E185">
-        <v>1000</v>
+        <v>399</v>
       </c>
       <c r="F185">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="G185">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B186" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="C186" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="D186" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="E186">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="F186">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="G186">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B187" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="C187" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="D187" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="E187">
-        <v>322</v>
+        <v>270</v>
       </c>
       <c r="F187">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G187">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B188" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="C188" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="D188" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E188">
-        <v>346</v>
+        <v>322</v>
       </c>
       <c r="F188">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="G188">
-        <v>53</v>
+        <v>18</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B189" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="C189" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D189" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="E189">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="F189">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G189">
-        <v>6</v>
+        <v>53</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B190" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="C190" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="D190" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E190">
-        <v>215</v>
+        <v>360</v>
       </c>
       <c r="F190">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G190">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B191" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C191" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="D191" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="E191">
-        <v>633</v>
+        <v>215</v>
       </c>
       <c r="F191">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G191">
-        <v>65</v>
+        <v>16</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B192" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="C192" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="D192" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="E192">
-        <v>291</v>
+        <v>633</v>
       </c>
       <c r="F192">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="G192">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="B193" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="C193" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="D193" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="E193">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="F193">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="G193">
-        <v>30</v>
+        <v>98</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B194" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C194" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="D194" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="E194">
-        <v>265</v>
+        <v>325</v>
       </c>
       <c r="F194">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G194">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B195" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="C195" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D195" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E195">
-        <v>554</v>
+        <v>265</v>
       </c>
       <c r="F195">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="G195">
-        <v>9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B196" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="C196" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="D196" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E196">
-        <v>380</v>
+        <v>554</v>
       </c>
       <c r="F196">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G196">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B197" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C197" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D197" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="E197">
-        <v>315</v>
+        <v>380</v>
       </c>
       <c r="F197">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G197">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="B198" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C198" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="D198" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="E198">
-        <v>400</v>
+        <v>315</v>
       </c>
       <c r="F198">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="G198">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="199" spans="1:7">
       <c r="A199" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="B199" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="C199" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="D199" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="E199">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="F199">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="G199">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="200" spans="1:7">
       <c r="A200" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B200" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C200" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D200" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="E200">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="F200">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G200">
-        <v>17</v>
+        <v>58</v>
       </c>
     </row>
     <row r="201" spans="1:7">
       <c r="A201" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B201" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="C201" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="D201" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="E201">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="F201">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="G201">
-        <v>288</v>
+        <v>17</v>
       </c>
     </row>
     <row r="202" spans="1:7">
       <c r="A202" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="B202" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="C202" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="D202" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="E202">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="F202">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="G202">
-        <v>350</v>
+        <v>288</v>
       </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="B203" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C203" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="D203" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="E203">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="F203">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G203">
-        <v>327</v>
+        <v>350</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="B204" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="C204" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="D204" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="E204">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="F204">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="G204">
-        <v>235</v>
+        <v>327</v>
       </c>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="B205" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="C205" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="D205" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="E205">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="F205">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="G205">
-        <v>455</v>
+        <v>235</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B206" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="C206" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="D206" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="E206">
-        <v>340</v>
+        <v>550</v>
       </c>
       <c r="F206">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G206">
-        <v>1</v>
+        <v>455</v>
       </c>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="B207" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="C207" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="D207" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="E207">
-        <v>250</v>
+        <v>340</v>
       </c>
       <c r="F207">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="G207">
-        <v>212</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:7">
       <c r="A208" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B208" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C208" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="D208" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="E208">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F208">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="G208">
-        <v>2</v>
+        <v>212</v>
       </c>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="B209" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="C209" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="D209" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="E209">
-        <v>550</v>
+        <v>248</v>
       </c>
       <c r="F209">
-        <v>230</v>
+        <v>37</v>
       </c>
       <c r="G209">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B210" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="C210" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="D210" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="E210">
-        <v>1680</v>
+        <v>550</v>
       </c>
       <c r="F210">
-        <v>555</v>
+        <v>230</v>
       </c>
       <c r="G210">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:7">
       <c r="A211" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="B211" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="C211" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="D211" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="E211">
-        <v>121</v>
+        <v>1680</v>
       </c>
       <c r="F211">
-        <v>97</v>
+        <v>555</v>
       </c>
       <c r="G211">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:7">
       <c r="A212" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B212" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="C212" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="D212" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E212">
-        <v>1660</v>
+        <v>121</v>
       </c>
       <c r="F212">
-        <v>600</v>
+        <v>97</v>
       </c>
       <c r="G212">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="B213" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="C213" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="D213" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="E213">
-        <v>137</v>
+        <v>1660</v>
       </c>
       <c r="F213">
-        <v>57</v>
+        <v>600</v>
       </c>
       <c r="G213">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="B214" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="C214" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="D214" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="E214">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F214">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G214">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:7">
       <c r="A215" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="B215" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="C215" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="D215" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="E215">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="F215">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="G215">
-        <v>0.3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="216" spans="1:7">
       <c r="A216" t="s">
-        <v>1486</v>
+        <v>832</v>
       </c>
       <c r="B216" t="s">
-        <v>1487</v>
+        <v>833</v>
       </c>
       <c r="C216" t="s">
-        <v>1487</v>
+        <v>834</v>
       </c>
       <c r="D216" t="s">
-        <v>1488</v>
+        <v>835</v>
       </c>
       <c r="E216">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="F216">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="G216">
-        <v>400</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="217" spans="1:7">
       <c r="A217" t="s">
-        <v>836</v>
+        <v>1486</v>
       </c>
       <c r="B217" t="s">
-        <v>837</v>
+        <v>1487</v>
       </c>
       <c r="C217" t="s">
-        <v>838</v>
+        <v>1487</v>
       </c>
       <c r="D217" t="s">
-        <v>839</v>
+        <v>1488</v>
       </c>
       <c r="E217">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="F217">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G217">
-        <v>7</v>
+        <v>400</v>
       </c>
     </row>
     <row r="218" spans="1:7">
       <c r="A218" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="B218" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="C218" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="D218" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="E218">
-        <v>3170</v>
+        <v>340</v>
       </c>
       <c r="F218">
-        <v>327</v>
+        <v>46</v>
       </c>
       <c r="G218">
-        <v>193</v>
+        <v>7</v>
       </c>
     </row>
     <row r="219" spans="1:7">
       <c r="A219" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B219" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="C219" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="D219" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="E219">
-        <v>129</v>
+        <v>3170</v>
       </c>
       <c r="F219">
-        <v>25</v>
+        <v>327</v>
       </c>
       <c r="G219">
-        <v>8</v>
+        <v>193</v>
       </c>
     </row>
     <row r="220" spans="1:7">
       <c r="A220" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B220" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="C220" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="D220" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="E220">
-        <v>176</v>
+        <v>129</v>
       </c>
       <c r="F220">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G220">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="221" spans="1:7">
       <c r="A221" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B221" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="C221" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="D221" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="E221">
-        <v>305</v>
+        <v>176</v>
       </c>
       <c r="F221">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G221">
         <v>2</v>
@@ -9995,436 +10007,436 @@
     </row>
     <row r="222" spans="1:7">
       <c r="A222" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B222" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C222" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="D222" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="E222">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="F222">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G222">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:7">
       <c r="A223" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="B223" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C223" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="D223" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="E223">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="F223">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="G223">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:7">
       <c r="A224" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="B224" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="C224" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="D224" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="E224">
-        <v>310</v>
+        <v>207</v>
       </c>
       <c r="F224">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="G224">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="225" spans="1:7">
       <c r="A225" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B225" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C225" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="D225" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="E225">
-        <v>192</v>
+        <v>310</v>
       </c>
       <c r="F225">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G225">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:7">
       <c r="A226" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="B226" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="C226" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="D226" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="E226">
-        <v>400</v>
+        <v>192</v>
       </c>
       <c r="F226">
-        <v>153</v>
+        <v>36</v>
       </c>
       <c r="G226">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227" spans="1:7">
       <c r="A227" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="B227" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="C227" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="D227" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="E227">
-        <v>234</v>
+        <v>400</v>
       </c>
       <c r="F227">
-        <v>49</v>
+        <v>153</v>
       </c>
       <c r="G227">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="228" spans="1:7">
       <c r="A228" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B228" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="C228" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="D228" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="E228">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="F228">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G228">
-        <v>274</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229" spans="1:7">
       <c r="A229" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="B229" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="C229" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="D229" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="E229">
-        <v>269</v>
+        <v>148</v>
       </c>
       <c r="F229">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="G229">
-        <v>759</v>
+        <v>274</v>
       </c>
     </row>
     <row r="230" spans="1:7">
       <c r="A230" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="B230" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="C230" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="D230" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="E230">
-        <v>50</v>
+        <v>269</v>
       </c>
       <c r="F230">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="G230">
-        <v>1353</v>
+        <v>759</v>
       </c>
     </row>
     <row r="231" spans="1:7">
       <c r="A231" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B231" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C231" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="D231" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="E231">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="F231">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G231">
-        <v>650</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="232" spans="1:7">
       <c r="A232" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="B232" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="C232" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="D232" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="E232">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="F232">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G232">
-        <v>2100</v>
+        <v>650</v>
       </c>
     </row>
     <row r="233" spans="1:7">
       <c r="A233" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="B233" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="C233" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="D233" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="E233">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="F233">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G233">
-        <v>1248</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="234" spans="1:7">
       <c r="A234" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B234" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="C234" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="D234" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="E234">
-        <v>800</v>
+        <v>131</v>
       </c>
       <c r="F234">
         <v>20</v>
       </c>
       <c r="G234">
-        <v>1200</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="235" spans="1:7">
       <c r="A235" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="B235" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="C235" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="D235" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="E235">
-        <v>220</v>
+        <v>800</v>
       </c>
       <c r="F235">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G235">
-        <v>360</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="236" spans="1:7">
       <c r="A236" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="B236" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="C236" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="D236" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="E236">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="F236">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="G236">
-        <v>450</v>
+        <v>360</v>
       </c>
     </row>
     <row r="237" spans="1:7">
       <c r="A237" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B237" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="C237" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="D237" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="E237">
+        <v>1000</v>
+      </c>
+      <c r="F237">
+        <v>70</v>
+      </c>
+      <c r="G237">
         <v>450</v>
-      </c>
-      <c r="F237">
-        <v>50</v>
-      </c>
-      <c r="G237">
-        <v>3</v>
       </c>
     </row>
     <row r="238" spans="1:7">
       <c r="A238" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="B238" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="C238" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="D238" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="E238">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="F238">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="G238">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239" spans="1:7">
       <c r="A239" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B239" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="C239" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="D239" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="E239">
-        <v>346</v>
+        <v>422</v>
       </c>
       <c r="F239">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G239">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:7">
       <c r="A240" t="s">
-        <v>1472</v>
+        <v>923</v>
       </c>
       <c r="B240" t="s">
-        <v>1473</v>
+        <v>924</v>
       </c>
       <c r="C240" t="s">
-        <v>1474</v>
+        <v>925</v>
       </c>
       <c r="D240" t="s">
-        <v>1473</v>
+        <v>926</v>
       </c>
       <c r="E240">
-        <v>277</v>
+        <v>346</v>
       </c>
       <c r="F240">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="G240">
         <v>2</v>
@@ -10432,114 +10444,114 @@
     </row>
     <row r="241" spans="1:7">
       <c r="A241" t="s">
-        <v>927</v>
+        <v>1472</v>
       </c>
       <c r="B241" t="s">
-        <v>928</v>
+        <v>1473</v>
       </c>
       <c r="C241" t="s">
-        <v>929</v>
+        <v>1474</v>
       </c>
       <c r="D241" t="s">
-        <v>930</v>
+        <v>1473</v>
       </c>
       <c r="E241">
-        <v>149</v>
+        <v>277</v>
       </c>
       <c r="F241">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G241">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="B242" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="C242" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D242" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="E242">
-        <v>210</v>
+        <v>149</v>
       </c>
       <c r="F242">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G242">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B243" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C243" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="D243" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="E243">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="F243">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G243">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B244" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="C244" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="D244" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="E244">
-        <v>177</v>
+        <v>260</v>
       </c>
       <c r="F244">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G244">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="B245" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="C245" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="D245" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="E245">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="F245">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G245">
         <v>1</v>
@@ -10547,68 +10559,68 @@
     </row>
     <row r="246" spans="1:7">
       <c r="A246" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B246" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C246" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="D246" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="E246">
-        <v>782</v>
+        <v>81</v>
       </c>
       <c r="F246">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="G246">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:7">
       <c r="A247" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="B247" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="C247" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="D247" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="E247">
-        <v>192</v>
+        <v>782</v>
       </c>
       <c r="F247">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="G247">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="248" spans="1:7">
       <c r="A248" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B248" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="C248" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="D248" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="E248">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="F248">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G248">
         <v>2</v>
@@ -10616,111 +10628,111 @@
     </row>
     <row r="249" spans="1:7">
       <c r="A249" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="B249" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="C249" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="D249" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="E249">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="F249">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G249">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250" spans="1:7">
       <c r="A250" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="B250" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C250" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="D250" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="E250">
-        <v>310</v>
+        <v>170</v>
       </c>
       <c r="F250">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G250">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:7">
       <c r="A251" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="B251" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="C251" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="D251" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="E251">
-        <v>238</v>
+        <v>310</v>
       </c>
       <c r="F251">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G251">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252" spans="1:7">
       <c r="A252" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B252" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="C252" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="D252" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="E252">
-        <v>114</v>
+        <v>238</v>
+      </c>
+      <c r="F252">
+        <v>27</v>
       </c>
       <c r="G252">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:7">
       <c r="A253" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B253" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="C253" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="D253" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="E253">
-        <v>144</v>
-      </c>
-      <c r="F253">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G253">
         <v>3</v>
@@ -10728,229 +10740,229 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="B254" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="C254" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="D254" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="E254">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="F254">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G254">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255" spans="1:7">
       <c r="A255" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="B255" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="C255" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D255" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="E255">
-        <v>1340</v>
+        <v>126</v>
       </c>
       <c r="F255">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="G255">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256" spans="1:7">
       <c r="A256" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B256" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="C256" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="D256" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="E256">
-        <v>205</v>
+        <v>1340</v>
       </c>
       <c r="F256">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="G256">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="257" spans="1:7">
       <c r="A257" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="B257" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="C257" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="D257" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="E257">
-        <v>1370</v>
+        <v>205</v>
       </c>
       <c r="F257">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="G257">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258" spans="1:7">
       <c r="A258" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="B258" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="C258" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="D258" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="E258">
-        <v>278</v>
+        <v>1370</v>
       </c>
       <c r="F258">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="G258">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="259" spans="1:7">
       <c r="A259" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B259" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="C259" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="D259" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="E259">
-        <v>860</v>
+        <v>278</v>
       </c>
       <c r="F259">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="G259">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="260" spans="1:7">
       <c r="A260" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="B260" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="C260" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="D260" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="E260">
-        <v>221</v>
+        <v>860</v>
       </c>
       <c r="F260">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="G260">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="261" spans="1:7">
       <c r="A261" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B261" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C261" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="D261" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="E261">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="F261">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G261">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262" spans="1:7">
       <c r="A262" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="B262" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="C262" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="D262" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="E262">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="F262">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G262">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="263" spans="1:7">
       <c r="A263" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="B263" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="C263" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="D263" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E263">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="F263">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G263">
         <v>2</v>
@@ -10958,229 +10970,229 @@
     </row>
     <row r="264" spans="1:7">
       <c r="A264" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="B264" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="C264" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="D264" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="E264">
-        <v>503</v>
+        <v>173</v>
       </c>
       <c r="F264">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="G264">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="265" spans="1:7">
       <c r="A265" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="B265" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="C265" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="D265" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="E265">
-        <v>393</v>
+        <v>503</v>
       </c>
       <c r="F265">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G265">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="266" spans="1:7">
       <c r="A266" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B266" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="C266" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="D266" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="E266">
-        <v>295</v>
+        <v>393</v>
       </c>
       <c r="F266">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G266">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267" spans="1:7">
       <c r="A267" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B267" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C267" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="D267" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E267">
-        <v>190</v>
+        <v>295</v>
       </c>
       <c r="F267">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G267">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="268" spans="1:7">
       <c r="A268" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B268" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="C268" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="D268" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="E268">
-        <v>330</v>
+        <v>190</v>
       </c>
       <c r="F268">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G268">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="269" spans="1:7">
       <c r="A269" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="B269" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="C269" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="D269" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="E269">
-        <v>158</v>
+        <v>330</v>
       </c>
       <c r="F269">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G269">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="270" spans="1:7">
       <c r="A270" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="B270" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="C270" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="D270" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E270">
-        <v>240</v>
+        <v>158</v>
       </c>
       <c r="F270">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G270">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271" spans="1:7">
       <c r="A271" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="B271" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="C271" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="D271" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="E271">
-        <v>850</v>
+        <v>240</v>
       </c>
       <c r="F271">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="G271">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272" spans="1:7">
       <c r="A272" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="B272" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="C272" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="D272" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="E272">
-        <v>140</v>
+        <v>850</v>
       </c>
       <c r="F272">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="G272">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="B273" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="C273" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="D273" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="E273">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="F273">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G273">
         <v>1</v>
@@ -11188,226 +11200,226 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="B274" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="C274" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="D274" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="E274">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F274">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G274">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="B275" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C275" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="D275" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="E275">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="F275">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G275">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="B276" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="C276" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="D276" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="E276">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F276">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G276">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="B277" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="C277" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="D277" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="E277">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F277">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G277">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278" spans="1:7">
       <c r="A278" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="B278" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="C278" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="D278" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="E278">
-        <v>33</v>
+        <v>200</v>
       </c>
       <c r="F278">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G278">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279" spans="1:7">
       <c r="A279" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="B279" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="C279" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="D279" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="E279">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="F279">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G279">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="B280" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="C280" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="D280" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="E280">
-        <v>362</v>
+        <v>78</v>
       </c>
       <c r="F280">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G280">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="B281" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="C281" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="D281" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="E281">
-        <v>50</v>
+        <v>362</v>
       </c>
       <c r="F281">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G281">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="B282" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="C282" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="D282" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="E282">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F282">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G282">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="B283" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="C283" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="D283" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="E283">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F283">
         <v>10</v>
@@ -11418,22 +11430,22 @@
     </row>
     <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="B284" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="C284" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="D284" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="E284">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F284">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G284">
         <v>1</v>
@@ -11441,22 +11453,22 @@
     </row>
     <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="B285" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C285" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D285" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="E285">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="F285">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G285">
         <v>1</v>
@@ -11464,22 +11476,22 @@
     </row>
     <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="B286" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="C286" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="D286" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="E286">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="F286">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G286">
         <v>1</v>
@@ -11487,22 +11499,22 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="B287" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="C287" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="D287" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="E287">
-        <v>150</v>
+        <v>94</v>
       </c>
       <c r="F287">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G287">
         <v>1</v>
@@ -11510,22 +11522,22 @@
     </row>
     <row r="288" spans="1:7">
       <c r="A288" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="B288" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="C288" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="D288" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="E288">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="F288">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G288">
         <v>1</v>
@@ -11533,22 +11545,22 @@
     </row>
     <row r="289" spans="1:7">
       <c r="A289" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="B289" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="C289" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="D289" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="E289">
-        <v>260</v>
+        <v>90</v>
       </c>
       <c r="F289">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G289">
         <v>1</v>
@@ -11556,114 +11568,114 @@
     </row>
     <row r="290" spans="1:7">
       <c r="A290" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="B290" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="C290" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="D290" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="E290">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="F290">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G290">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291" spans="1:7">
       <c r="A291" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="B291" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="C291" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="D291" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="E291">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="F291">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G291">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:7">
       <c r="A292" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="B292" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="C292" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="D292" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="E292">
-        <v>407</v>
+        <v>125</v>
       </c>
       <c r="F292">
-        <v>152</v>
+        <v>15</v>
       </c>
       <c r="G292">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="293" spans="1:7">
       <c r="A293" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="B293" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="C293" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="D293" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="E293">
-        <v>45</v>
+        <v>407</v>
       </c>
       <c r="F293">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="G293">
-        <v>50</v>
+        <v>107</v>
       </c>
     </row>
     <row r="294" spans="1:7">
       <c r="A294" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="B294" t="s">
-        <v>954</v>
+        <v>1126</v>
       </c>
       <c r="C294" t="s">
-        <v>955</v>
+        <v>1127</v>
       </c>
       <c r="D294" t="s">
-        <v>956</v>
+        <v>1128</v>
       </c>
       <c r="E294">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="F294">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G294">
         <v>50</v>
@@ -11671,275 +11683,275 @@
     </row>
     <row r="295" spans="1:7">
       <c r="A295" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B295" t="s">
-        <v>1131</v>
+        <v>954</v>
       </c>
       <c r="C295" t="s">
-        <v>1132</v>
+        <v>955</v>
       </c>
       <c r="D295" t="s">
-        <v>1133</v>
+        <v>956</v>
       </c>
       <c r="E295">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F295">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G295">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="296" spans="1:7">
       <c r="A296" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B296" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="C296" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="D296" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="E296">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F296">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G296">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="297" spans="1:7">
       <c r="A297" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="B297" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="C297" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="D297" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="E297">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="F297">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G297">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="298" spans="1:7">
       <c r="A298" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="B298" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="C298" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="D298" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="E298">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="F298">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G298">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="B299" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="C299" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="D299" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="E299">
-        <v>705</v>
+        <v>44</v>
       </c>
       <c r="F299">
-        <v>481</v>
+        <v>13</v>
       </c>
       <c r="G299">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="300" spans="1:7">
       <c r="A300" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="B300" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="C300" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D300" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="E300">
-        <v>592</v>
+        <v>705</v>
       </c>
       <c r="F300">
-        <v>107</v>
+        <v>481</v>
       </c>
       <c r="G300">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="301" spans="1:7">
       <c r="A301" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="B301" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="C301" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="D301" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="E301">
-        <v>500</v>
+        <v>592</v>
       </c>
       <c r="F301">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="G301">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302" spans="1:7">
       <c r="A302" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="B302" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="C302" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="D302" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="E302">
-        <v>777</v>
+        <v>500</v>
       </c>
       <c r="F302">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="G302">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303" spans="1:7">
       <c r="A303" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="B303" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="C303" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="D303" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="E303">
-        <v>786</v>
+        <v>777</v>
       </c>
       <c r="F303">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G303">
-        <v>420</v>
+        <v>6</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="B304" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="C304" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="D304" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="E304">
-        <v>379</v>
+        <v>786</v>
       </c>
       <c r="F304">
-        <v>94</v>
+        <v>410</v>
       </c>
       <c r="G304">
-        <v>35</v>
+        <v>420</v>
       </c>
     </row>
     <row r="305" spans="1:7">
       <c r="A305" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="B305" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="C305" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="D305" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="E305">
-        <v>704</v>
+        <v>379</v>
       </c>
       <c r="F305">
-        <v>333</v>
+        <v>94</v>
       </c>
       <c r="G305">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="306" spans="1:7">
       <c r="A306" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B306" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="C306" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="D306" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="E306">
-        <v>544</v>
+        <v>704</v>
       </c>
       <c r="F306">
-        <v>409</v>
+        <v>333</v>
       </c>
       <c r="G306">
         <v>2</v>
@@ -11947,936 +11959,936 @@
     </row>
     <row r="307" spans="1:7">
       <c r="A307" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="B307" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="C307" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="D307" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="E307">
-        <v>818</v>
+        <v>544</v>
       </c>
       <c r="F307">
-        <v>1144</v>
+        <v>409</v>
       </c>
       <c r="G307">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="308" spans="1:7">
       <c r="A308" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="B308" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="C308" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="D308" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="E308">
-        <v>705</v>
+        <v>818</v>
       </c>
       <c r="F308">
-        <v>854</v>
+        <v>1144</v>
       </c>
       <c r="G308">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="309" spans="1:7">
       <c r="A309" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="B309" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="C309" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="D309" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="E309">
-        <v>458</v>
+        <v>705</v>
       </c>
       <c r="F309">
-        <v>607</v>
+        <v>854</v>
       </c>
       <c r="G309">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="310" spans="1:7">
       <c r="A310" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="B310" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="C310" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="D310" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="E310">
-        <v>690</v>
+        <v>458</v>
       </c>
       <c r="F310">
-        <v>100</v>
+        <v>607</v>
       </c>
       <c r="G310">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="311" spans="1:7">
       <c r="A311" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="B311" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="C311" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="D311" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="E311">
-        <v>100</v>
+        <v>690</v>
       </c>
       <c r="F311">
         <v>100</v>
       </c>
       <c r="G311">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312" spans="1:7">
       <c r="A312" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="B312" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="C312" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="D312" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E312">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F312">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G312">
-        <v>250</v>
+        <v>40</v>
       </c>
     </row>
     <row r="313" spans="1:7">
       <c r="A313" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="B313" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="C313" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="D313" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="E313">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F313">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G313">
-        <v>360</v>
+        <v>250</v>
       </c>
     </row>
     <row r="314" spans="1:7">
       <c r="A314" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="B314" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="C314" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="D314" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="E314">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="F314">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G314">
-        <v>1000</v>
+        <v>360</v>
       </c>
     </row>
     <row r="315" spans="1:7">
       <c r="A315" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="B315" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="C315" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="D315" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E315">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="F315">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="G315">
-        <v>10</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="316" spans="1:7">
       <c r="A316" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B316" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="C316" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="D316" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="E316">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F316">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G316">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="317" spans="1:7">
       <c r="A317" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="B317" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="C317" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="D317" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="E317">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F317">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G317">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318" spans="1:7">
       <c r="A318" t="s">
-        <v>1475</v>
+        <v>1214</v>
       </c>
       <c r="B318" t="s">
-        <v>1476</v>
+        <v>1215</v>
       </c>
       <c r="C318" t="s">
-        <v>1477</v>
+        <v>1216</v>
       </c>
       <c r="D318" t="s">
-        <v>1478</v>
+        <v>1217</v>
       </c>
       <c r="E318">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F318">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G318">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="319" spans="1:7">
       <c r="A319" t="s">
-        <v>1218</v>
+        <v>1475</v>
       </c>
       <c r="B319" t="s">
-        <v>502</v>
+        <v>1476</v>
       </c>
       <c r="C319" t="s">
-        <v>503</v>
+        <v>1477</v>
       </c>
       <c r="D319" t="s">
-        <v>504</v>
+        <v>1478</v>
       </c>
       <c r="E319">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="F319">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="G319">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="320" spans="1:7">
       <c r="A320" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B320" t="s">
-        <v>1220</v>
+        <v>502</v>
       </c>
       <c r="C320" t="s">
-        <v>1221</v>
+        <v>503</v>
       </c>
       <c r="D320" t="s">
-        <v>1222</v>
+        <v>504</v>
       </c>
       <c r="E320">
-        <v>151</v>
+        <v>400</v>
       </c>
       <c r="F320">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="G320">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="321" spans="1:7">
       <c r="A321" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B321" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="C321" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D321" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="E321">
-        <v>452</v>
+        <v>151</v>
       </c>
       <c r="F321">
-        <v>264</v>
+        <v>117</v>
       </c>
       <c r="G321">
-        <v>12</v>
+        <v>90</v>
       </c>
     </row>
     <row r="322" spans="1:7">
       <c r="A322" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="B322" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="C322" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="D322" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="E322">
-        <v>160</v>
+        <v>452</v>
       </c>
       <c r="F322">
-        <v>189</v>
+        <v>264</v>
       </c>
       <c r="G322">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="323" spans="1:7">
       <c r="A323" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="B323" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="C323" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="D323" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="E323">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="F323">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="G323">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="324" spans="1:7">
       <c r="A324" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="B324" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="C324" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="D324" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="E324">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="F324">
-        <v>256</v>
+        <v>115</v>
       </c>
       <c r="G324">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="325" spans="1:7">
       <c r="A325" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="B325" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="C325" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="D325" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="E325">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="F325">
-        <v>59</v>
+        <v>256</v>
       </c>
       <c r="G325">
-        <v>910</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326" spans="1:7">
       <c r="A326" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="B326" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="C326" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="D326" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="E326">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="F326">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="G326">
-        <v>1</v>
+        <v>910</v>
       </c>
     </row>
     <row r="327" spans="1:7">
       <c r="A327" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="B327" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="C327" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="D327" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="E327">
-        <v>274</v>
+        <v>157</v>
       </c>
       <c r="F327">
-        <v>300</v>
+        <v>73</v>
       </c>
       <c r="G327">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328" spans="1:7">
       <c r="A328" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="B328" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="C328" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="D328" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="E328">
-        <v>225</v>
+        <v>274</v>
       </c>
       <c r="F328">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G328">
-        <v>600</v>
+        <v>4</v>
       </c>
     </row>
     <row r="329" spans="1:7">
       <c r="A329" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="B329" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="C329" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="D329" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="E329">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="F329">
-        <v>103</v>
+        <v>250</v>
       </c>
       <c r="G329">
-        <v>17</v>
+        <v>600</v>
       </c>
     </row>
     <row r="330" spans="1:7">
       <c r="A330" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="B330" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="C330" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="D330" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="E330">
-        <v>502</v>
+        <v>249</v>
       </c>
       <c r="F330">
-        <v>344</v>
+        <v>103</v>
       </c>
       <c r="G330">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="331" spans="1:7">
       <c r="A331" t="s">
-        <v>1227</v>
+        <v>1259</v>
       </c>
       <c r="B331" t="s">
-        <v>1228</v>
+        <v>1260</v>
       </c>
       <c r="C331" t="s">
-        <v>1229</v>
+        <v>1261</v>
       </c>
       <c r="D331" t="s">
-        <v>1230</v>
+        <v>1262</v>
       </c>
       <c r="E331">
-        <v>112</v>
+        <v>502</v>
       </c>
       <c r="F331">
-        <v>75</v>
+        <v>344</v>
       </c>
       <c r="G331">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:7">
       <c r="A332" t="s">
-        <v>1263</v>
+        <v>1227</v>
       </c>
       <c r="B332" t="s">
-        <v>1264</v>
+        <v>1228</v>
       </c>
       <c r="C332" t="s">
-        <v>1265</v>
+        <v>1229</v>
       </c>
       <c r="D332" t="s">
-        <v>1264</v>
+        <v>1230</v>
       </c>
       <c r="E332">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F332">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G332">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333" spans="1:7">
       <c r="A333" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="B333" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="C333" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="D333" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="E333">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F333">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="G333">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334" spans="1:7">
       <c r="A334" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="B334" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="C334" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="D334" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="E334">
-        <v>1390</v>
+        <v>126</v>
       </c>
       <c r="F334">
-        <v>1280</v>
+        <v>113</v>
       </c>
       <c r="G334">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335" spans="1:7">
       <c r="A335" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="B335" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="C335" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="D335" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="E335">
-        <v>380</v>
+        <v>1390</v>
       </c>
       <c r="F335">
-        <v>350</v>
+        <v>1280</v>
       </c>
       <c r="G335">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336" spans="1:7">
       <c r="A336" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="B336" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="C336" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="D336" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="E336">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="F336">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="G336">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="337" spans="1:7">
       <c r="A337" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="B337" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="C337" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="D337" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="E337">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="F337">
-        <v>120</v>
+        <v>325</v>
       </c>
       <c r="G337">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="338" spans="1:7">
       <c r="A338" t="s">
-        <v>1459</v>
+        <v>1281</v>
       </c>
       <c r="B338" t="s">
-        <v>1460</v>
+        <v>1282</v>
       </c>
       <c r="C338" t="s">
-        <v>1461</v>
+        <v>1283</v>
       </c>
       <c r="D338" t="s">
-        <v>1462</v>
+        <v>1284</v>
       </c>
       <c r="E338">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="F338">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="G338">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="339" spans="1:7">
       <c r="A339" t="s">
-        <v>1285</v>
+        <v>1459</v>
       </c>
       <c r="B339" t="s">
-        <v>1286</v>
+        <v>1460</v>
       </c>
       <c r="C339" t="s">
-        <v>1287</v>
+        <v>1461</v>
       </c>
       <c r="D339" t="s">
-        <v>1288</v>
+        <v>1462</v>
       </c>
       <c r="E339">
-        <v>260</v>
+        <v>31</v>
       </c>
       <c r="F339">
-        <v>250</v>
+        <v>36</v>
       </c>
       <c r="G339">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340" spans="1:7">
       <c r="A340" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="B340" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="C340" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="D340" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="E340">
-        <v>355</v>
+        <v>260</v>
       </c>
       <c r="F340">
-        <v>342</v>
+        <v>250</v>
       </c>
       <c r="G340">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="341" spans="1:7">
       <c r="A341" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="B341" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="C341" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="D341" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="E341">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="F341">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="G341">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="342" spans="1:7">
       <c r="A342" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="B342" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="C342" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D342" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="E342">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="F342">
-        <v>98</v>
+        <v>391</v>
       </c>
       <c r="G342">
-        <v>390</v>
+        <v>5</v>
       </c>
     </row>
     <row r="343" spans="1:7">
       <c r="A343" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="B343" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="C343" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="D343" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="E343">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="F343">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="G343">
-        <v>564</v>
+        <v>390</v>
       </c>
     </row>
     <row r="344" spans="1:7">
       <c r="A344" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="B344" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="C344" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="D344" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="E344">
-        <v>219</v>
+        <v>348</v>
       </c>
       <c r="F344">
-        <v>140</v>
+        <v>298</v>
       </c>
       <c r="G344">
-        <v>281</v>
+        <v>564</v>
       </c>
     </row>
     <row r="345" spans="1:7">
       <c r="A345" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="B345" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="C345" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="D345" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="E345">
-        <v>32</v>
+        <v>219</v>
       </c>
       <c r="F345">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="G345">
-        <v>400</v>
+        <v>281</v>
       </c>
     </row>
     <row r="346" spans="1:7">
       <c r="A346" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B346" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C346" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="D346" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="E346">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F346">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="G346">
-        <v>1</v>
+        <v>400</v>
       </c>
     </row>
     <row r="347" spans="1:7">
       <c r="A347" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="B347" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="C347" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="D347" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="E347">
         <v>70</v>
@@ -12890,183 +12902,183 @@
     </row>
     <row r="348" spans="1:7">
       <c r="A348" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="B348" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="C348" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D348" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="E348">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="F348">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="G348">
-        <v>400</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349" spans="1:7">
       <c r="A349" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="B349" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="C349" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="D349" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="E349">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="F349">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G349">
-        <v>150</v>
+        <v>400</v>
       </c>
     </row>
     <row r="350" spans="1:7">
       <c r="A350" t="s">
-        <v>1489</v>
+        <v>1322</v>
       </c>
       <c r="B350" t="s">
-        <v>1492</v>
+        <v>1323</v>
       </c>
       <c r="C350" t="s">
-        <v>1491</v>
+        <v>1324</v>
       </c>
       <c r="D350" t="s">
-        <v>1490</v>
+        <v>1325</v>
       </c>
       <c r="E350">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F350">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="G350">
-        <v>180</v>
+        <v>150</v>
       </c>
     </row>
     <row r="351" spans="1:7">
       <c r="A351" t="s">
-        <v>1326</v>
+        <v>1489</v>
       </c>
       <c r="B351" t="s">
-        <v>1327</v>
+        <v>1492</v>
       </c>
       <c r="C351" t="s">
-        <v>1328</v>
+        <v>1491</v>
       </c>
       <c r="D351" t="s">
-        <v>1329</v>
+        <v>1490</v>
       </c>
       <c r="E351">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="F351">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="G351">
-        <v>450</v>
+        <v>180</v>
       </c>
     </row>
     <row r="352" spans="1:7">
       <c r="A352" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="B352" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="C352" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="D352" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="E352">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="F352">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="G352">
-        <v>100</v>
+        <v>450</v>
       </c>
     </row>
     <row r="353" spans="1:7">
       <c r="A353" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="B353" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="C353" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="D353" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="E353">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F353">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="G353">
-        <v>350</v>
+        <v>100</v>
       </c>
     </row>
     <row r="354" spans="1:7">
       <c r="A354" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="B354" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="C354" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="D354" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="E354">
+        <v>200</v>
+      </c>
+      <c r="F354">
         <v>150</v>
       </c>
-      <c r="F354">
-        <v>110</v>
-      </c>
       <c r="G354">
-        <v>500</v>
+        <v>350</v>
       </c>
     </row>
     <row r="355" spans="1:7">
       <c r="A355" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="B355" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="C355" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="D355" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="E355">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F355">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="G355">
         <v>500</v>
@@ -13074,16 +13086,16 @@
     </row>
     <row r="356" spans="1:7">
       <c r="A356" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="B356" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="C356" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="D356" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="E356">
         <v>100</v>
@@ -13097,22 +13109,22 @@
     </row>
     <row r="357" spans="1:7">
       <c r="A357" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="B357" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="C357" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="D357" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="E357">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="F357">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="G357">
         <v>500</v>
@@ -13120,45 +13132,45 @@
     </row>
     <row r="358" spans="1:7">
       <c r="A358" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="B358" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="C358" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="D358" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="E358">
-        <v>338</v>
+        <v>145</v>
       </c>
       <c r="F358">
-        <v>347</v>
+        <v>135</v>
       </c>
       <c r="G358">
-        <v>370</v>
+        <v>500</v>
       </c>
     </row>
     <row r="359" spans="1:7">
       <c r="A359" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="B359" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="C359" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="D359" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="E359">
-        <v>209</v>
+        <v>338</v>
       </c>
       <c r="F359">
-        <v>244</v>
+        <v>347</v>
       </c>
       <c r="G359">
         <v>370</v>
@@ -13166,691 +13178,714 @@
     </row>
     <row r="360" spans="1:7">
       <c r="A360" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B360" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C360" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D360" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E360">
+        <v>209</v>
+      </c>
+      <c r="F360">
+        <v>244</v>
+      </c>
+      <c r="G360">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7">
+      <c r="A361" t="s">
         <v>1362</v>
       </c>
-      <c r="B360" t="s">
+      <c r="B361" t="s">
         <v>1363</v>
       </c>
-      <c r="C360" t="s">
+      <c r="C361" t="s">
         <v>1364</v>
       </c>
-      <c r="D360" t="s">
+      <c r="D361" t="s">
         <v>1365</v>
       </c>
-      <c r="E360">
+      <c r="E361">
         <v>131</v>
       </c>
-      <c r="F360">
+      <c r="F361">
         <v>120</v>
       </c>
-      <c r="G360">
+      <c r="G361">
         <v>635</v>
       </c>
     </row>
-    <row r="361" spans="1:7" s="2" customFormat="1" ht="17.850000000000001" customHeight="1">
-      <c r="A361" s="2" t="s">
+    <row r="362" spans="1:7" s="2" customFormat="1" ht="17.850000000000001" customHeight="1">
+      <c r="A362" s="2" t="s">
         <v>1497</v>
       </c>
-      <c r="B361" s="2" t="s">
+      <c r="B362" s="2" t="s">
         <v>1500</v>
       </c>
-      <c r="C361" s="2" t="s">
+      <c r="C362" s="2" t="s">
         <v>1501</v>
       </c>
-      <c r="D361" s="3" t="s">
+      <c r="D362" s="3" t="s">
         <v>1502</v>
       </c>
-      <c r="E361" s="2">
+      <c r="E362" s="2">
         <v>42</v>
       </c>
-      <c r="F361" s="2">
+      <c r="F362" s="2">
         <v>14</v>
       </c>
-      <c r="G361" s="2">
+      <c r="G362" s="2">
         <v>88</v>
       </c>
     </row>
-    <row r="362" spans="1:7" s="2" customFormat="1" ht="16.7" customHeight="1">
-      <c r="A362" s="2" t="s">
+    <row r="363" spans="1:7" s="2" customFormat="1" ht="16.7" customHeight="1">
+      <c r="A363" s="2" t="s">
         <v>1498</v>
       </c>
-      <c r="B362" s="3" t="s">
+      <c r="B363" s="3" t="s">
         <v>1505</v>
       </c>
-      <c r="C362" s="2" t="s">
+      <c r="C363" s="2" t="s">
         <v>1504</v>
       </c>
-      <c r="D362" s="2" t="s">
+      <c r="D363" s="2" t="s">
         <v>1503</v>
       </c>
-      <c r="E362" s="2">
+      <c r="E363" s="2">
         <v>53</v>
       </c>
-      <c r="F362" s="2">
+      <c r="F363" s="2">
         <v>9</v>
       </c>
-      <c r="G362" s="2">
+      <c r="G363" s="2">
         <v>96</v>
       </c>
     </row>
-    <row r="363" spans="1:7" s="2" customFormat="1" ht="19.05" customHeight="1">
-      <c r="A363" s="2" t="s">
+    <row r="364" spans="1:7" s="2" customFormat="1" ht="19.05" customHeight="1">
+      <c r="A364" s="2" t="s">
         <v>1499</v>
       </c>
-      <c r="B363" s="2" t="s">
+      <c r="B364" s="2" t="s">
         <v>1506</v>
       </c>
-      <c r="C363" s="3" t="s">
+      <c r="C364" s="3" t="s">
         <v>1507</v>
       </c>
-      <c r="D363" s="4" t="s">
+      <c r="D364" s="4" t="s">
         <v>1508</v>
       </c>
-      <c r="E363" s="2">
+      <c r="E364" s="2">
         <v>77</v>
       </c>
-      <c r="F363" s="2">
+      <c r="F364" s="2">
         <v>47</v>
       </c>
-      <c r="G363" s="2">
+      <c r="G364" s="2">
         <v>223</v>
-      </c>
-    </row>
-    <row r="364" spans="1:7">
-      <c r="A364" t="s">
-        <v>1366</v>
-      </c>
-      <c r="B364" t="s">
-        <v>1367</v>
-      </c>
-      <c r="C364" t="s">
-        <v>1368</v>
-      </c>
-      <c r="D364" t="s">
-        <v>1369</v>
-      </c>
-      <c r="E364">
-        <v>1</v>
-      </c>
-      <c r="F364">
-        <v>1</v>
-      </c>
-      <c r="G364">
-        <v>10</v>
       </c>
     </row>
     <row r="365" spans="1:7">
       <c r="A365" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B365" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C365" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D365" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E365">
+        <v>1</v>
+      </c>
+      <c r="F365">
+        <v>1</v>
+      </c>
+      <c r="G365">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7">
+      <c r="A366" t="s">
         <v>1370</v>
       </c>
-      <c r="B365" t="s">
+      <c r="B366" t="s">
         <v>1371</v>
       </c>
-      <c r="C365" t="s">
+      <c r="C366" t="s">
         <v>1372</v>
       </c>
-      <c r="D365" t="s">
+      <c r="D366" t="s">
         <v>1373</v>
       </c>
-      <c r="E365">
+      <c r="E366">
         <v>0</v>
-      </c>
-      <c r="F365">
-        <v>0</v>
-      </c>
-      <c r="G365">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="366" spans="1:7" ht="15">
-      <c r="A366" t="s">
-        <v>1493</v>
-      </c>
-      <c r="B366" s="1" t="s">
-        <v>1494</v>
-      </c>
-      <c r="C366" s="1" t="s">
-        <v>1495</v>
-      </c>
-      <c r="D366" s="1" t="s">
-        <v>1496</v>
-      </c>
-      <c r="E366">
-        <v>1</v>
       </c>
       <c r="F366">
         <v>0</v>
       </c>
       <c r="G366">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="367" spans="1:7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" ht="15">
       <c r="A367" t="s">
-        <v>1374</v>
-      </c>
-      <c r="B367" t="s">
-        <v>1375</v>
-      </c>
-      <c r="C367" t="s">
-        <v>1376</v>
-      </c>
-      <c r="D367" t="s">
-        <v>1377</v>
+        <v>1493</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>1496</v>
       </c>
       <c r="E367">
         <v>1</v>
       </c>
       <c r="F367">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G367">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="368" spans="1:7">
       <c r="A368" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="B368" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="C368" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="D368" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="E368">
-        <v>10.8</v>
+        <v>1</v>
       </c>
       <c r="F368">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G368">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="369" spans="1:7">
       <c r="A369" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="B369" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="C369" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="D369" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="E369">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="F369">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G369">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="370" spans="1:7">
       <c r="A370" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="B370" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="C370" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="D370" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
       <c r="E370">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F370">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G370">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="371" spans="1:7">
       <c r="A371" t="s">
-        <v>1482</v>
+        <v>1386</v>
       </c>
       <c r="B371" t="s">
-        <v>1483</v>
+        <v>1387</v>
       </c>
       <c r="C371" t="s">
-        <v>1484</v>
+        <v>1388</v>
       </c>
       <c r="D371" t="s">
-        <v>1485</v>
+        <v>1389</v>
       </c>
       <c r="E371">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F371">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="G371">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="372" spans="1:7">
       <c r="A372" t="s">
-        <v>1390</v>
+        <v>1482</v>
       </c>
       <c r="B372" t="s">
-        <v>1391</v>
+        <v>1483</v>
       </c>
       <c r="C372" t="s">
-        <v>1392</v>
+        <v>1484</v>
       </c>
       <c r="D372" t="s">
-        <v>1393</v>
+        <v>1485</v>
       </c>
       <c r="E372">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F372">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G372">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="373" spans="1:7">
       <c r="A373" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
       <c r="B373" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="C373" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="D373" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="E373">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F373">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G373">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="374" spans="1:7">
       <c r="A374" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B374" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="C374" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="D374" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="E374">
-        <v>400</v>
+        <v>37</v>
       </c>
       <c r="F374">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G374">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="375" spans="1:7">
       <c r="A375" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B375" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="C375" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="D375" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E375">
-        <v>549</v>
+        <v>400</v>
       </c>
       <c r="F375">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c r="G375">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
-        <v>1479</v>
+        <v>1402</v>
       </c>
       <c r="B376" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="C376" t="s">
-        <v>1481</v>
+        <v>1404</v>
       </c>
       <c r="D376" t="s">
-        <v>1480</v>
+        <v>1405</v>
       </c>
       <c r="E376">
-        <v>15</v>
+        <v>549</v>
       </c>
       <c r="F376">
-        <v>9</v>
+        <v>152</v>
       </c>
       <c r="G376">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="377" spans="1:7">
       <c r="A377" t="s">
-        <v>1407</v>
+        <v>1479</v>
       </c>
       <c r="B377" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="C377" t="s">
-        <v>1409</v>
+        <v>1481</v>
       </c>
       <c r="D377" t="s">
-        <v>1410</v>
+        <v>1480</v>
       </c>
       <c r="E377">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="F377">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="G377">
-        <v>150</v>
+        <v>15</v>
       </c>
     </row>
     <row r="378" spans="1:7">
       <c r="A378" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B378" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="C378" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="D378" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="E378">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="F378">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="G378">
-        <v>2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="379" spans="1:7">
       <c r="A379" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="B379" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="C379" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="D379" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="E379">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="F379">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G379">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="380" spans="1:7">
       <c r="A380" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="B380" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="C380" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="D380" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
       <c r="E380">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F380">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="G380">
-        <v>39</v>
+        <v>4</v>
       </c>
     </row>
     <row r="381" spans="1:7">
       <c r="A381" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
       <c r="B381" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
       <c r="C381" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="D381" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="E381">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="F381">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G381">
-        <v>91</v>
+        <v>39</v>
       </c>
     </row>
     <row r="382" spans="1:7">
       <c r="A382" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="B382" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="C382" t="s">
-        <v>1429</v>
+        <v>1425</v>
       </c>
       <c r="D382" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
       <c r="E382">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="F382">
         <v>0</v>
       </c>
       <c r="G382">
-        <v>219</v>
+        <v>91</v>
       </c>
     </row>
     <row r="383" spans="1:7">
       <c r="A383" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
       <c r="B383" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="C383" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="D383" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="E383">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="F383">
         <v>0</v>
       </c>
       <c r="G383">
-        <v>119</v>
+        <v>219</v>
       </c>
     </row>
     <row r="384" spans="1:7">
       <c r="A384" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
       <c r="B384" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="C384" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="D384" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="E384">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F384">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G384">
-        <v>14</v>
+        <v>119</v>
       </c>
     </row>
     <row r="385" spans="1:7">
       <c r="A385" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="B385" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="C385" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
       <c r="D385" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="E385">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F385">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G385">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="386" spans="1:7">
       <c r="A386" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="B386" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="C386" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="D386" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="E386">
         <v>27</v>
       </c>
       <c r="F386">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G386">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="387" spans="1:7">
       <c r="A387" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="B387" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="C387" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="D387" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="E387">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="F387">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G387">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="388" spans="1:7">
       <c r="A388" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="B388" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="C388" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="D388" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="E388">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="F388">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G388">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389" spans="1:7">
       <c r="A389" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B389" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C389" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D389" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E389">
+        <v>102</v>
+      </c>
+      <c r="F389">
+        <v>10</v>
+      </c>
+      <c r="G389">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7">
+      <c r="A390" t="s">
         <v>1455</v>
       </c>
-      <c r="B389" t="s">
+      <c r="B390" t="s">
         <v>1456</v>
       </c>
-      <c r="C389" t="s">
+      <c r="C390" t="s">
         <v>1457</v>
       </c>
-      <c r="D389" t="s">
+      <c r="D390" t="s">
         <v>1458</v>
       </c>
-      <c r="E389">
+      <c r="E390">
         <v>0</v>
       </c>
-      <c r="F389">
+      <c r="F390">
         <v>0</v>
       </c>
-      <c r="G389">
+      <c r="G390">
         <v>0</v>
       </c>
     </row>

--- a/KPH-AI-GLOBAL.xlsx
+++ b/KPH-AI-GLOBAL.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="1513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="1521">
   <si>
     <t>Namirnica</t>
   </si>
@@ -4508,9 +4508,6 @@
   </si>
   <si>
     <t>Hleb sa marmeladom namaz snita</t>
-  </si>
-  <si>
-    <t>Hleb sa medom namaz snita</t>
   </si>
   <si>
     <t>Kiflice sa dzemom</t>
@@ -4556,6 +4553,33 @@
   </si>
   <si>
     <t>Trapist-Käse</t>
+  </si>
+  <si>
+    <t>Supa kocka porcija tanjir 250ml</t>
+  </si>
+  <si>
+    <t>Soup cube plate portion 250ml</t>
+  </si>
+  <si>
+    <t>cubo de sopa ración de plato 250ml</t>
+  </si>
+  <si>
+    <t>Suppenwürfel Tellerportion 250 ml</t>
+  </si>
+  <si>
+    <t>Sok Limunada 6%</t>
+  </si>
+  <si>
+    <t>Limonade 6%</t>
+  </si>
+  <si>
+    <t>Limonada 6%</t>
+  </si>
+  <si>
+    <t>Lemonade 6%</t>
+  </si>
+  <si>
+    <t>Hleb sa medom namaz 1 snita</t>
   </si>
 </sst>
 </file>
@@ -4913,12 +4937,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G390"/>
+  <dimension ref="A1:G392"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.796875" customWidth="1"/>
-    <col min="3" max="3" width="25.296875" customWidth="1"/>
+    <col min="3" max="3" width="57.09765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="57.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8213,16 +8237,16 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B144" t="s">
         <v>1509</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" t="s">
         <v>1510</v>
       </c>
-      <c r="C144" t="s">
+      <c r="D144" t="s">
         <v>1511</v>
-      </c>
-      <c r="D144" t="s">
-        <v>1512</v>
       </c>
       <c r="E144">
         <v>130</v>
@@ -9616,413 +9640,413 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>788</v>
+        <v>1512</v>
       </c>
       <c r="B205" t="s">
-        <v>789</v>
+        <v>1513</v>
       </c>
       <c r="C205" t="s">
-        <v>790</v>
+        <v>1514</v>
       </c>
       <c r="D205" t="s">
-        <v>791</v>
+        <v>1515</v>
       </c>
       <c r="E205">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="F205">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="G205">
-        <v>235</v>
+        <v>450</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="B206" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="C206" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="D206" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="E206">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="F206">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="G206">
-        <v>455</v>
+        <v>235</v>
       </c>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B207" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="C207" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="D207" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="E207">
-        <v>340</v>
+        <v>550</v>
       </c>
       <c r="F207">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G207">
-        <v>1</v>
+        <v>455</v>
       </c>
     </row>
     <row r="208" spans="1:7">
       <c r="A208" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="B208" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="C208" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="D208" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="E208">
-        <v>250</v>
+        <v>340</v>
       </c>
       <c r="F208">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="G208">
-        <v>212</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B209" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C209" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="D209" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="E209">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F209">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="G209">
-        <v>2</v>
+        <v>212</v>
       </c>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="B210" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="C210" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="D210" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="E210">
-        <v>550</v>
+        <v>248</v>
       </c>
       <c r="F210">
-        <v>230</v>
+        <v>37</v>
       </c>
       <c r="G210">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211" spans="1:7">
       <c r="A211" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B211" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="C211" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="D211" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="E211">
-        <v>1680</v>
+        <v>550</v>
       </c>
       <c r="F211">
-        <v>555</v>
+        <v>230</v>
       </c>
       <c r="G211">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:7">
       <c r="A212" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="B212" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="C212" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="D212" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="E212">
-        <v>121</v>
+        <v>1680</v>
       </c>
       <c r="F212">
-        <v>97</v>
+        <v>555</v>
       </c>
       <c r="G212">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B213" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="C213" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="D213" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E213">
-        <v>1660</v>
+        <v>121</v>
       </c>
       <c r="F213">
-        <v>600</v>
+        <v>97</v>
       </c>
       <c r="G213">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="B214" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="C214" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="D214" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="E214">
-        <v>137</v>
+        <v>1660</v>
       </c>
       <c r="F214">
-        <v>57</v>
+        <v>600</v>
       </c>
       <c r="G214">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:7">
       <c r="A215" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="B215" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="C215" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="D215" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="E215">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F215">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G215">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:7">
       <c r="A216" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="B216" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="C216" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="D216" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="E216">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="F216">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="G216">
-        <v>0.3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="217" spans="1:7">
       <c r="A217" t="s">
-        <v>1486</v>
+        <v>832</v>
       </c>
       <c r="B217" t="s">
-        <v>1487</v>
+        <v>833</v>
       </c>
       <c r="C217" t="s">
-        <v>1487</v>
+        <v>834</v>
       </c>
       <c r="D217" t="s">
-        <v>1488</v>
+        <v>835</v>
       </c>
       <c r="E217">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="F217">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="G217">
-        <v>400</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="218" spans="1:7">
       <c r="A218" t="s">
-        <v>836</v>
+        <v>1486</v>
       </c>
       <c r="B218" t="s">
-        <v>837</v>
+        <v>1487</v>
       </c>
       <c r="C218" t="s">
-        <v>838</v>
+        <v>1487</v>
       </c>
       <c r="D218" t="s">
-        <v>839</v>
+        <v>1488</v>
       </c>
       <c r="E218">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="F218">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G218">
-        <v>7</v>
+        <v>400</v>
       </c>
     </row>
     <row r="219" spans="1:7">
       <c r="A219" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="B219" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="C219" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="D219" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="E219">
-        <v>3170</v>
+        <v>340</v>
       </c>
       <c r="F219">
-        <v>327</v>
+        <v>46</v>
       </c>
       <c r="G219">
-        <v>193</v>
+        <v>7</v>
       </c>
     </row>
     <row r="220" spans="1:7">
       <c r="A220" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B220" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="C220" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="D220" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="E220">
-        <v>129</v>
+        <v>3170</v>
       </c>
       <c r="F220">
-        <v>25</v>
+        <v>327</v>
       </c>
       <c r="G220">
-        <v>8</v>
+        <v>193</v>
       </c>
     </row>
     <row r="221" spans="1:7">
       <c r="A221" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B221" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="C221" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="D221" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="E221">
-        <v>176</v>
+        <v>129</v>
       </c>
       <c r="F221">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G221">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:7">
       <c r="A222" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B222" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="C222" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="D222" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="E222">
-        <v>305</v>
+        <v>176</v>
       </c>
       <c r="F222">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G222">
         <v>2</v>
@@ -10030,436 +10054,436 @@
     </row>
     <row r="223" spans="1:7">
       <c r="A223" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B223" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C223" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="D223" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="E223">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="F223">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G223">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224" spans="1:7">
       <c r="A224" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="B224" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C224" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="D224" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="E224">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="F224">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="G224">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="225" spans="1:7">
       <c r="A225" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="B225" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="C225" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="D225" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="E225">
-        <v>310</v>
+        <v>207</v>
       </c>
       <c r="F225">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="G225">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="226" spans="1:7">
       <c r="A226" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B226" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C226" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="D226" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="E226">
-        <v>192</v>
+        <v>310</v>
       </c>
       <c r="F226">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G226">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:7">
       <c r="A227" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="B227" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="C227" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="D227" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="E227">
-        <v>400</v>
+        <v>192</v>
       </c>
       <c r="F227">
-        <v>153</v>
+        <v>36</v>
       </c>
       <c r="G227">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" spans="1:7">
       <c r="A228" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="B228" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="C228" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="D228" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="E228">
-        <v>234</v>
+        <v>400</v>
       </c>
       <c r="F228">
-        <v>49</v>
+        <v>153</v>
       </c>
       <c r="G228">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="229" spans="1:7">
       <c r="A229" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B229" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="C229" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="D229" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="E229">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="F229">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G229">
-        <v>274</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230" spans="1:7">
       <c r="A230" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="B230" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="C230" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="D230" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="E230">
-        <v>269</v>
+        <v>148</v>
       </c>
       <c r="F230">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="G230">
-        <v>759</v>
+        <v>274</v>
       </c>
     </row>
     <row r="231" spans="1:7">
       <c r="A231" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="B231" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="C231" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="D231" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="E231">
-        <v>50</v>
+        <v>269</v>
       </c>
       <c r="F231">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="G231">
-        <v>1353</v>
+        <v>759</v>
       </c>
     </row>
     <row r="232" spans="1:7">
       <c r="A232" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B232" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C232" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="D232" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="E232">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="F232">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G232">
-        <v>650</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="233" spans="1:7">
       <c r="A233" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="B233" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="C233" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="D233" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="E233">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="F233">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G233">
-        <v>2100</v>
+        <v>650</v>
       </c>
     </row>
     <row r="234" spans="1:7">
       <c r="A234" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="B234" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="C234" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="D234" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="E234">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="F234">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G234">
-        <v>1248</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="235" spans="1:7">
       <c r="A235" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B235" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="C235" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="D235" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="E235">
-        <v>800</v>
+        <v>131</v>
       </c>
       <c r="F235">
         <v>20</v>
       </c>
       <c r="G235">
-        <v>1200</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="236" spans="1:7">
       <c r="A236" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="B236" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="C236" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="D236" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="E236">
-        <v>220</v>
+        <v>800</v>
       </c>
       <c r="F236">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G236">
-        <v>360</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="237" spans="1:7">
       <c r="A237" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="B237" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="C237" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="D237" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="E237">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="F237">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="G237">
-        <v>450</v>
+        <v>360</v>
       </c>
     </row>
     <row r="238" spans="1:7">
       <c r="A238" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B238" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="C238" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="D238" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="E238">
+        <v>1000</v>
+      </c>
+      <c r="F238">
+        <v>70</v>
+      </c>
+      <c r="G238">
         <v>450</v>
-      </c>
-      <c r="F238">
-        <v>50</v>
-      </c>
-      <c r="G238">
-        <v>3</v>
       </c>
     </row>
     <row r="239" spans="1:7">
       <c r="A239" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="B239" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="C239" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="D239" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="E239">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="F239">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="G239">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240" spans="1:7">
       <c r="A240" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B240" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="C240" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="D240" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="E240">
-        <v>346</v>
+        <v>422</v>
       </c>
       <c r="F240">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G240">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:7">
       <c r="A241" t="s">
-        <v>1472</v>
+        <v>923</v>
       </c>
       <c r="B241" t="s">
-        <v>1473</v>
+        <v>924</v>
       </c>
       <c r="C241" t="s">
-        <v>1474</v>
+        <v>925</v>
       </c>
       <c r="D241" t="s">
-        <v>1473</v>
+        <v>926</v>
       </c>
       <c r="E241">
-        <v>277</v>
+        <v>346</v>
       </c>
       <c r="F241">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="G241">
         <v>2</v>
@@ -10467,114 +10491,114 @@
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
-        <v>927</v>
+        <v>1472</v>
       </c>
       <c r="B242" t="s">
-        <v>928</v>
+        <v>1473</v>
       </c>
       <c r="C242" t="s">
-        <v>929</v>
+        <v>1474</v>
       </c>
       <c r="D242" t="s">
-        <v>930</v>
+        <v>1473</v>
       </c>
       <c r="E242">
-        <v>149</v>
+        <v>277</v>
       </c>
       <c r="F242">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G242">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="B243" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="C243" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D243" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="E243">
-        <v>210</v>
+        <v>149</v>
       </c>
       <c r="F243">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G243">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B244" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C244" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="D244" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="E244">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="F244">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G244">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B245" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="C245" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="D245" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="E245">
-        <v>177</v>
+        <v>260</v>
       </c>
       <c r="F245">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G245">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="246" spans="1:7">
       <c r="A246" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="B246" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="C246" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="D246" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="E246">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="F246">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G246">
         <v>1</v>
@@ -10582,68 +10606,68 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B247" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C247" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="D247" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="E247">
-        <v>782</v>
+        <v>81</v>
       </c>
       <c r="F247">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="G247">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:7">
       <c r="A248" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="B248" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="C248" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="D248" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="E248">
-        <v>192</v>
+        <v>782</v>
       </c>
       <c r="F248">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="G248">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="249" spans="1:7">
       <c r="A249" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B249" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="C249" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="D249" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="E249">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="F249">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G249">
         <v>2</v>
@@ -10651,111 +10675,111 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="B250" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="C250" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="D250" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="E250">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="F250">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G250">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251" spans="1:7">
       <c r="A251" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="B251" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C251" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="D251" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="E251">
-        <v>310</v>
+        <v>170</v>
       </c>
       <c r="F251">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G251">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:7">
       <c r="A252" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="B252" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="C252" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="D252" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="E252">
-        <v>238</v>
+        <v>310</v>
       </c>
       <c r="F252">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G252">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253" spans="1:7">
       <c r="A253" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B253" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="C253" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="D253" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="E253">
-        <v>114</v>
+        <v>238</v>
+      </c>
+      <c r="F253">
+        <v>27</v>
       </c>
       <c r="G253">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:7">
       <c r="A254" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B254" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="C254" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="D254" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="E254">
-        <v>144</v>
-      </c>
-      <c r="F254">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G254">
         <v>3</v>
@@ -10763,229 +10787,229 @@
     </row>
     <row r="255" spans="1:7">
       <c r="A255" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="B255" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="C255" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="D255" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="E255">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="F255">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G255">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256" spans="1:7">
       <c r="A256" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="B256" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="C256" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D256" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="E256">
-        <v>1340</v>
+        <v>126</v>
       </c>
       <c r="F256">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="G256">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257" spans="1:7">
       <c r="A257" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B257" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="C257" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="D257" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="E257">
-        <v>205</v>
+        <v>1340</v>
       </c>
       <c r="F257">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="G257">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="258" spans="1:7">
       <c r="A258" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="B258" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="C258" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="D258" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="E258">
-        <v>1370</v>
+        <v>205</v>
       </c>
       <c r="F258">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="G258">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259" spans="1:7">
       <c r="A259" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="B259" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="C259" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="D259" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="E259">
-        <v>278</v>
+        <v>1370</v>
       </c>
       <c r="F259">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="G259">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="260" spans="1:7">
       <c r="A260" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B260" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="C260" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="D260" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="E260">
-        <v>860</v>
+        <v>278</v>
       </c>
       <c r="F260">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="G260">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261" spans="1:7">
       <c r="A261" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="B261" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="C261" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="D261" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="E261">
-        <v>221</v>
+        <v>860</v>
       </c>
       <c r="F261">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="G261">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="262" spans="1:7">
       <c r="A262" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B262" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C262" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="D262" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="E262">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="F262">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G262">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="263" spans="1:7">
       <c r="A263" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="B263" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="C263" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="D263" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="E263">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="F263">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G263">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="264" spans="1:7">
       <c r="A264" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="B264" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="C264" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="D264" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E264">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="F264">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G264">
         <v>2</v>
@@ -10993,229 +11017,229 @@
     </row>
     <row r="265" spans="1:7">
       <c r="A265" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="B265" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="C265" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="D265" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="E265">
-        <v>503</v>
+        <v>173</v>
       </c>
       <c r="F265">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="G265">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266" spans="1:7">
       <c r="A266" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="B266" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="C266" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="D266" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="E266">
-        <v>393</v>
+        <v>503</v>
       </c>
       <c r="F266">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G266">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="267" spans="1:7">
       <c r="A267" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B267" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="C267" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="D267" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="E267">
-        <v>295</v>
+        <v>393</v>
       </c>
       <c r="F267">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G267">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:7">
       <c r="A268" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B268" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C268" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="D268" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E268">
-        <v>190</v>
+        <v>295</v>
       </c>
       <c r="F268">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G268">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="269" spans="1:7">
       <c r="A269" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B269" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="C269" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="D269" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="E269">
-        <v>330</v>
+        <v>190</v>
       </c>
       <c r="F269">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G269">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="270" spans="1:7">
       <c r="A270" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="B270" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="C270" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="D270" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="E270">
-        <v>158</v>
+        <v>330</v>
       </c>
       <c r="F270">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G270">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="271" spans="1:7">
       <c r="A271" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="B271" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="C271" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="D271" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E271">
-        <v>240</v>
+        <v>158</v>
       </c>
       <c r="F271">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G271">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272" spans="1:7">
       <c r="A272" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="B272" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="C272" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="D272" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="E272">
-        <v>850</v>
+        <v>240</v>
       </c>
       <c r="F272">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="G272">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="B273" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="C273" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="D273" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="E273">
-        <v>140</v>
+        <v>850</v>
       </c>
       <c r="F273">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="G273">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="B274" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="C274" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="D274" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="E274">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="F274">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G274">
         <v>1</v>
@@ -11223,226 +11247,226 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="B275" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="C275" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="D275" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="E275">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F275">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G275">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="B276" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C276" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="D276" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="E276">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="F276">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G276">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="B277" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="C277" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="D277" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="E277">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F277">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G277">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="278" spans="1:7">
       <c r="A278" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="B278" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="C278" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="D278" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="E278">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F278">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G278">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279" spans="1:7">
       <c r="A279" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="B279" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="C279" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="D279" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="E279">
-        <v>33</v>
+        <v>200</v>
       </c>
       <c r="F279">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G279">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="B280" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="C280" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="D280" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="E280">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="F280">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G280">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="B281" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="C281" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="D281" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="E281">
-        <v>362</v>
+        <v>78</v>
       </c>
       <c r="F281">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G281">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="B282" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="C282" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="D282" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="E282">
-        <v>50</v>
+        <v>362</v>
       </c>
       <c r="F282">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G282">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="B283" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="C283" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="D283" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="E283">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F283">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G283">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="B284" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="C284" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="D284" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="E284">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F284">
         <v>10</v>
@@ -11453,22 +11477,22 @@
     </row>
     <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="B285" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="C285" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="D285" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="E285">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F285">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G285">
         <v>1</v>
@@ -11476,22 +11500,22 @@
     </row>
     <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="B286" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C286" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D286" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="E286">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="F286">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G286">
         <v>1</v>
@@ -11499,22 +11523,22 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="B287" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="C287" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="D287" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="E287">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="F287">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G287">
         <v>1</v>
@@ -11522,22 +11546,22 @@
     </row>
     <row r="288" spans="1:7">
       <c r="A288" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="B288" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="C288" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="D288" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="E288">
-        <v>150</v>
+        <v>94</v>
       </c>
       <c r="F288">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G288">
         <v>1</v>
@@ -11545,22 +11569,22 @@
     </row>
     <row r="289" spans="1:7">
       <c r="A289" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="B289" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="C289" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="D289" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="E289">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="F289">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G289">
         <v>1</v>
@@ -11568,22 +11592,22 @@
     </row>
     <row r="290" spans="1:7">
       <c r="A290" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="B290" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="C290" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="D290" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="E290">
-        <v>260</v>
+        <v>90</v>
       </c>
       <c r="F290">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G290">
         <v>1</v>
@@ -11591,114 +11615,114 @@
     </row>
     <row r="291" spans="1:7">
       <c r="A291" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="B291" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="C291" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="D291" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="E291">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="F291">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G291">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292" spans="1:7">
       <c r="A292" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="B292" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="C292" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="D292" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="E292">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="F292">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G292">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:7">
       <c r="A293" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="B293" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="C293" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="D293" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="E293">
-        <v>407</v>
+        <v>125</v>
       </c>
       <c r="F293">
-        <v>152</v>
+        <v>15</v>
       </c>
       <c r="G293">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="294" spans="1:7">
       <c r="A294" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="B294" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="C294" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="D294" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="E294">
-        <v>45</v>
+        <v>407</v>
       </c>
       <c r="F294">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="G294">
-        <v>50</v>
+        <v>107</v>
       </c>
     </row>
     <row r="295" spans="1:7">
       <c r="A295" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="B295" t="s">
-        <v>954</v>
+        <v>1126</v>
       </c>
       <c r="C295" t="s">
-        <v>955</v>
+        <v>1127</v>
       </c>
       <c r="D295" t="s">
-        <v>956</v>
+        <v>1128</v>
       </c>
       <c r="E295">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="F295">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G295">
         <v>50</v>
@@ -11706,275 +11730,275 @@
     </row>
     <row r="296" spans="1:7">
       <c r="A296" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B296" t="s">
-        <v>1131</v>
+        <v>954</v>
       </c>
       <c r="C296" t="s">
-        <v>1132</v>
+        <v>955</v>
       </c>
       <c r="D296" t="s">
-        <v>1133</v>
+        <v>956</v>
       </c>
       <c r="E296">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F296">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G296">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="297" spans="1:7">
       <c r="A297" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B297" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="C297" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="D297" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="E297">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F297">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G297">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="298" spans="1:7">
       <c r="A298" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="B298" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="C298" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="D298" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="E298">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="F298">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G298">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="B299" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="C299" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="D299" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="E299">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="F299">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G299">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="300" spans="1:7">
       <c r="A300" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="B300" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="C300" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="D300" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="E300">
-        <v>705</v>
+        <v>44</v>
       </c>
       <c r="F300">
-        <v>481</v>
+        <v>13</v>
       </c>
       <c r="G300">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="301" spans="1:7">
       <c r="A301" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="B301" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="C301" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D301" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="E301">
-        <v>592</v>
+        <v>705</v>
       </c>
       <c r="F301">
-        <v>107</v>
+        <v>481</v>
       </c>
       <c r="G301">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="302" spans="1:7">
       <c r="A302" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="B302" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="C302" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="D302" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="E302">
-        <v>500</v>
+        <v>592</v>
       </c>
       <c r="F302">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="G302">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303" spans="1:7">
       <c r="A303" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="B303" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="C303" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="D303" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="E303">
-        <v>777</v>
+        <v>500</v>
       </c>
       <c r="F303">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="G303">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="B304" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="C304" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="D304" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="E304">
-        <v>786</v>
+        <v>777</v>
       </c>
       <c r="F304">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G304">
-        <v>420</v>
+        <v>6</v>
       </c>
     </row>
     <row r="305" spans="1:7">
       <c r="A305" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="B305" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="C305" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="D305" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="E305">
-        <v>379</v>
+        <v>786</v>
       </c>
       <c r="F305">
-        <v>94</v>
+        <v>410</v>
       </c>
       <c r="G305">
-        <v>35</v>
+        <v>420</v>
       </c>
     </row>
     <row r="306" spans="1:7">
       <c r="A306" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="B306" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="C306" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="D306" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="E306">
-        <v>704</v>
+        <v>379</v>
       </c>
       <c r="F306">
-        <v>333</v>
+        <v>94</v>
       </c>
       <c r="G306">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="307" spans="1:7">
       <c r="A307" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B307" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="C307" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="D307" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="E307">
-        <v>544</v>
+        <v>704</v>
       </c>
       <c r="F307">
-        <v>409</v>
+        <v>333</v>
       </c>
       <c r="G307">
         <v>2</v>
@@ -11982,936 +12006,936 @@
     </row>
     <row r="308" spans="1:7">
       <c r="A308" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="B308" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="C308" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="D308" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="E308">
-        <v>818</v>
+        <v>544</v>
       </c>
       <c r="F308">
-        <v>1144</v>
+        <v>409</v>
       </c>
       <c r="G308">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="309" spans="1:7">
       <c r="A309" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="B309" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="C309" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="D309" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="E309">
-        <v>705</v>
+        <v>818</v>
       </c>
       <c r="F309">
-        <v>854</v>
+        <v>1144</v>
       </c>
       <c r="G309">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="310" spans="1:7">
       <c r="A310" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="B310" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="C310" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="D310" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="E310">
-        <v>458</v>
+        <v>705</v>
       </c>
       <c r="F310">
-        <v>607</v>
+        <v>854</v>
       </c>
       <c r="G310">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="311" spans="1:7">
       <c r="A311" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="B311" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="C311" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="D311" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="E311">
-        <v>690</v>
+        <v>458</v>
       </c>
       <c r="F311">
-        <v>100</v>
+        <v>607</v>
       </c>
       <c r="G311">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="312" spans="1:7">
       <c r="A312" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="B312" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="C312" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="D312" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="E312">
-        <v>100</v>
+        <v>690</v>
       </c>
       <c r="F312">
         <v>100</v>
       </c>
       <c r="G312">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313" spans="1:7">
       <c r="A313" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="B313" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="C313" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="D313" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E313">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F313">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G313">
-        <v>250</v>
+        <v>40</v>
       </c>
     </row>
     <row r="314" spans="1:7">
       <c r="A314" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="B314" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="C314" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="D314" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="E314">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F314">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G314">
-        <v>360</v>
+        <v>250</v>
       </c>
     </row>
     <row r="315" spans="1:7">
       <c r="A315" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="B315" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="C315" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="D315" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="E315">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="F315">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G315">
-        <v>1000</v>
+        <v>360</v>
       </c>
     </row>
     <row r="316" spans="1:7">
       <c r="A316" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="B316" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="C316" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="D316" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E316">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="F316">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="G316">
-        <v>10</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="317" spans="1:7">
       <c r="A317" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B317" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="C317" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="D317" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="E317">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F317">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G317">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="318" spans="1:7">
       <c r="A318" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="B318" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="C318" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="D318" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="E318">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F318">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G318">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:7">
       <c r="A319" t="s">
-        <v>1475</v>
+        <v>1214</v>
       </c>
       <c r="B319" t="s">
-        <v>1476</v>
+        <v>1215</v>
       </c>
       <c r="C319" t="s">
-        <v>1477</v>
+        <v>1216</v>
       </c>
       <c r="D319" t="s">
-        <v>1478</v>
+        <v>1217</v>
       </c>
       <c r="E319">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F319">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G319">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="320" spans="1:7">
       <c r="A320" t="s">
-        <v>1218</v>
+        <v>1475</v>
       </c>
       <c r="B320" t="s">
-        <v>502</v>
+        <v>1476</v>
       </c>
       <c r="C320" t="s">
-        <v>503</v>
+        <v>1477</v>
       </c>
       <c r="D320" t="s">
-        <v>504</v>
+        <v>1478</v>
       </c>
       <c r="E320">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="F320">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="G320">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="321" spans="1:7">
       <c r="A321" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B321" t="s">
-        <v>1220</v>
+        <v>502</v>
       </c>
       <c r="C321" t="s">
-        <v>1221</v>
+        <v>503</v>
       </c>
       <c r="D321" t="s">
-        <v>1222</v>
+        <v>504</v>
       </c>
       <c r="E321">
-        <v>151</v>
+        <v>400</v>
       </c>
       <c r="F321">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="G321">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="322" spans="1:7">
       <c r="A322" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B322" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="C322" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D322" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="E322">
-        <v>452</v>
+        <v>151</v>
       </c>
       <c r="F322">
-        <v>264</v>
+        <v>117</v>
       </c>
       <c r="G322">
-        <v>12</v>
+        <v>90</v>
       </c>
     </row>
     <row r="323" spans="1:7">
       <c r="A323" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="B323" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="C323" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="D323" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="E323">
-        <v>160</v>
+        <v>452</v>
       </c>
       <c r="F323">
-        <v>189</v>
+        <v>264</v>
       </c>
       <c r="G323">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="324" spans="1:7">
       <c r="A324" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="B324" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="C324" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="D324" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="E324">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="F324">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="G324">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325" spans="1:7">
       <c r="A325" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="B325" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="C325" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="D325" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="E325">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="F325">
-        <v>256</v>
+        <v>115</v>
       </c>
       <c r="G325">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="326" spans="1:7">
       <c r="A326" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="B326" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="C326" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="D326" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="E326">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="F326">
-        <v>59</v>
+        <v>256</v>
       </c>
       <c r="G326">
-        <v>910</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327" spans="1:7">
       <c r="A327" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="B327" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="C327" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="D327" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="E327">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="F327">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="G327">
-        <v>1</v>
+        <v>910</v>
       </c>
     </row>
     <row r="328" spans="1:7">
       <c r="A328" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="B328" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="C328" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="D328" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="E328">
-        <v>274</v>
+        <v>157</v>
       </c>
       <c r="F328">
-        <v>300</v>
+        <v>73</v>
       </c>
       <c r="G328">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329" spans="1:7">
       <c r="A329" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="B329" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="C329" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="D329" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="E329">
-        <v>225</v>
+        <v>274</v>
       </c>
       <c r="F329">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G329">
-        <v>600</v>
+        <v>4</v>
       </c>
     </row>
     <row r="330" spans="1:7">
       <c r="A330" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="B330" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="C330" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="D330" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="E330">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="F330">
-        <v>103</v>
+        <v>250</v>
       </c>
       <c r="G330">
-        <v>17</v>
+        <v>600</v>
       </c>
     </row>
     <row r="331" spans="1:7">
       <c r="A331" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="B331" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="C331" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="D331" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="E331">
-        <v>502</v>
+        <v>249</v>
       </c>
       <c r="F331">
-        <v>344</v>
+        <v>103</v>
       </c>
       <c r="G331">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="332" spans="1:7">
       <c r="A332" t="s">
-        <v>1227</v>
+        <v>1259</v>
       </c>
       <c r="B332" t="s">
-        <v>1228</v>
+        <v>1260</v>
       </c>
       <c r="C332" t="s">
-        <v>1229</v>
+        <v>1261</v>
       </c>
       <c r="D332" t="s">
-        <v>1230</v>
+        <v>1262</v>
       </c>
       <c r="E332">
-        <v>112</v>
+        <v>502</v>
       </c>
       <c r="F332">
-        <v>75</v>
+        <v>344</v>
       </c>
       <c r="G332">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="333" spans="1:7">
       <c r="A333" t="s">
-        <v>1263</v>
+        <v>1227</v>
       </c>
       <c r="B333" t="s">
-        <v>1264</v>
+        <v>1228</v>
       </c>
       <c r="C333" t="s">
-        <v>1265</v>
+        <v>1229</v>
       </c>
       <c r="D333" t="s">
-        <v>1264</v>
+        <v>1230</v>
       </c>
       <c r="E333">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F333">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G333">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334" spans="1:7">
       <c r="A334" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="B334" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="C334" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="D334" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="E334">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F334">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="G334">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335" spans="1:7">
       <c r="A335" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="B335" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="C335" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="D335" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="E335">
-        <v>1390</v>
+        <v>126</v>
       </c>
       <c r="F335">
-        <v>1280</v>
+        <v>113</v>
       </c>
       <c r="G335">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336" spans="1:7">
       <c r="A336" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="B336" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="C336" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="D336" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="E336">
-        <v>380</v>
+        <v>1390</v>
       </c>
       <c r="F336">
-        <v>350</v>
+        <v>1280</v>
       </c>
       <c r="G336">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337" spans="1:7">
       <c r="A337" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="B337" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="C337" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="D337" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="E337">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="F337">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="G337">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="338" spans="1:7">
       <c r="A338" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="B338" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="C338" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="D338" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="E338">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="F338">
-        <v>120</v>
+        <v>325</v>
       </c>
       <c r="G338">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="339" spans="1:7">
       <c r="A339" t="s">
-        <v>1459</v>
+        <v>1281</v>
       </c>
       <c r="B339" t="s">
-        <v>1460</v>
+        <v>1282</v>
       </c>
       <c r="C339" t="s">
-        <v>1461</v>
+        <v>1283</v>
       </c>
       <c r="D339" t="s">
-        <v>1462</v>
+        <v>1284</v>
       </c>
       <c r="E339">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="F339">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="G339">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="340" spans="1:7">
       <c r="A340" t="s">
-        <v>1285</v>
+        <v>1459</v>
       </c>
       <c r="B340" t="s">
-        <v>1286</v>
+        <v>1460</v>
       </c>
       <c r="C340" t="s">
-        <v>1287</v>
+        <v>1461</v>
       </c>
       <c r="D340" t="s">
-        <v>1288</v>
+        <v>1462</v>
       </c>
       <c r="E340">
-        <v>260</v>
+        <v>31</v>
       </c>
       <c r="F340">
-        <v>250</v>
+        <v>36</v>
       </c>
       <c r="G340">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341" spans="1:7">
       <c r="A341" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="B341" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="C341" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="D341" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="E341">
-        <v>355</v>
+        <v>260</v>
       </c>
       <c r="F341">
-        <v>342</v>
+        <v>250</v>
       </c>
       <c r="G341">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="342" spans="1:7">
       <c r="A342" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="B342" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="C342" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="D342" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="E342">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="F342">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="G342">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="343" spans="1:7">
       <c r="A343" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="B343" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="C343" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D343" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="E343">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="F343">
-        <v>98</v>
+        <v>391</v>
       </c>
       <c r="G343">
-        <v>390</v>
+        <v>5</v>
       </c>
     </row>
     <row r="344" spans="1:7">
       <c r="A344" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="B344" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="C344" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="D344" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="E344">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="F344">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="G344">
-        <v>564</v>
+        <v>390</v>
       </c>
     </row>
     <row r="345" spans="1:7">
       <c r="A345" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="B345" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="C345" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="D345" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="E345">
-        <v>219</v>
+        <v>348</v>
       </c>
       <c r="F345">
-        <v>140</v>
+        <v>298</v>
       </c>
       <c r="G345">
-        <v>281</v>
+        <v>564</v>
       </c>
     </row>
     <row r="346" spans="1:7">
       <c r="A346" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="B346" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="C346" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="D346" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="E346">
-        <v>32</v>
+        <v>219</v>
       </c>
       <c r="F346">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="G346">
-        <v>400</v>
+        <v>281</v>
       </c>
     </row>
     <row r="347" spans="1:7">
       <c r="A347" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B347" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C347" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="D347" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="E347">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F347">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="G347">
-        <v>1</v>
+        <v>400</v>
       </c>
     </row>
     <row r="348" spans="1:7">
       <c r="A348" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="B348" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="C348" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="D348" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="E348">
         <v>70</v>
@@ -12925,183 +12949,183 @@
     </row>
     <row r="349" spans="1:7">
       <c r="A349" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="B349" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="C349" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D349" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="E349">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="F349">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="G349">
-        <v>400</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350" spans="1:7">
       <c r="A350" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="B350" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="C350" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="D350" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="E350">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="F350">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G350">
-        <v>150</v>
+        <v>400</v>
       </c>
     </row>
     <row r="351" spans="1:7">
       <c r="A351" t="s">
-        <v>1489</v>
+        <v>1322</v>
       </c>
       <c r="B351" t="s">
-        <v>1492</v>
+        <v>1323</v>
       </c>
       <c r="C351" t="s">
-        <v>1491</v>
+        <v>1324</v>
       </c>
       <c r="D351" t="s">
-        <v>1490</v>
+        <v>1325</v>
       </c>
       <c r="E351">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F351">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="G351">
-        <v>180</v>
+        <v>150</v>
       </c>
     </row>
     <row r="352" spans="1:7">
       <c r="A352" t="s">
-        <v>1326</v>
+        <v>1489</v>
       </c>
       <c r="B352" t="s">
-        <v>1327</v>
+        <v>1492</v>
       </c>
       <c r="C352" t="s">
-        <v>1328</v>
+        <v>1491</v>
       </c>
       <c r="D352" t="s">
-        <v>1329</v>
+        <v>1490</v>
       </c>
       <c r="E352">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="F352">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="G352">
-        <v>450</v>
+        <v>180</v>
       </c>
     </row>
     <row r="353" spans="1:7">
       <c r="A353" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="B353" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="C353" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="D353" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="E353">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="F353">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="G353">
-        <v>100</v>
+        <v>450</v>
       </c>
     </row>
     <row r="354" spans="1:7">
       <c r="A354" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="B354" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="C354" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="D354" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="E354">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F354">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="G354">
-        <v>350</v>
+        <v>100</v>
       </c>
     </row>
     <row r="355" spans="1:7">
       <c r="A355" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="B355" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="C355" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="D355" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="E355">
+        <v>200</v>
+      </c>
+      <c r="F355">
         <v>150</v>
       </c>
-      <c r="F355">
-        <v>110</v>
-      </c>
       <c r="G355">
-        <v>500</v>
+        <v>350</v>
       </c>
     </row>
     <row r="356" spans="1:7">
       <c r="A356" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="B356" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="C356" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="D356" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="E356">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F356">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="G356">
         <v>500</v>
@@ -13109,16 +13133,16 @@
     </row>
     <row r="357" spans="1:7">
       <c r="A357" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="B357" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="C357" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="D357" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="E357">
         <v>100</v>
@@ -13132,22 +13156,22 @@
     </row>
     <row r="358" spans="1:7">
       <c r="A358" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="B358" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="C358" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="D358" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="E358">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="F358">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="G358">
         <v>500</v>
@@ -13155,45 +13179,45 @@
     </row>
     <row r="359" spans="1:7">
       <c r="A359" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="B359" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="C359" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="D359" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="E359">
-        <v>338</v>
+        <v>145</v>
       </c>
       <c r="F359">
-        <v>347</v>
+        <v>135</v>
       </c>
       <c r="G359">
-        <v>370</v>
+        <v>500</v>
       </c>
     </row>
     <row r="360" spans="1:7">
       <c r="A360" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="B360" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="C360" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="D360" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="E360">
-        <v>209</v>
+        <v>338</v>
       </c>
       <c r="F360">
-        <v>244</v>
+        <v>347</v>
       </c>
       <c r="G360">
         <v>370</v>
@@ -13201,691 +13225,737 @@
     </row>
     <row r="361" spans="1:7">
       <c r="A361" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B361" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C361" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D361" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E361">
+        <v>209</v>
+      </c>
+      <c r="F361">
+        <v>244</v>
+      </c>
+      <c r="G361">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7">
+      <c r="A362" t="s">
         <v>1362</v>
       </c>
-      <c r="B361" t="s">
+      <c r="B362" t="s">
         <v>1363</v>
       </c>
-      <c r="C361" t="s">
+      <c r="C362" t="s">
         <v>1364</v>
       </c>
-      <c r="D361" t="s">
+      <c r="D362" t="s">
         <v>1365</v>
       </c>
-      <c r="E361">
+      <c r="E362">
         <v>131</v>
       </c>
-      <c r="F361">
+      <c r="F362">
         <v>120</v>
       </c>
-      <c r="G361">
+      <c r="G362">
         <v>635</v>
       </c>
     </row>
-    <row r="362" spans="1:7" s="2" customFormat="1" ht="17.850000000000001" customHeight="1">
-      <c r="A362" s="2" t="s">
+    <row r="363" spans="1:7" s="2" customFormat="1" ht="17.850000000000001" customHeight="1">
+      <c r="A363" s="2" t="s">
         <v>1497</v>
       </c>
-      <c r="B362" s="2" t="s">
+      <c r="B363" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C363" s="2" t="s">
         <v>1500</v>
       </c>
-      <c r="C362" s="2" t="s">
+      <c r="D363" s="3" t="s">
         <v>1501</v>
       </c>
-      <c r="D362" s="3" t="s">
+      <c r="E363" s="2">
+        <v>42</v>
+      </c>
+      <c r="F363" s="2">
+        <v>14</v>
+      </c>
+      <c r="G363" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" s="2" customFormat="1" ht="16.7" customHeight="1">
+      <c r="A364" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B364" s="3" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D364" s="2" t="s">
         <v>1502</v>
       </c>
-      <c r="E362" s="2">
-        <v>42</v>
-      </c>
-      <c r="F362" s="2">
-        <v>14</v>
-      </c>
-      <c r="G362" s="2">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="363" spans="1:7" s="2" customFormat="1" ht="16.7" customHeight="1">
-      <c r="A363" s="2" t="s">
+      <c r="E364" s="2">
+        <v>53</v>
+      </c>
+      <c r="F364" s="2">
+        <v>9</v>
+      </c>
+      <c r="G364" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" s="2" customFormat="1" ht="15.55" customHeight="1">
+      <c r="A365" s="2" t="s">
         <v>1498</v>
       </c>
-      <c r="B363" s="3" t="s">
+      <c r="B365" s="2" t="s">
         <v>1505</v>
       </c>
-      <c r="C363" s="2" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D363" s="2" t="s">
-        <v>1503</v>
-      </c>
-      <c r="E363" s="2">
-        <v>53</v>
-      </c>
-      <c r="F363" s="2">
-        <v>9</v>
-      </c>
-      <c r="G363" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="364" spans="1:7" s="2" customFormat="1" ht="19.05" customHeight="1">
-      <c r="A364" s="2" t="s">
-        <v>1499</v>
-      </c>
-      <c r="B364" s="2" t="s">
+      <c r="C365" s="3" t="s">
         <v>1506</v>
       </c>
-      <c r="C364" s="3" t="s">
+      <c r="D365" s="4" t="s">
         <v>1507</v>
       </c>
-      <c r="D364" s="4" t="s">
-        <v>1508</v>
-      </c>
-      <c r="E364" s="2">
+      <c r="E365" s="2">
         <v>77</v>
       </c>
-      <c r="F364" s="2">
+      <c r="F365" s="2">
         <v>47</v>
       </c>
-      <c r="G364" s="2">
+      <c r="G365" s="2">
         <v>223</v>
-      </c>
-    </row>
-    <row r="365" spans="1:7">
-      <c r="A365" t="s">
-        <v>1366</v>
-      </c>
-      <c r="B365" t="s">
-        <v>1367</v>
-      </c>
-      <c r="C365" t="s">
-        <v>1368</v>
-      </c>
-      <c r="D365" t="s">
-        <v>1369</v>
-      </c>
-      <c r="E365">
-        <v>1</v>
-      </c>
-      <c r="F365">
-        <v>1</v>
-      </c>
-      <c r="G365">
-        <v>10</v>
       </c>
     </row>
     <row r="366" spans="1:7">
       <c r="A366" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B366" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C366" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D366" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E366">
+        <v>1</v>
+      </c>
+      <c r="F366">
+        <v>1</v>
+      </c>
+      <c r="G366">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7">
+      <c r="A367" t="s">
         <v>1370</v>
       </c>
-      <c r="B366" t="s">
+      <c r="B367" t="s">
         <v>1371</v>
       </c>
-      <c r="C366" t="s">
+      <c r="C367" t="s">
         <v>1372</v>
       </c>
-      <c r="D366" t="s">
+      <c r="D367" t="s">
         <v>1373</v>
       </c>
-      <c r="E366">
+      <c r="E367">
         <v>0</v>
-      </c>
-      <c r="F366">
-        <v>0</v>
-      </c>
-      <c r="G366">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="367" spans="1:7" ht="15">
-      <c r="A367" t="s">
-        <v>1493</v>
-      </c>
-      <c r="B367" s="1" t="s">
-        <v>1494</v>
-      </c>
-      <c r="C367" s="1" t="s">
-        <v>1495</v>
-      </c>
-      <c r="D367" s="1" t="s">
-        <v>1496</v>
-      </c>
-      <c r="E367">
-        <v>1</v>
       </c>
       <c r="F367">
         <v>0</v>
       </c>
       <c r="G367">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="368" spans="1:7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" ht="15">
       <c r="A368" t="s">
-        <v>1374</v>
-      </c>
-      <c r="B368" t="s">
-        <v>1375</v>
-      </c>
-      <c r="C368" t="s">
-        <v>1376</v>
-      </c>
-      <c r="D368" t="s">
-        <v>1377</v>
+        <v>1493</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>1496</v>
       </c>
       <c r="E368">
         <v>1</v>
       </c>
       <c r="F368">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G368">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="369" spans="1:7">
       <c r="A369" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="B369" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="C369" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="D369" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="E369">
-        <v>10.8</v>
+        <v>1</v>
       </c>
       <c r="F369">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G369">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="370" spans="1:7">
       <c r="A370" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="B370" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="C370" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="D370" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="E370">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="F370">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G370">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="371" spans="1:7">
       <c r="A371" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="B371" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="C371" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="D371" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
       <c r="E371">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F371">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G371">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="372" spans="1:7">
       <c r="A372" t="s">
-        <v>1482</v>
+        <v>1386</v>
       </c>
       <c r="B372" t="s">
-        <v>1483</v>
+        <v>1387</v>
       </c>
       <c r="C372" t="s">
-        <v>1484</v>
+        <v>1388</v>
       </c>
       <c r="D372" t="s">
-        <v>1485</v>
+        <v>1389</v>
       </c>
       <c r="E372">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F372">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="G372">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373" spans="1:7">
       <c r="A373" t="s">
-        <v>1390</v>
+        <v>1482</v>
       </c>
       <c r="B373" t="s">
-        <v>1391</v>
+        <v>1483</v>
       </c>
       <c r="C373" t="s">
-        <v>1392</v>
+        <v>1484</v>
       </c>
       <c r="D373" t="s">
-        <v>1393</v>
+        <v>1485</v>
       </c>
       <c r="E373">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F373">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G373">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="374" spans="1:7">
       <c r="A374" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
       <c r="B374" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="C374" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="D374" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="E374">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F374">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G374">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="375" spans="1:7">
       <c r="A375" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B375" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="C375" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="D375" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="E375">
-        <v>400</v>
+        <v>37</v>
       </c>
       <c r="F375">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G375">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B376" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="C376" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="D376" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E376">
-        <v>549</v>
+        <v>400</v>
       </c>
       <c r="F376">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c r="G376">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="377" spans="1:7">
       <c r="A377" t="s">
-        <v>1479</v>
+        <v>1402</v>
       </c>
       <c r="B377" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="C377" t="s">
-        <v>1481</v>
+        <v>1404</v>
       </c>
       <c r="D377" t="s">
-        <v>1480</v>
+        <v>1405</v>
       </c>
       <c r="E377">
-        <v>15</v>
+        <v>549</v>
       </c>
       <c r="F377">
-        <v>9</v>
+        <v>152</v>
       </c>
       <c r="G377">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="378" spans="1:7">
       <c r="A378" t="s">
-        <v>1407</v>
+        <v>1479</v>
       </c>
       <c r="B378" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="C378" t="s">
-        <v>1409</v>
+        <v>1481</v>
       </c>
       <c r="D378" t="s">
-        <v>1410</v>
+        <v>1480</v>
       </c>
       <c r="E378">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="F378">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="G378">
-        <v>150</v>
+        <v>15</v>
       </c>
     </row>
     <row r="379" spans="1:7">
       <c r="A379" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B379" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="C379" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="D379" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="E379">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="F379">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="G379">
-        <v>2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="380" spans="1:7">
       <c r="A380" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="B380" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="C380" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="D380" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="E380">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="F380">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G380">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="381" spans="1:7">
       <c r="A381" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="B381" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="C381" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="D381" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
       <c r="E381">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F381">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="G381">
-        <v>39</v>
+        <v>4</v>
       </c>
     </row>
     <row r="382" spans="1:7">
       <c r="A382" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
       <c r="B382" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
       <c r="C382" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="D382" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="E382">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="F382">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G382">
-        <v>91</v>
+        <v>39</v>
       </c>
     </row>
     <row r="383" spans="1:7">
       <c r="A383" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="B383" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="C383" t="s">
-        <v>1429</v>
+        <v>1425</v>
       </c>
       <c r="D383" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
       <c r="E383">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="F383">
         <v>0</v>
       </c>
       <c r="G383">
-        <v>219</v>
+        <v>91</v>
       </c>
     </row>
     <row r="384" spans="1:7">
       <c r="A384" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
       <c r="B384" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="C384" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="D384" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="E384">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="F384">
         <v>0</v>
       </c>
       <c r="G384">
-        <v>119</v>
+        <v>219</v>
       </c>
     </row>
     <row r="385" spans="1:7">
       <c r="A385" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
       <c r="B385" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="C385" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="D385" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="E385">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F385">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G385">
-        <v>14</v>
+        <v>119</v>
       </c>
     </row>
     <row r="386" spans="1:7">
       <c r="A386" t="s">
-        <v>1439</v>
+        <v>1516</v>
       </c>
       <c r="B386" t="s">
-        <v>1440</v>
+        <v>1519</v>
       </c>
       <c r="C386" t="s">
-        <v>1441</v>
+        <v>1518</v>
       </c>
       <c r="D386" t="s">
-        <v>1442</v>
+        <v>1517</v>
       </c>
       <c r="E386">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F386">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G386">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="387" spans="1:7">
       <c r="A387" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B387" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="C387" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="D387" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="E387">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F387">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G387">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="388" spans="1:7">
       <c r="A388" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B388" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="C388" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="D388" t="s">
-        <v>1450</v>
+        <v>1442</v>
       </c>
       <c r="E388">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="F388">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G388">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="389" spans="1:7">
       <c r="A389" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
       <c r="B389" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="C389" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="D389" t="s">
-        <v>1454</v>
+        <v>1446</v>
       </c>
       <c r="E389">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="F389">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G389">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="390" spans="1:7">
       <c r="A390" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B390" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C390" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D390" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E390">
+        <v>82</v>
+      </c>
+      <c r="F390">
+        <v>15</v>
+      </c>
+      <c r="G390">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7">
+      <c r="A391" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B391" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C391" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D391" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E391">
+        <v>102</v>
+      </c>
+      <c r="F391">
+        <v>10</v>
+      </c>
+      <c r="G391">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7">
+      <c r="A392" t="s">
         <v>1455</v>
       </c>
-      <c r="B390" t="s">
+      <c r="B392" t="s">
         <v>1456</v>
       </c>
-      <c r="C390" t="s">
+      <c r="C392" t="s">
         <v>1457</v>
       </c>
-      <c r="D390" t="s">
+      <c r="D392" t="s">
         <v>1458</v>
       </c>
-      <c r="E390">
+      <c r="E392">
         <v>0</v>
       </c>
-      <c r="F390">
+      <c r="F392">
         <v>0</v>
       </c>
-      <c r="G390">
+      <c r="G392">
         <v>0</v>
       </c>
     </row>

--- a/KPH-AI-GLOBAL.xlsx
+++ b/KPH-AI-GLOBAL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="196" yWindow="518" windowWidth="18904" windowHeight="8087"/>
+    <workbookView xWindow="196" yWindow="518" windowWidth="18904" windowHeight="8087" tabRatio="169"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="1521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="1518">
   <si>
     <t>Namirnica</t>
   </si>
@@ -1579,18 +1579,6 @@
     <t>Sauerrahm 30 % Fett</t>
   </si>
   <si>
-    <t>Palacinke kom. Cca 60g (prazna + fil)</t>
-  </si>
-  <si>
-    <t>Pancakes pc. approx. 60g (empty + filling)</t>
-  </si>
-  <si>
-    <t>Panqueques ud. aprox. 60g (vacío + relleno)</t>
-  </si>
-  <si>
-    <t>Pfannkuchen Stk. ca. 60g (leer + Füllung)</t>
-  </si>
-  <si>
     <t>Bel-paese</t>
   </si>
   <si>
@@ -2356,30 +2344,6 @@
     <t>Bob Young hat gekocht</t>
   </si>
   <si>
-    <t>Supa koksija - porcija tanjir 250ml</t>
-  </si>
-  <si>
-    <t>Coke soup - serving plate 250ml</t>
-  </si>
-  <si>
-    <t>Sopa de coca cola - plato para servir 250ml</t>
-  </si>
-  <si>
-    <t>Cola-Suppe – Servierteller 250 ml</t>
-  </si>
-  <si>
-    <t>Supa govedja - porcija tanjir 250ml</t>
-  </si>
-  <si>
-    <t>Beef soup - plate portion 250ml</t>
-  </si>
-  <si>
-    <t>Sopa de ternera - ración de plato 250ml</t>
-  </si>
-  <si>
-    <t>Rindersuppe - Tellerportion 250 ml</t>
-  </si>
-  <si>
     <t>Pasulj kuvani</t>
   </si>
   <si>
@@ -4150,30 +4114,6 @@
     <t>Coca Cola +e338!</t>
   </si>
   <si>
-    <t>Red Bull 0.25 zeroo</t>
-  </si>
-  <si>
-    <t>Red bull 0.25 zeroo</t>
-  </si>
-  <si>
-    <t>Toro rojo 0,25 cero</t>
-  </si>
-  <si>
-    <t>Red Bull 0,25 Nullo</t>
-  </si>
-  <si>
-    <t>Red Bull 0.25 clasic</t>
-  </si>
-  <si>
-    <t>Red bull 0.25 classic</t>
-  </si>
-  <si>
-    <t>Red bull 0.25 clásico</t>
-  </si>
-  <si>
-    <t>Red Bull 0,25 Klassiker</t>
-  </si>
-  <si>
     <t>Caj biljni + secer</t>
   </si>
   <si>
@@ -4234,21 +4174,6 @@
     <t>Kakao mit Milch</t>
   </si>
   <si>
-    <t>Milk for coffee portion 5ml</t>
-  </si>
-  <si>
-    <t>Mleko za kafu 100ml</t>
-  </si>
-  <si>
-    <t>Milk for coffee 100ml</t>
-  </si>
-  <si>
-    <t>Leche para café 100ml</t>
-  </si>
-  <si>
-    <t>Milch für Kaffee 100 ml</t>
-  </si>
-  <si>
     <t>Kafa espresso</t>
   </si>
   <si>
@@ -4451,15 +4376,6 @@
   </si>
   <si>
     <t>Gummibonbons Haribo</t>
-  </si>
-  <si>
-    <t>Mleko za kafu porcija 10ml</t>
-  </si>
-  <si>
-    <t>Milch für Kaffee, Portion 10 ml</t>
-  </si>
-  <si>
-    <t>Leche para porción de café 10ml</t>
   </si>
   <si>
     <t xml:space="preserve">Boza belo kukuruzno brasno </t>
@@ -4523,16 +4439,6 @@
 </t>
   </si>
   <si>
-    <t>Brot mit Honigaufstrich, in Scheiben geschnitten</t>
-  </si>
-  <si>
-    <t>Pan untado con miel, en rebanadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bread with honey spread, sliced
-</t>
-  </si>
-  <si>
     <t>Rolls with jam</t>
   </si>
   <si>
@@ -4555,18 +4461,9 @@
     <t>Trapist-Käse</t>
   </si>
   <si>
-    <t>Supa kocka porcija tanjir 250ml</t>
-  </si>
-  <si>
     <t>Soup cube plate portion 250ml</t>
   </si>
   <si>
-    <t>cubo de sopa ración de plato 250ml</t>
-  </si>
-  <si>
-    <t>Suppenwürfel Tellerportion 250 ml</t>
-  </si>
-  <si>
     <t>Sok Limunada 6%</t>
   </si>
   <si>
@@ -4579,7 +4476,101 @@
     <t>Lemonade 6%</t>
   </si>
   <si>
-    <t>Hleb sa medom namaz 1 snita</t>
+    <t>Supa koksija</t>
+  </si>
+  <si>
+    <t>Coke soup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sopa de coca cola </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cola-Suppe </t>
+  </si>
+  <si>
+    <t>Supa govedja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beef soup </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sopa de ternera </t>
+  </si>
+  <si>
+    <t>Rindersuppe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppenwürfel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">cubo de sopa </t>
+  </si>
+  <si>
+    <t>Supa kocka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palacinke </t>
+  </si>
+  <si>
+    <t>Pancakes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panqueques </t>
+  </si>
+  <si>
+    <t>Pfannkuchen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hleb sa medom namaz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bread with honey spread, 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pan untado con miel, </t>
+  </si>
+  <si>
+    <t>Brot mit Honigaufstrich, in Scheiben</t>
+  </si>
+  <si>
+    <t>Bel-paese sir</t>
+  </si>
+  <si>
+    <t>Red Bull  zeroo</t>
+  </si>
+  <si>
+    <t>Red Bull  clasic</t>
+  </si>
+  <si>
+    <t>Red bull  zeroo</t>
+  </si>
+  <si>
+    <t>Red bull  classic</t>
+  </si>
+  <si>
+    <t>Toro rojo  cero</t>
+  </si>
+  <si>
+    <t>Red bull  clásico</t>
+  </si>
+  <si>
+    <t>Red Bull Nullo</t>
+  </si>
+  <si>
+    <t>Red Bull  Klassiker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mleko za kafu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milk for coffee </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leche para café </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milch für Kaffee </t>
   </si>
 </sst>
 </file>
@@ -4937,13 +4928,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G392"/>
+  <dimension ref="A1:G391"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.796875" customWidth="1"/>
-    <col min="3" max="3" width="57.09765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="57.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.19921875" customWidth="1"/>
+    <col min="2" max="2" width="34.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5983,16 +5974,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>1466</v>
+        <v>1441</v>
       </c>
       <c r="B46" t="s">
-        <v>1467</v>
+        <v>1442</v>
       </c>
       <c r="C46" t="s">
-        <v>1468</v>
+        <v>1443</v>
       </c>
       <c r="D46" t="s">
-        <v>1469</v>
+        <v>1444</v>
       </c>
       <c r="E46">
         <v>173</v>
@@ -6098,16 +6089,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>1463</v>
+        <v>1438</v>
       </c>
       <c r="B51" t="s">
-        <v>1464</v>
+        <v>1439</v>
       </c>
       <c r="C51" t="s">
-        <v>1465</v>
+        <v>1440</v>
       </c>
       <c r="D51" t="s">
-        <v>1464</v>
+        <v>1439</v>
       </c>
       <c r="E51">
         <v>230</v>
@@ -7156,7 +7147,7 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>1470</v>
+        <v>1445</v>
       </c>
       <c r="B97" t="s">
         <v>374</v>
@@ -7570,7 +7561,7 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>1471</v>
+        <v>1446</v>
       </c>
       <c r="B115" t="s">
         <v>442</v>
@@ -8030,39 +8021,39 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>521</v>
+        <v>1497</v>
       </c>
       <c r="B135" t="s">
-        <v>522</v>
+        <v>1498</v>
       </c>
       <c r="C135" t="s">
-        <v>523</v>
+        <v>1499</v>
       </c>
       <c r="D135" t="s">
-        <v>524</v>
+        <v>1500</v>
       </c>
       <c r="E135">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="F135">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="G135">
-        <v>100</v>
+        <v>166</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>525</v>
+        <v>1505</v>
       </c>
       <c r="B136" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C136" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="D136" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E136">
         <v>156</v>
@@ -8076,16 +8067,16 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B137" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C137" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="D137" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="E137">
         <v>132</v>
@@ -8099,16 +8090,16 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B138" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C138" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D138" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="E138">
         <v>120</v>
@@ -8122,16 +8113,16 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B139" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C139" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="D139" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="E139">
         <v>102</v>
@@ -8145,16 +8136,16 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B140" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C140" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="D140" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E140">
         <v>95</v>
@@ -8168,16 +8159,16 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="B141" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C141" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D141" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="E141">
         <v>87</v>
@@ -8191,16 +8182,16 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B142" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C142" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="D142" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E142">
         <v>107</v>
@@ -8214,16 +8205,16 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B143" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C143" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="D143" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="E143">
         <v>62</v>
@@ -8237,16 +8228,16 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>1508</v>
+        <v>1477</v>
       </c>
       <c r="B144" t="s">
-        <v>1509</v>
+        <v>1478</v>
       </c>
       <c r="C144" t="s">
-        <v>1510</v>
+        <v>1479</v>
       </c>
       <c r="D144" t="s">
-        <v>1511</v>
+        <v>1480</v>
       </c>
       <c r="E144">
         <v>130</v>
@@ -8260,16 +8251,16 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B145" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C145" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="D145" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E145">
         <v>76</v>
@@ -8283,16 +8274,16 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B146" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C146" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="D146" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E146">
         <v>123</v>
@@ -8306,16 +8297,16 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B147" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C147" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D147" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E147">
         <v>81</v>
@@ -8329,16 +8320,16 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B148" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C148" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="D148" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="E148">
         <v>128</v>
@@ -8352,16 +8343,16 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B149" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C149" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="D149" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="E149">
         <v>38</v>
@@ -8375,16 +8366,16 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B150" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C150" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D150" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="E150">
         <v>55</v>
@@ -8398,16 +8389,16 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B151" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C151" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="D151" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="E151">
         <v>95</v>
@@ -8421,16 +8412,16 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B152" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C152" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="D152" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="E152">
         <v>190</v>
@@ -8444,16 +8435,16 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B153" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C153" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="D153" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="E153">
         <v>190</v>
@@ -8467,16 +8458,16 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B154" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C154" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D154" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E154">
         <v>149</v>
@@ -8490,16 +8481,16 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B155" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C155" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="D155" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="E155">
         <v>147</v>
@@ -8513,16 +8504,16 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B156" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C156" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="D156" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E156">
         <v>130</v>
@@ -8536,16 +8527,16 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B157" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C157" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="D157" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="E157">
         <v>210</v>
@@ -8559,16 +8550,16 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B158" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C158" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="D158" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="E158">
         <v>233</v>
@@ -8582,16 +8573,16 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B159" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C159" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="D159" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="E159">
         <v>132</v>
@@ -8605,16 +8596,16 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B160" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C160" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D160" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="E160">
         <v>142</v>
@@ -8628,16 +8619,16 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B161" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C161" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="D161" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="E161">
         <v>42</v>
@@ -8651,16 +8642,16 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B162" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C162" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="D162" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="E162">
         <v>30</v>
@@ -8674,16 +8665,16 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B163" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C163" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="D163" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E163">
         <v>26</v>
@@ -8697,16 +8688,16 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B164" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C164" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="D164" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -8720,16 +8711,16 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B165" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C165" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="D165" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -8743,16 +8734,16 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B166" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C166" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="D166" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -8766,16 +8757,16 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B167" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C167" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="D167" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="E167">
         <v>130</v>
@@ -8789,16 +8780,16 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B168" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C168" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="D168" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="E168">
         <v>570</v>
@@ -8812,16 +8803,16 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B169" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C169" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D169" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="E169">
         <v>310</v>
@@ -8835,16 +8826,16 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B170" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C170" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="D170" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="E170">
         <v>455</v>
@@ -8858,16 +8849,16 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B171" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C171" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="D171" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="E171">
         <v>350</v>
@@ -8881,16 +8872,16 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B172" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C172" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D172" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="E172">
         <v>500</v>
@@ -8904,16 +8895,16 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B173" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C173" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="D173" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="E173">
         <v>460</v>
@@ -8927,16 +8918,16 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B174" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C174" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="D174" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="E174">
         <v>1275</v>
@@ -8950,16 +8941,16 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B175" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="C175" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="D175" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="E175">
         <v>376</v>
@@ -8973,16 +8964,16 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B176" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C176" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D176" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="E176">
         <v>328</v>
@@ -8996,16 +8987,16 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B177" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C177" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="D177" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="E177">
         <v>340</v>
@@ -9019,16 +9010,16 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B178" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C178" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="D178" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="E178">
         <v>550</v>
@@ -9042,16 +9033,16 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B179" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C179" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="D179" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="E179">
         <v>490</v>
@@ -9065,16 +9056,16 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B180" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C180" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="D180" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="E180">
         <v>464</v>
@@ -9088,16 +9079,16 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="B181" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="C181" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="D181" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="E181">
         <v>227</v>
@@ -9111,16 +9102,16 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B182" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="C182" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="D182" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="E182">
         <v>266</v>
@@ -9134,16 +9125,16 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B183" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="C183" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="D183" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="E183">
         <v>288</v>
@@ -9157,16 +9148,16 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B184" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="C184" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="D184" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="E184">
         <v>300</v>
@@ -9180,16 +9171,16 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B185" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C185" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D185" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="E185">
         <v>399</v>
@@ -9203,16 +9194,16 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B186" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C186" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="D186" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="E186">
         <v>1000</v>
@@ -9226,16 +9217,16 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B187" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="C187" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="D187" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="E187">
         <v>270</v>
@@ -9249,16 +9240,16 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B188" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="C188" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="D188" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="E188">
         <v>322</v>
@@ -9272,16 +9263,16 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B189" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="C189" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="D189" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E189">
         <v>346</v>
@@ -9295,16 +9286,16 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B190" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="C190" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D190" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="E190">
         <v>360</v>
@@ -9318,16 +9309,16 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B191" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="C191" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="D191" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E191">
         <v>215</v>
@@ -9341,16 +9332,16 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B192" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C192" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="D192" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="E192">
         <v>633</v>
@@ -9364,16 +9355,16 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B193" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="C193" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="D193" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="E193">
         <v>291</v>
@@ -9387,16 +9378,16 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="B194" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="C194" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="D194" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="E194">
         <v>325</v>
@@ -9410,16 +9401,16 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B195" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C195" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="D195" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="E195">
         <v>265</v>
@@ -9433,16 +9424,16 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B196" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="C196" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="D196" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="E196">
         <v>554</v>
@@ -9456,16 +9447,16 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B197" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="C197" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="D197" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="E197">
         <v>380</v>
@@ -9479,16 +9470,16 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="B198" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="C198" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="D198" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="E198">
         <v>315</v>
@@ -9502,16 +9493,16 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="B199" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C199" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="D199" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="E199">
         <v>400</v>
@@ -9525,16 +9516,16 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="B200" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="C200" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="D200" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="E200">
         <v>240</v>
@@ -9548,16 +9539,16 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B201" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C201" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D201" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="E201">
         <v>255</v>
@@ -9571,16 +9562,16 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B202" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="C202" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="D202" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="E202">
         <v>230</v>
@@ -9594,85 +9585,85 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>780</v>
+        <v>1486</v>
       </c>
       <c r="B203" t="s">
-        <v>781</v>
+        <v>1487</v>
       </c>
       <c r="C203" t="s">
-        <v>782</v>
+        <v>1488</v>
       </c>
       <c r="D203" t="s">
-        <v>783</v>
+        <v>1489</v>
       </c>
       <c r="E203">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="F203">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G203">
-        <v>350</v>
+        <v>140</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>784</v>
+        <v>1490</v>
       </c>
       <c r="B204" t="s">
-        <v>785</v>
+        <v>1491</v>
       </c>
       <c r="C204" t="s">
-        <v>786</v>
+        <v>1492</v>
       </c>
       <c r="D204" t="s">
-        <v>787</v>
+        <v>1493</v>
       </c>
       <c r="E204">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="F204">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G204">
-        <v>327</v>
+        <v>131</v>
       </c>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>1512</v>
+        <v>1496</v>
       </c>
       <c r="B205" t="s">
-        <v>1513</v>
+        <v>1481</v>
       </c>
       <c r="C205" t="s">
-        <v>1514</v>
+        <v>1495</v>
       </c>
       <c r="D205" t="s">
-        <v>1515</v>
+        <v>1494</v>
       </c>
       <c r="E205">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F205">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G205">
-        <v>450</v>
+        <v>180</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="B206" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="C206" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="D206" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="E206">
         <v>400</v>
@@ -9686,16 +9677,16 @@
     </row>
     <row r="207" spans="1:7">
       <c r="A207" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="B207" t="s">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="C207" t="s">
-        <v>794</v>
+        <v>782</v>
       </c>
       <c r="D207" t="s">
-        <v>795</v>
+        <v>783</v>
       </c>
       <c r="E207">
         <v>550</v>
@@ -9709,16 +9700,16 @@
     </row>
     <row r="208" spans="1:7">
       <c r="A208" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="B208" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="C208" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="D208" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="E208">
         <v>340</v>
@@ -9732,16 +9723,16 @@
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="B209" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="C209" t="s">
-        <v>802</v>
+        <v>790</v>
       </c>
       <c r="D209" t="s">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="E209">
         <v>250</v>
@@ -9755,16 +9746,16 @@
     </row>
     <row r="210" spans="1:7">
       <c r="A210" t="s">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="B210" t="s">
-        <v>805</v>
+        <v>793</v>
       </c>
       <c r="C210" t="s">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="D210" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
       <c r="E210">
         <v>248</v>
@@ -9778,16 +9769,16 @@
     </row>
     <row r="211" spans="1:7">
       <c r="A211" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="B211" t="s">
-        <v>809</v>
+        <v>797</v>
       </c>
       <c r="C211" t="s">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="D211" t="s">
-        <v>811</v>
+        <v>799</v>
       </c>
       <c r="E211">
         <v>550</v>
@@ -9801,16 +9792,16 @@
     </row>
     <row r="212" spans="1:7">
       <c r="A212" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="B212" t="s">
-        <v>813</v>
+        <v>801</v>
       </c>
       <c r="C212" t="s">
-        <v>814</v>
+        <v>802</v>
       </c>
       <c r="D212" t="s">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="E212">
         <v>1680</v>
@@ -9824,16 +9815,16 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213" t="s">
-        <v>816</v>
+        <v>804</v>
       </c>
       <c r="B213" t="s">
-        <v>817</v>
+        <v>805</v>
       </c>
       <c r="C213" t="s">
-        <v>818</v>
+        <v>806</v>
       </c>
       <c r="D213" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
       <c r="E213">
         <v>121</v>
@@ -9847,16 +9838,16 @@
     </row>
     <row r="214" spans="1:7">
       <c r="A214" t="s">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="B214" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
       <c r="C214" t="s">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="D214" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="E214">
         <v>1660</v>
@@ -9870,16 +9861,16 @@
     </row>
     <row r="215" spans="1:7">
       <c r="A215" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="B215" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="C215" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="D215" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="E215">
         <v>137</v>
@@ -9893,16 +9884,16 @@
     </row>
     <row r="216" spans="1:7">
       <c r="A216" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="B216" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="C216" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="D216" t="s">
-        <v>831</v>
+        <v>819</v>
       </c>
       <c r="E216">
         <v>140</v>
@@ -9916,16 +9907,16 @@
     </row>
     <row r="217" spans="1:7">
       <c r="A217" t="s">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="B217" t="s">
-        <v>833</v>
+        <v>821</v>
       </c>
       <c r="C217" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="D217" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="E217">
         <v>300</v>
@@ -9939,16 +9930,16 @@
     </row>
     <row r="218" spans="1:7">
       <c r="A218" t="s">
-        <v>1486</v>
+        <v>1458</v>
       </c>
       <c r="B218" t="s">
-        <v>1487</v>
+        <v>1459</v>
       </c>
       <c r="C218" t="s">
-        <v>1487</v>
+        <v>1459</v>
       </c>
       <c r="D218" t="s">
-        <v>1488</v>
+        <v>1460</v>
       </c>
       <c r="E218">
         <v>320</v>
@@ -9962,16 +9953,16 @@
     </row>
     <row r="219" spans="1:7">
       <c r="A219" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="B219" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
       <c r="C219" t="s">
-        <v>838</v>
+        <v>826</v>
       </c>
       <c r="D219" t="s">
-        <v>839</v>
+        <v>827</v>
       </c>
       <c r="E219">
         <v>340</v>
@@ -9985,16 +9976,16 @@
     </row>
     <row r="220" spans="1:7">
       <c r="A220" t="s">
-        <v>840</v>
+        <v>828</v>
       </c>
       <c r="B220" t="s">
-        <v>841</v>
+        <v>829</v>
       </c>
       <c r="C220" t="s">
-        <v>842</v>
+        <v>830</v>
       </c>
       <c r="D220" t="s">
-        <v>843</v>
+        <v>831</v>
       </c>
       <c r="E220">
         <v>3170</v>
@@ -10008,16 +9999,16 @@
     </row>
     <row r="221" spans="1:7">
       <c r="A221" t="s">
-        <v>844</v>
+        <v>832</v>
       </c>
       <c r="B221" t="s">
-        <v>845</v>
+        <v>833</v>
       </c>
       <c r="C221" t="s">
-        <v>846</v>
+        <v>834</v>
       </c>
       <c r="D221" t="s">
-        <v>847</v>
+        <v>835</v>
       </c>
       <c r="E221">
         <v>129</v>
@@ -10031,16 +10022,16 @@
     </row>
     <row r="222" spans="1:7">
       <c r="A222" t="s">
-        <v>848</v>
+        <v>836</v>
       </c>
       <c r="B222" t="s">
-        <v>849</v>
+        <v>837</v>
       </c>
       <c r="C222" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
       <c r="D222" t="s">
-        <v>851</v>
+        <v>839</v>
       </c>
       <c r="E222">
         <v>176</v>
@@ -10054,16 +10045,16 @@
     </row>
     <row r="223" spans="1:7">
       <c r="A223" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
       <c r="B223" t="s">
-        <v>853</v>
+        <v>841</v>
       </c>
       <c r="C223" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
       <c r="D223" t="s">
-        <v>853</v>
+        <v>841</v>
       </c>
       <c r="E223">
         <v>305</v>
@@ -10077,16 +10068,16 @@
     </row>
     <row r="224" spans="1:7">
       <c r="A224" t="s">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="B224" t="s">
-        <v>856</v>
+        <v>844</v>
       </c>
       <c r="C224" t="s">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="D224" t="s">
-        <v>858</v>
+        <v>846</v>
       </c>
       <c r="E224">
         <v>275</v>
@@ -10100,16 +10091,16 @@
     </row>
     <row r="225" spans="1:7">
       <c r="A225" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="B225" t="s">
-        <v>860</v>
+        <v>848</v>
       </c>
       <c r="C225" t="s">
-        <v>861</v>
+        <v>849</v>
       </c>
       <c r="D225" t="s">
-        <v>862</v>
+        <v>850</v>
       </c>
       <c r="E225">
         <v>207</v>
@@ -10123,16 +10114,16 @@
     </row>
     <row r="226" spans="1:7">
       <c r="A226" t="s">
-        <v>863</v>
+        <v>851</v>
       </c>
       <c r="B226" t="s">
-        <v>864</v>
+        <v>852</v>
       </c>
       <c r="C226" t="s">
-        <v>865</v>
+        <v>853</v>
       </c>
       <c r="D226" t="s">
-        <v>866</v>
+        <v>854</v>
       </c>
       <c r="E226">
         <v>310</v>
@@ -10146,16 +10137,16 @@
     </row>
     <row r="227" spans="1:7">
       <c r="A227" t="s">
-        <v>867</v>
+        <v>855</v>
       </c>
       <c r="B227" t="s">
-        <v>868</v>
+        <v>856</v>
       </c>
       <c r="C227" t="s">
-        <v>869</v>
+        <v>857</v>
       </c>
       <c r="D227" t="s">
-        <v>870</v>
+        <v>858</v>
       </c>
       <c r="E227">
         <v>192</v>
@@ -10169,16 +10160,16 @@
     </row>
     <row r="228" spans="1:7">
       <c r="A228" t="s">
-        <v>871</v>
+        <v>859</v>
       </c>
       <c r="B228" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
       <c r="C228" t="s">
-        <v>873</v>
+        <v>861</v>
       </c>
       <c r="D228" t="s">
-        <v>874</v>
+        <v>862</v>
       </c>
       <c r="E228">
         <v>400</v>
@@ -10192,16 +10183,16 @@
     </row>
     <row r="229" spans="1:7">
       <c r="A229" t="s">
-        <v>875</v>
+        <v>863</v>
       </c>
       <c r="B229" t="s">
-        <v>876</v>
+        <v>864</v>
       </c>
       <c r="C229" t="s">
-        <v>877</v>
+        <v>865</v>
       </c>
       <c r="D229" t="s">
-        <v>878</v>
+        <v>866</v>
       </c>
       <c r="E229">
         <v>234</v>
@@ -10215,16 +10206,16 @@
     </row>
     <row r="230" spans="1:7">
       <c r="A230" t="s">
-        <v>879</v>
+        <v>867</v>
       </c>
       <c r="B230" t="s">
-        <v>880</v>
+        <v>868</v>
       </c>
       <c r="C230" t="s">
-        <v>881</v>
+        <v>869</v>
       </c>
       <c r="D230" t="s">
-        <v>882</v>
+        <v>870</v>
       </c>
       <c r="E230">
         <v>148</v>
@@ -10238,16 +10229,16 @@
     </row>
     <row r="231" spans="1:7">
       <c r="A231" t="s">
-        <v>883</v>
+        <v>871</v>
       </c>
       <c r="B231" t="s">
-        <v>884</v>
+        <v>872</v>
       </c>
       <c r="C231" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="D231" t="s">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="E231">
         <v>269</v>
@@ -10261,16 +10252,16 @@
     </row>
     <row r="232" spans="1:7">
       <c r="A232" t="s">
-        <v>887</v>
+        <v>875</v>
       </c>
       <c r="B232" t="s">
-        <v>888</v>
+        <v>876</v>
       </c>
       <c r="C232" t="s">
-        <v>889</v>
+        <v>877</v>
       </c>
       <c r="D232" t="s">
-        <v>890</v>
+        <v>878</v>
       </c>
       <c r="E232">
         <v>50</v>
@@ -10284,16 +10275,16 @@
     </row>
     <row r="233" spans="1:7">
       <c r="A233" t="s">
-        <v>891</v>
+        <v>879</v>
       </c>
       <c r="B233" t="s">
-        <v>892</v>
+        <v>880</v>
       </c>
       <c r="C233" t="s">
-        <v>893</v>
+        <v>881</v>
       </c>
       <c r="D233" t="s">
-        <v>894</v>
+        <v>882</v>
       </c>
       <c r="E233">
         <v>140</v>
@@ -10307,16 +10298,16 @@
     </row>
     <row r="234" spans="1:7">
       <c r="A234" t="s">
-        <v>895</v>
+        <v>883</v>
       </c>
       <c r="B234" t="s">
-        <v>896</v>
+        <v>884</v>
       </c>
       <c r="C234" t="s">
-        <v>897</v>
+        <v>885</v>
       </c>
       <c r="D234" t="s">
-        <v>898</v>
+        <v>886</v>
       </c>
       <c r="E234">
         <v>43</v>
@@ -10330,16 +10321,16 @@
     </row>
     <row r="235" spans="1:7">
       <c r="A235" t="s">
-        <v>899</v>
+        <v>887</v>
       </c>
       <c r="B235" t="s">
-        <v>900</v>
+        <v>888</v>
       </c>
       <c r="C235" t="s">
-        <v>901</v>
+        <v>889</v>
       </c>
       <c r="D235" t="s">
-        <v>902</v>
+        <v>890</v>
       </c>
       <c r="E235">
         <v>131</v>
@@ -10353,16 +10344,16 @@
     </row>
     <row r="236" spans="1:7">
       <c r="A236" t="s">
-        <v>903</v>
+        <v>891</v>
       </c>
       <c r="B236" t="s">
-        <v>904</v>
+        <v>892</v>
       </c>
       <c r="C236" t="s">
-        <v>905</v>
+        <v>893</v>
       </c>
       <c r="D236" t="s">
-        <v>906</v>
+        <v>894</v>
       </c>
       <c r="E236">
         <v>800</v>
@@ -10376,16 +10367,16 @@
     </row>
     <row r="237" spans="1:7">
       <c r="A237" t="s">
-        <v>907</v>
+        <v>895</v>
       </c>
       <c r="B237" t="s">
-        <v>908</v>
+        <v>896</v>
       </c>
       <c r="C237" t="s">
-        <v>909</v>
+        <v>897</v>
       </c>
       <c r="D237" t="s">
-        <v>910</v>
+        <v>898</v>
       </c>
       <c r="E237">
         <v>220</v>
@@ -10399,16 +10390,16 @@
     </row>
     <row r="238" spans="1:7">
       <c r="A238" t="s">
-        <v>911</v>
+        <v>899</v>
       </c>
       <c r="B238" t="s">
-        <v>912</v>
+        <v>900</v>
       </c>
       <c r="C238" t="s">
-        <v>913</v>
+        <v>901</v>
       </c>
       <c r="D238" t="s">
-        <v>914</v>
+        <v>902</v>
       </c>
       <c r="E238">
         <v>1000</v>
@@ -10422,16 +10413,16 @@
     </row>
     <row r="239" spans="1:7">
       <c r="A239" t="s">
-        <v>915</v>
+        <v>903</v>
       </c>
       <c r="B239" t="s">
-        <v>916</v>
+        <v>904</v>
       </c>
       <c r="C239" t="s">
-        <v>917</v>
+        <v>905</v>
       </c>
       <c r="D239" t="s">
-        <v>918</v>
+        <v>906</v>
       </c>
       <c r="E239">
         <v>450</v>
@@ -10445,16 +10436,16 @@
     </row>
     <row r="240" spans="1:7">
       <c r="A240" t="s">
-        <v>919</v>
+        <v>907</v>
       </c>
       <c r="B240" t="s">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="C240" t="s">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="D240" t="s">
-        <v>922</v>
+        <v>910</v>
       </c>
       <c r="E240">
         <v>422</v>
@@ -10468,16 +10459,16 @@
     </row>
     <row r="241" spans="1:7">
       <c r="A241" t="s">
-        <v>923</v>
+        <v>911</v>
       </c>
       <c r="B241" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
       <c r="C241" t="s">
-        <v>925</v>
+        <v>913</v>
       </c>
       <c r="D241" t="s">
-        <v>926</v>
+        <v>914</v>
       </c>
       <c r="E241">
         <v>346</v>
@@ -10491,16 +10482,16 @@
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
-        <v>1472</v>
+        <v>1447</v>
       </c>
       <c r="B242" t="s">
-        <v>1473</v>
+        <v>1448</v>
       </c>
       <c r="C242" t="s">
-        <v>1474</v>
+        <v>1449</v>
       </c>
       <c r="D242" t="s">
-        <v>1473</v>
+        <v>1448</v>
       </c>
       <c r="E242">
         <v>277</v>
@@ -10514,16 +10505,16 @@
     </row>
     <row r="243" spans="1:7">
       <c r="A243" t="s">
-        <v>927</v>
+        <v>915</v>
       </c>
       <c r="B243" t="s">
-        <v>928</v>
+        <v>916</v>
       </c>
       <c r="C243" t="s">
-        <v>929</v>
+        <v>917</v>
       </c>
       <c r="D243" t="s">
-        <v>930</v>
+        <v>918</v>
       </c>
       <c r="E243">
         <v>149</v>
@@ -10537,16 +10528,16 @@
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
-        <v>931</v>
+        <v>919</v>
       </c>
       <c r="B244" t="s">
-        <v>932</v>
+        <v>920</v>
       </c>
       <c r="C244" t="s">
-        <v>931</v>
+        <v>919</v>
       </c>
       <c r="D244" t="s">
-        <v>933</v>
+        <v>921</v>
       </c>
       <c r="E244">
         <v>210</v>
@@ -10560,16 +10551,16 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>934</v>
+        <v>922</v>
       </c>
       <c r="B245" t="s">
-        <v>935</v>
+        <v>923</v>
       </c>
       <c r="C245" t="s">
-        <v>936</v>
+        <v>924</v>
       </c>
       <c r="D245" t="s">
-        <v>937</v>
+        <v>925</v>
       </c>
       <c r="E245">
         <v>260</v>
@@ -10583,16 +10574,16 @@
     </row>
     <row r="246" spans="1:7">
       <c r="A246" t="s">
-        <v>938</v>
+        <v>926</v>
       </c>
       <c r="B246" t="s">
-        <v>939</v>
+        <v>927</v>
       </c>
       <c r="C246" t="s">
-        <v>940</v>
+        <v>928</v>
       </c>
       <c r="D246" t="s">
-        <v>939</v>
+        <v>927</v>
       </c>
       <c r="E246">
         <v>177</v>
@@ -10606,16 +10597,16 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247" t="s">
-        <v>941</v>
+        <v>929</v>
       </c>
       <c r="B247" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="C247" t="s">
-        <v>943</v>
+        <v>931</v>
       </c>
       <c r="D247" t="s">
-        <v>944</v>
+        <v>932</v>
       </c>
       <c r="E247">
         <v>81</v>
@@ -10629,16 +10620,16 @@
     </row>
     <row r="248" spans="1:7">
       <c r="A248" t="s">
-        <v>945</v>
+        <v>933</v>
       </c>
       <c r="B248" t="s">
-        <v>946</v>
+        <v>934</v>
       </c>
       <c r="C248" t="s">
-        <v>947</v>
+        <v>935</v>
       </c>
       <c r="D248" t="s">
-        <v>948</v>
+        <v>936</v>
       </c>
       <c r="E248">
         <v>782</v>
@@ -10652,16 +10643,16 @@
     </row>
     <row r="249" spans="1:7">
       <c r="A249" t="s">
-        <v>949</v>
+        <v>937</v>
       </c>
       <c r="B249" t="s">
-        <v>950</v>
+        <v>938</v>
       </c>
       <c r="C249" t="s">
-        <v>951</v>
+        <v>939</v>
       </c>
       <c r="D249" t="s">
-        <v>952</v>
+        <v>940</v>
       </c>
       <c r="E249">
         <v>192</v>
@@ -10675,16 +10666,16 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250" t="s">
-        <v>953</v>
+        <v>941</v>
       </c>
       <c r="B250" t="s">
-        <v>954</v>
+        <v>942</v>
       </c>
       <c r="C250" t="s">
-        <v>955</v>
+        <v>943</v>
       </c>
       <c r="D250" t="s">
-        <v>956</v>
+        <v>944</v>
       </c>
       <c r="E250">
         <v>147</v>
@@ -10698,16 +10689,16 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251" t="s">
-        <v>957</v>
+        <v>945</v>
       </c>
       <c r="B251" t="s">
-        <v>958</v>
+        <v>946</v>
       </c>
       <c r="C251" t="s">
-        <v>959</v>
+        <v>947</v>
       </c>
       <c r="D251" t="s">
-        <v>960</v>
+        <v>948</v>
       </c>
       <c r="E251">
         <v>170</v>
@@ -10721,16 +10712,16 @@
     </row>
     <row r="252" spans="1:7">
       <c r="A252" t="s">
-        <v>961</v>
+        <v>949</v>
       </c>
       <c r="B252" t="s">
-        <v>962</v>
+        <v>950</v>
       </c>
       <c r="C252" t="s">
-        <v>963</v>
+        <v>951</v>
       </c>
       <c r="D252" t="s">
-        <v>964</v>
+        <v>952</v>
       </c>
       <c r="E252">
         <v>310</v>
@@ -10744,16 +10735,16 @@
     </row>
     <row r="253" spans="1:7">
       <c r="A253" t="s">
-        <v>965</v>
+        <v>953</v>
       </c>
       <c r="B253" t="s">
-        <v>966</v>
+        <v>954</v>
       </c>
       <c r="C253" t="s">
-        <v>967</v>
+        <v>955</v>
       </c>
       <c r="D253" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="E253">
         <v>238</v>
@@ -10767,16 +10758,16 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254" t="s">
-        <v>969</v>
+        <v>957</v>
       </c>
       <c r="B254" t="s">
-        <v>970</v>
+        <v>958</v>
       </c>
       <c r="C254" t="s">
-        <v>971</v>
+        <v>959</v>
       </c>
       <c r="D254" t="s">
-        <v>972</v>
+        <v>960</v>
       </c>
       <c r="E254">
         <v>114</v>
@@ -10787,16 +10778,16 @@
     </row>
     <row r="255" spans="1:7">
       <c r="A255" t="s">
-        <v>973</v>
+        <v>961</v>
       </c>
       <c r="B255" t="s">
-        <v>974</v>
+        <v>962</v>
       </c>
       <c r="C255" t="s">
-        <v>975</v>
+        <v>963</v>
       </c>
       <c r="D255" t="s">
-        <v>976</v>
+        <v>964</v>
       </c>
       <c r="E255">
         <v>144</v>
@@ -10810,16 +10801,16 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256" t="s">
-        <v>977</v>
+        <v>965</v>
       </c>
       <c r="B256" t="s">
-        <v>978</v>
+        <v>966</v>
       </c>
       <c r="C256" t="s">
-        <v>979</v>
+        <v>967</v>
       </c>
       <c r="D256" t="s">
-        <v>980</v>
+        <v>968</v>
       </c>
       <c r="E256">
         <v>126</v>
@@ -10833,16 +10824,16 @@
     </row>
     <row r="257" spans="1:7">
       <c r="A257" t="s">
-        <v>981</v>
+        <v>969</v>
       </c>
       <c r="B257" t="s">
-        <v>982</v>
+        <v>970</v>
       </c>
       <c r="C257" t="s">
-        <v>983</v>
+        <v>971</v>
       </c>
       <c r="D257" t="s">
-        <v>984</v>
+        <v>972</v>
       </c>
       <c r="E257">
         <v>1340</v>
@@ -10856,16 +10847,16 @@
     </row>
     <row r="258" spans="1:7">
       <c r="A258" t="s">
-        <v>985</v>
+        <v>973</v>
       </c>
       <c r="B258" t="s">
-        <v>986</v>
+        <v>974</v>
       </c>
       <c r="C258" t="s">
-        <v>987</v>
+        <v>975</v>
       </c>
       <c r="D258" t="s">
-        <v>988</v>
+        <v>976</v>
       </c>
       <c r="E258">
         <v>205</v>
@@ -10879,16 +10870,16 @@
     </row>
     <row r="259" spans="1:7">
       <c r="A259" t="s">
-        <v>989</v>
+        <v>977</v>
       </c>
       <c r="B259" t="s">
-        <v>990</v>
+        <v>978</v>
       </c>
       <c r="C259" t="s">
-        <v>991</v>
+        <v>979</v>
       </c>
       <c r="D259" t="s">
-        <v>992</v>
+        <v>980</v>
       </c>
       <c r="E259">
         <v>1370</v>
@@ -10902,16 +10893,16 @@
     </row>
     <row r="260" spans="1:7">
       <c r="A260" t="s">
-        <v>993</v>
+        <v>981</v>
       </c>
       <c r="B260" t="s">
-        <v>994</v>
+        <v>982</v>
       </c>
       <c r="C260" t="s">
-        <v>995</v>
+        <v>983</v>
       </c>
       <c r="D260" t="s">
-        <v>996</v>
+        <v>984</v>
       </c>
       <c r="E260">
         <v>278</v>
@@ -10925,16 +10916,16 @@
     </row>
     <row r="261" spans="1:7">
       <c r="A261" t="s">
-        <v>997</v>
+        <v>985</v>
       </c>
       <c r="B261" t="s">
-        <v>998</v>
+        <v>986</v>
       </c>
       <c r="C261" t="s">
-        <v>999</v>
+        <v>987</v>
       </c>
       <c r="D261" t="s">
-        <v>1000</v>
+        <v>988</v>
       </c>
       <c r="E261">
         <v>860</v>
@@ -10948,16 +10939,16 @@
     </row>
     <row r="262" spans="1:7">
       <c r="A262" t="s">
-        <v>1001</v>
+        <v>989</v>
       </c>
       <c r="B262" t="s">
-        <v>1002</v>
+        <v>990</v>
       </c>
       <c r="C262" t="s">
-        <v>1003</v>
+        <v>991</v>
       </c>
       <c r="D262" t="s">
-        <v>1004</v>
+        <v>992</v>
       </c>
       <c r="E262">
         <v>221</v>
@@ -10971,16 +10962,16 @@
     </row>
     <row r="263" spans="1:7">
       <c r="A263" t="s">
-        <v>1005</v>
+        <v>993</v>
       </c>
       <c r="B263" t="s">
-        <v>1006</v>
+        <v>994</v>
       </c>
       <c r="C263" t="s">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="D263" t="s">
-        <v>1008</v>
+        <v>996</v>
       </c>
       <c r="E263">
         <v>229</v>
@@ -10994,16 +10985,16 @@
     </row>
     <row r="264" spans="1:7">
       <c r="A264" t="s">
-        <v>1009</v>
+        <v>997</v>
       </c>
       <c r="B264" t="s">
-        <v>1010</v>
+        <v>998</v>
       </c>
       <c r="C264" t="s">
-        <v>1011</v>
+        <v>999</v>
       </c>
       <c r="D264" t="s">
-        <v>1012</v>
+        <v>1000</v>
       </c>
       <c r="E264">
         <v>191</v>
@@ -11017,16 +11008,16 @@
     </row>
     <row r="265" spans="1:7">
       <c r="A265" t="s">
-        <v>1013</v>
+        <v>1001</v>
       </c>
       <c r="B265" t="s">
-        <v>1014</v>
+        <v>1002</v>
       </c>
       <c r="C265" t="s">
-        <v>1015</v>
+        <v>1003</v>
       </c>
       <c r="D265" t="s">
-        <v>1013</v>
+        <v>1001</v>
       </c>
       <c r="E265">
         <v>173</v>
@@ -11040,16 +11031,16 @@
     </row>
     <row r="266" spans="1:7">
       <c r="A266" t="s">
-        <v>1016</v>
+        <v>1004</v>
       </c>
       <c r="B266" t="s">
-        <v>1017</v>
+        <v>1005</v>
       </c>
       <c r="C266" t="s">
-        <v>1018</v>
+        <v>1006</v>
       </c>
       <c r="D266" t="s">
-        <v>1017</v>
+        <v>1005</v>
       </c>
       <c r="E266">
         <v>503</v>
@@ -11063,16 +11054,16 @@
     </row>
     <row r="267" spans="1:7">
       <c r="A267" t="s">
-        <v>1019</v>
+        <v>1007</v>
       </c>
       <c r="B267" t="s">
-        <v>1019</v>
+        <v>1007</v>
       </c>
       <c r="C267" t="s">
-        <v>1019</v>
+        <v>1007</v>
       </c>
       <c r="D267" t="s">
-        <v>1020</v>
+        <v>1008</v>
       </c>
       <c r="E267">
         <v>393</v>
@@ -11086,16 +11077,16 @@
     </row>
     <row r="268" spans="1:7">
       <c r="A268" t="s">
-        <v>1021</v>
+        <v>1009</v>
       </c>
       <c r="B268" t="s">
-        <v>1022</v>
+        <v>1010</v>
       </c>
       <c r="C268" t="s">
-        <v>1022</v>
+        <v>1010</v>
       </c>
       <c r="D268" t="s">
-        <v>1022</v>
+        <v>1010</v>
       </c>
       <c r="E268">
         <v>295</v>
@@ -11109,16 +11100,16 @@
     </row>
     <row r="269" spans="1:7">
       <c r="A269" t="s">
-        <v>1023</v>
+        <v>1011</v>
       </c>
       <c r="B269" t="s">
-        <v>1023</v>
+        <v>1011</v>
       </c>
       <c r="C269" t="s">
-        <v>1024</v>
+        <v>1012</v>
       </c>
       <c r="D269" t="s">
-        <v>1023</v>
+        <v>1011</v>
       </c>
       <c r="E269">
         <v>190</v>
@@ -11132,16 +11123,16 @@
     </row>
     <row r="270" spans="1:7">
       <c r="A270" t="s">
-        <v>1025</v>
+        <v>1013</v>
       </c>
       <c r="B270" t="s">
-        <v>1026</v>
+        <v>1014</v>
       </c>
       <c r="C270" t="s">
-        <v>1027</v>
+        <v>1015</v>
       </c>
       <c r="D270" t="s">
-        <v>1028</v>
+        <v>1016</v>
       </c>
       <c r="E270">
         <v>330</v>
@@ -11155,16 +11146,16 @@
     </row>
     <row r="271" spans="1:7">
       <c r="A271" t="s">
-        <v>1029</v>
+        <v>1017</v>
       </c>
       <c r="B271" t="s">
-        <v>1030</v>
+        <v>1018</v>
       </c>
       <c r="C271" t="s">
-        <v>1031</v>
+        <v>1019</v>
       </c>
       <c r="D271" t="s">
-        <v>1032</v>
+        <v>1020</v>
       </c>
       <c r="E271">
         <v>158</v>
@@ -11178,16 +11169,16 @@
     </row>
     <row r="272" spans="1:7">
       <c r="A272" t="s">
-        <v>1033</v>
+        <v>1021</v>
       </c>
       <c r="B272" t="s">
-        <v>1034</v>
+        <v>1022</v>
       </c>
       <c r="C272" t="s">
-        <v>1035</v>
+        <v>1023</v>
       </c>
       <c r="D272" t="s">
-        <v>1036</v>
+        <v>1024</v>
       </c>
       <c r="E272">
         <v>240</v>
@@ -11201,16 +11192,16 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
-        <v>1037</v>
+        <v>1025</v>
       </c>
       <c r="B273" t="s">
-        <v>1038</v>
+        <v>1026</v>
       </c>
       <c r="C273" t="s">
-        <v>1039</v>
+        <v>1027</v>
       </c>
       <c r="D273" t="s">
-        <v>1040</v>
+        <v>1028</v>
       </c>
       <c r="E273">
         <v>850</v>
@@ -11224,16 +11215,16 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>1041</v>
+        <v>1029</v>
       </c>
       <c r="B274" t="s">
-        <v>1042</v>
+        <v>1030</v>
       </c>
       <c r="C274" t="s">
-        <v>1043</v>
+        <v>1031</v>
       </c>
       <c r="D274" t="s">
-        <v>1044</v>
+        <v>1032</v>
       </c>
       <c r="E274">
         <v>140</v>
@@ -11247,16 +11238,16 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>1045</v>
+        <v>1033</v>
       </c>
       <c r="B275" t="s">
-        <v>1046</v>
+        <v>1034</v>
       </c>
       <c r="C275" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
       <c r="D275" t="s">
-        <v>1048</v>
+        <v>1036</v>
       </c>
       <c r="E275">
         <v>124</v>
@@ -11270,16 +11261,16 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>1049</v>
+        <v>1037</v>
       </c>
       <c r="B276" t="s">
-        <v>1050</v>
+        <v>1038</v>
       </c>
       <c r="C276" t="s">
-        <v>1051</v>
+        <v>1039</v>
       </c>
       <c r="D276" t="s">
-        <v>1052</v>
+        <v>1040</v>
       </c>
       <c r="E276">
         <v>132</v>
@@ -11293,16 +11284,16 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>1053</v>
+        <v>1041</v>
       </c>
       <c r="B277" t="s">
-        <v>1054</v>
+        <v>1042</v>
       </c>
       <c r="C277" t="s">
-        <v>1055</v>
+        <v>1043</v>
       </c>
       <c r="D277" t="s">
-        <v>1056</v>
+        <v>1044</v>
       </c>
       <c r="E277">
         <v>105</v>
@@ -11316,16 +11307,16 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278" t="s">
-        <v>1057</v>
+        <v>1045</v>
       </c>
       <c r="B278" t="s">
-        <v>1058</v>
+        <v>1046</v>
       </c>
       <c r="C278" t="s">
-        <v>1059</v>
+        <v>1047</v>
       </c>
       <c r="D278" t="s">
-        <v>1060</v>
+        <v>1048</v>
       </c>
       <c r="E278">
         <v>100</v>
@@ -11339,16 +11330,16 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279" t="s">
-        <v>1061</v>
+        <v>1049</v>
       </c>
       <c r="B279" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="C279" t="s">
-        <v>1063</v>
+        <v>1051</v>
       </c>
       <c r="D279" t="s">
-        <v>1064</v>
+        <v>1052</v>
       </c>
       <c r="E279">
         <v>200</v>
@@ -11362,16 +11353,16 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="B280" t="s">
-        <v>1066</v>
+        <v>1054</v>
       </c>
       <c r="C280" t="s">
-        <v>1067</v>
+        <v>1055</v>
       </c>
       <c r="D280" t="s">
-        <v>1068</v>
+        <v>1056</v>
       </c>
       <c r="E280">
         <v>33</v>
@@ -11385,16 +11376,16 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>1069</v>
+        <v>1057</v>
       </c>
       <c r="B281" t="s">
-        <v>1070</v>
+        <v>1058</v>
       </c>
       <c r="C281" t="s">
-        <v>1071</v>
+        <v>1059</v>
       </c>
       <c r="D281" t="s">
-        <v>1072</v>
+        <v>1060</v>
       </c>
       <c r="E281">
         <v>78</v>
@@ -11408,16 +11399,16 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>1073</v>
+        <v>1061</v>
       </c>
       <c r="B282" t="s">
-        <v>1074</v>
+        <v>1062</v>
       </c>
       <c r="C282" t="s">
-        <v>1075</v>
+        <v>1063</v>
       </c>
       <c r="D282" t="s">
-        <v>1076</v>
+        <v>1064</v>
       </c>
       <c r="E282">
         <v>362</v>
@@ -11431,16 +11422,16 @@
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>1077</v>
+        <v>1065</v>
       </c>
       <c r="B283" t="s">
-        <v>1078</v>
+        <v>1066</v>
       </c>
       <c r="C283" t="s">
-        <v>1079</v>
+        <v>1067</v>
       </c>
       <c r="D283" t="s">
-        <v>1080</v>
+        <v>1068</v>
       </c>
       <c r="E283">
         <v>50</v>
@@ -11454,16 +11445,16 @@
     </row>
     <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>1081</v>
+        <v>1069</v>
       </c>
       <c r="B284" t="s">
-        <v>1082</v>
+        <v>1070</v>
       </c>
       <c r="C284" t="s">
-        <v>1083</v>
+        <v>1071</v>
       </c>
       <c r="D284" t="s">
-        <v>1084</v>
+        <v>1072</v>
       </c>
       <c r="E284">
         <v>80</v>
@@ -11477,16 +11468,16 @@
     </row>
     <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="B285" t="s">
-        <v>1086</v>
+        <v>1074</v>
       </c>
       <c r="C285" t="s">
-        <v>1087</v>
+        <v>1075</v>
       </c>
       <c r="D285" t="s">
-        <v>1088</v>
+        <v>1076</v>
       </c>
       <c r="E285">
         <v>100</v>
@@ -11500,16 +11491,16 @@
     </row>
     <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>1089</v>
+        <v>1077</v>
       </c>
       <c r="B286" t="s">
-        <v>1090</v>
+        <v>1078</v>
       </c>
       <c r="C286" t="s">
-        <v>1091</v>
+        <v>1079</v>
       </c>
       <c r="D286" t="s">
-        <v>1092</v>
+        <v>1080</v>
       </c>
       <c r="E286">
         <v>60</v>
@@ -11523,16 +11514,16 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" t="s">
-        <v>1093</v>
+        <v>1081</v>
       </c>
       <c r="B287" t="s">
-        <v>1094</v>
+        <v>1082</v>
       </c>
       <c r="C287" t="s">
-        <v>1095</v>
+        <v>1083</v>
       </c>
       <c r="D287" t="s">
-        <v>1096</v>
+        <v>1084</v>
       </c>
       <c r="E287">
         <v>130</v>
@@ -11546,16 +11537,16 @@
     </row>
     <row r="288" spans="1:7">
       <c r="A288" t="s">
-        <v>1097</v>
+        <v>1085</v>
       </c>
       <c r="B288" t="s">
-        <v>1098</v>
+        <v>1086</v>
       </c>
       <c r="C288" t="s">
-        <v>1099</v>
+        <v>1087</v>
       </c>
       <c r="D288" t="s">
-        <v>1100</v>
+        <v>1088</v>
       </c>
       <c r="E288">
         <v>94</v>
@@ -11569,16 +11560,16 @@
     </row>
     <row r="289" spans="1:7">
       <c r="A289" t="s">
-        <v>1101</v>
+        <v>1089</v>
       </c>
       <c r="B289" t="s">
-        <v>1102</v>
+        <v>1090</v>
       </c>
       <c r="C289" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="D289" t="s">
-        <v>1104</v>
+        <v>1092</v>
       </c>
       <c r="E289">
         <v>150</v>
@@ -11592,16 +11583,16 @@
     </row>
     <row r="290" spans="1:7">
       <c r="A290" t="s">
-        <v>1105</v>
+        <v>1093</v>
       </c>
       <c r="B290" t="s">
-        <v>1106</v>
+        <v>1094</v>
       </c>
       <c r="C290" t="s">
-        <v>1107</v>
+        <v>1095</v>
       </c>
       <c r="D290" t="s">
-        <v>1108</v>
+        <v>1096</v>
       </c>
       <c r="E290">
         <v>90</v>
@@ -11615,16 +11606,16 @@
     </row>
     <row r="291" spans="1:7">
       <c r="A291" t="s">
-        <v>1109</v>
+        <v>1097</v>
       </c>
       <c r="B291" t="s">
-        <v>1110</v>
+        <v>1098</v>
       </c>
       <c r="C291" t="s">
-        <v>1111</v>
+        <v>1099</v>
       </c>
       <c r="D291" t="s">
-        <v>1112</v>
+        <v>1100</v>
       </c>
       <c r="E291">
         <v>260</v>
@@ -11638,16 +11629,16 @@
     </row>
     <row r="292" spans="1:7">
       <c r="A292" t="s">
-        <v>1113</v>
+        <v>1101</v>
       </c>
       <c r="B292" t="s">
-        <v>1114</v>
+        <v>1102</v>
       </c>
       <c r="C292" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="D292" t="s">
-        <v>1116</v>
+        <v>1104</v>
       </c>
       <c r="E292">
         <v>80</v>
@@ -11661,16 +11652,16 @@
     </row>
     <row r="293" spans="1:7">
       <c r="A293" t="s">
-        <v>1117</v>
+        <v>1105</v>
       </c>
       <c r="B293" t="s">
-        <v>1118</v>
+        <v>1106</v>
       </c>
       <c r="C293" t="s">
-        <v>1119</v>
+        <v>1107</v>
       </c>
       <c r="D293" t="s">
-        <v>1120</v>
+        <v>1108</v>
       </c>
       <c r="E293">
         <v>125</v>
@@ -11684,16 +11675,16 @@
     </row>
     <row r="294" spans="1:7">
       <c r="A294" t="s">
-        <v>1121</v>
+        <v>1109</v>
       </c>
       <c r="B294" t="s">
-        <v>1122</v>
+        <v>1110</v>
       </c>
       <c r="C294" t="s">
-        <v>1123</v>
+        <v>1111</v>
       </c>
       <c r="D294" t="s">
-        <v>1124</v>
+        <v>1112</v>
       </c>
       <c r="E294">
         <v>407</v>
@@ -11707,16 +11698,16 @@
     </row>
     <row r="295" spans="1:7">
       <c r="A295" t="s">
-        <v>1125</v>
+        <v>1113</v>
       </c>
       <c r="B295" t="s">
-        <v>1126</v>
+        <v>1114</v>
       </c>
       <c r="C295" t="s">
-        <v>1127</v>
+        <v>1115</v>
       </c>
       <c r="D295" t="s">
-        <v>1128</v>
+        <v>1116</v>
       </c>
       <c r="E295">
         <v>45</v>
@@ -11730,16 +11721,16 @@
     </row>
     <row r="296" spans="1:7">
       <c r="A296" t="s">
-        <v>1129</v>
+        <v>1117</v>
       </c>
       <c r="B296" t="s">
-        <v>954</v>
+        <v>942</v>
       </c>
       <c r="C296" t="s">
-        <v>955</v>
+        <v>943</v>
       </c>
       <c r="D296" t="s">
-        <v>956</v>
+        <v>944</v>
       </c>
       <c r="E296">
         <v>80</v>
@@ -11753,16 +11744,16 @@
     </row>
     <row r="297" spans="1:7">
       <c r="A297" t="s">
-        <v>1130</v>
+        <v>1118</v>
       </c>
       <c r="B297" t="s">
-        <v>1131</v>
+        <v>1119</v>
       </c>
       <c r="C297" t="s">
-        <v>1132</v>
+        <v>1120</v>
       </c>
       <c r="D297" t="s">
-        <v>1133</v>
+        <v>1121</v>
       </c>
       <c r="E297">
         <v>65</v>
@@ -11776,16 +11767,16 @@
     </row>
     <row r="298" spans="1:7">
       <c r="A298" t="s">
-        <v>1134</v>
+        <v>1122</v>
       </c>
       <c r="B298" t="s">
-        <v>1135</v>
+        <v>1123</v>
       </c>
       <c r="C298" t="s">
-        <v>1136</v>
+        <v>1124</v>
       </c>
       <c r="D298" t="s">
-        <v>1137</v>
+        <v>1125</v>
       </c>
       <c r="E298">
         <v>104</v>
@@ -11799,16 +11790,16 @@
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>1138</v>
+        <v>1126</v>
       </c>
       <c r="B299" t="s">
-        <v>1139</v>
+        <v>1127</v>
       </c>
       <c r="C299" t="s">
-        <v>1140</v>
+        <v>1128</v>
       </c>
       <c r="D299" t="s">
-        <v>1141</v>
+        <v>1129</v>
       </c>
       <c r="E299">
         <v>130</v>
@@ -11822,16 +11813,16 @@
     </row>
     <row r="300" spans="1:7">
       <c r="A300" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="B300" t="s">
-        <v>1143</v>
+        <v>1131</v>
       </c>
       <c r="C300" t="s">
-        <v>1144</v>
+        <v>1132</v>
       </c>
       <c r="D300" t="s">
-        <v>1145</v>
+        <v>1133</v>
       </c>
       <c r="E300">
         <v>44</v>
@@ -11845,16 +11836,16 @@
     </row>
     <row r="301" spans="1:7">
       <c r="A301" t="s">
-        <v>1146</v>
+        <v>1134</v>
       </c>
       <c r="B301" t="s">
-        <v>1147</v>
+        <v>1135</v>
       </c>
       <c r="C301" t="s">
-        <v>1148</v>
+        <v>1136</v>
       </c>
       <c r="D301" t="s">
-        <v>1149</v>
+        <v>1137</v>
       </c>
       <c r="E301">
         <v>705</v>
@@ -11868,16 +11859,16 @@
     </row>
     <row r="302" spans="1:7">
       <c r="A302" t="s">
-        <v>1150</v>
+        <v>1138</v>
       </c>
       <c r="B302" t="s">
-        <v>1151</v>
+        <v>1139</v>
       </c>
       <c r="C302" t="s">
-        <v>1152</v>
+        <v>1140</v>
       </c>
       <c r="D302" t="s">
-        <v>1153</v>
+        <v>1141</v>
       </c>
       <c r="E302">
         <v>592</v>
@@ -11891,16 +11882,16 @@
     </row>
     <row r="303" spans="1:7">
       <c r="A303" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="B303" t="s">
-        <v>1155</v>
+        <v>1143</v>
       </c>
       <c r="C303" t="s">
-        <v>1156</v>
+        <v>1144</v>
       </c>
       <c r="D303" t="s">
-        <v>1157</v>
+        <v>1145</v>
       </c>
       <c r="E303">
         <v>500</v>
@@ -11914,16 +11905,16 @@
     </row>
     <row r="304" spans="1:7">
       <c r="A304" t="s">
-        <v>1158</v>
+        <v>1146</v>
       </c>
       <c r="B304" t="s">
-        <v>1159</v>
+        <v>1147</v>
       </c>
       <c r="C304" t="s">
-        <v>1160</v>
+        <v>1148</v>
       </c>
       <c r="D304" t="s">
-        <v>1161</v>
+        <v>1149</v>
       </c>
       <c r="E304">
         <v>777</v>
@@ -11937,16 +11928,16 @@
     </row>
     <row r="305" spans="1:7">
       <c r="A305" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="B305" t="s">
-        <v>1163</v>
+        <v>1151</v>
       </c>
       <c r="C305" t="s">
-        <v>1164</v>
+        <v>1152</v>
       </c>
       <c r="D305" t="s">
-        <v>1165</v>
+        <v>1153</v>
       </c>
       <c r="E305">
         <v>786</v>
@@ -11960,16 +11951,16 @@
     </row>
     <row r="306" spans="1:7">
       <c r="A306" t="s">
-        <v>1166</v>
+        <v>1154</v>
       </c>
       <c r="B306" t="s">
-        <v>1167</v>
+        <v>1155</v>
       </c>
       <c r="C306" t="s">
-        <v>1168</v>
+        <v>1156</v>
       </c>
       <c r="D306" t="s">
-        <v>1169</v>
+        <v>1157</v>
       </c>
       <c r="E306">
         <v>379</v>
@@ -11983,16 +11974,16 @@
     </row>
     <row r="307" spans="1:7">
       <c r="A307" t="s">
-        <v>1170</v>
+        <v>1158</v>
       </c>
       <c r="B307" t="s">
-        <v>1171</v>
+        <v>1159</v>
       </c>
       <c r="C307" t="s">
-        <v>1172</v>
+        <v>1160</v>
       </c>
       <c r="D307" t="s">
-        <v>1173</v>
+        <v>1161</v>
       </c>
       <c r="E307">
         <v>704</v>
@@ -12006,16 +11997,16 @@
     </row>
     <row r="308" spans="1:7">
       <c r="A308" t="s">
-        <v>1174</v>
+        <v>1162</v>
       </c>
       <c r="B308" t="s">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="C308" t="s">
-        <v>1176</v>
+        <v>1164</v>
       </c>
       <c r="D308" t="s">
-        <v>1177</v>
+        <v>1165</v>
       </c>
       <c r="E308">
         <v>544</v>
@@ -12029,16 +12020,16 @@
     </row>
     <row r="309" spans="1:7">
       <c r="A309" t="s">
-        <v>1178</v>
+        <v>1166</v>
       </c>
       <c r="B309" t="s">
-        <v>1179</v>
+        <v>1167</v>
       </c>
       <c r="C309" t="s">
-        <v>1180</v>
+        <v>1168</v>
       </c>
       <c r="D309" t="s">
-        <v>1181</v>
+        <v>1169</v>
       </c>
       <c r="E309">
         <v>818</v>
@@ -12052,16 +12043,16 @@
     </row>
     <row r="310" spans="1:7">
       <c r="A310" t="s">
-        <v>1182</v>
+        <v>1170</v>
       </c>
       <c r="B310" t="s">
-        <v>1183</v>
+        <v>1171</v>
       </c>
       <c r="C310" t="s">
-        <v>1184</v>
+        <v>1172</v>
       </c>
       <c r="D310" t="s">
-        <v>1185</v>
+        <v>1173</v>
       </c>
       <c r="E310">
         <v>705</v>
@@ -12075,16 +12066,16 @@
     </row>
     <row r="311" spans="1:7">
       <c r="A311" t="s">
-        <v>1186</v>
+        <v>1174</v>
       </c>
       <c r="B311" t="s">
-        <v>1187</v>
+        <v>1175</v>
       </c>
       <c r="C311" t="s">
-        <v>1188</v>
+        <v>1176</v>
       </c>
       <c r="D311" t="s">
-        <v>1189</v>
+        <v>1177</v>
       </c>
       <c r="E311">
         <v>458</v>
@@ -12098,16 +12089,16 @@
     </row>
     <row r="312" spans="1:7">
       <c r="A312" t="s">
-        <v>1190</v>
+        <v>1178</v>
       </c>
       <c r="B312" t="s">
-        <v>1191</v>
+        <v>1179</v>
       </c>
       <c r="C312" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="D312" t="s">
-        <v>1193</v>
+        <v>1181</v>
       </c>
       <c r="E312">
         <v>690</v>
@@ -12121,16 +12112,16 @@
     </row>
     <row r="313" spans="1:7">
       <c r="A313" t="s">
-        <v>1194</v>
+        <v>1182</v>
       </c>
       <c r="B313" t="s">
-        <v>1195</v>
+        <v>1183</v>
       </c>
       <c r="C313" t="s">
-        <v>1196</v>
+        <v>1184</v>
       </c>
       <c r="D313" t="s">
-        <v>1197</v>
+        <v>1185</v>
       </c>
       <c r="E313">
         <v>100</v>
@@ -12144,16 +12135,16 @@
     </row>
     <row r="314" spans="1:7">
       <c r="A314" t="s">
-        <v>1198</v>
+        <v>1186</v>
       </c>
       <c r="B314" t="s">
-        <v>1199</v>
+        <v>1187</v>
       </c>
       <c r="C314" t="s">
-        <v>1199</v>
+        <v>1187</v>
       </c>
       <c r="D314" t="s">
-        <v>1199</v>
+        <v>1187</v>
       </c>
       <c r="E314">
         <v>250</v>
@@ -12167,16 +12158,16 @@
     </row>
     <row r="315" spans="1:7">
       <c r="A315" t="s">
-        <v>1200</v>
+        <v>1188</v>
       </c>
       <c r="B315" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="C315" t="s">
-        <v>1202</v>
+        <v>1190</v>
       </c>
       <c r="D315" t="s">
-        <v>1203</v>
+        <v>1191</v>
       </c>
       <c r="E315">
         <v>100</v>
@@ -12190,16 +12181,16 @@
     </row>
     <row r="316" spans="1:7">
       <c r="A316" t="s">
-        <v>1204</v>
+        <v>1192</v>
       </c>
       <c r="B316" t="s">
-        <v>1205</v>
+        <v>1193</v>
       </c>
       <c r="C316" t="s">
-        <v>1206</v>
+        <v>1194</v>
       </c>
       <c r="D316" t="s">
-        <v>1207</v>
+        <v>1195</v>
       </c>
       <c r="E316">
         <v>130</v>
@@ -12213,16 +12204,16 @@
     </row>
     <row r="317" spans="1:7">
       <c r="A317" t="s">
-        <v>1208</v>
+        <v>1196</v>
       </c>
       <c r="B317" t="s">
-        <v>1208</v>
+        <v>1196</v>
       </c>
       <c r="C317" t="s">
-        <v>1209</v>
+        <v>1197</v>
       </c>
       <c r="D317" t="s">
-        <v>1208</v>
+        <v>1196</v>
       </c>
       <c r="E317">
         <v>50</v>
@@ -12236,16 +12227,16 @@
     </row>
     <row r="318" spans="1:7">
       <c r="A318" t="s">
-        <v>1210</v>
+        <v>1198</v>
       </c>
       <c r="B318" t="s">
-        <v>1211</v>
+        <v>1199</v>
       </c>
       <c r="C318" t="s">
-        <v>1212</v>
+        <v>1200</v>
       </c>
       <c r="D318" t="s">
-        <v>1213</v>
+        <v>1201</v>
       </c>
       <c r="E318">
         <v>0</v>
@@ -12259,16 +12250,16 @@
     </row>
     <row r="319" spans="1:7">
       <c r="A319" t="s">
-        <v>1214</v>
+        <v>1202</v>
       </c>
       <c r="B319" t="s">
-        <v>1215</v>
+        <v>1203</v>
       </c>
       <c r="C319" t="s">
-        <v>1216</v>
+        <v>1204</v>
       </c>
       <c r="D319" t="s">
-        <v>1217</v>
+        <v>1205</v>
       </c>
       <c r="E319">
         <v>3</v>
@@ -12282,16 +12273,16 @@
     </row>
     <row r="320" spans="1:7">
       <c r="A320" t="s">
-        <v>1475</v>
+        <v>1450</v>
       </c>
       <c r="B320" t="s">
-        <v>1476</v>
+        <v>1451</v>
       </c>
       <c r="C320" t="s">
-        <v>1477</v>
+        <v>1452</v>
       </c>
       <c r="D320" t="s">
-        <v>1478</v>
+        <v>1453</v>
       </c>
       <c r="E320">
         <v>50</v>
@@ -12305,7 +12296,7 @@
     </row>
     <row r="321" spans="1:7">
       <c r="A321" t="s">
-        <v>1218</v>
+        <v>1206</v>
       </c>
       <c r="B321" t="s">
         <v>502</v>
@@ -12328,16 +12319,16 @@
     </row>
     <row r="322" spans="1:7">
       <c r="A322" t="s">
-        <v>1219</v>
+        <v>1207</v>
       </c>
       <c r="B322" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="C322" t="s">
-        <v>1221</v>
+        <v>1209</v>
       </c>
       <c r="D322" t="s">
-        <v>1222</v>
+        <v>1210</v>
       </c>
       <c r="E322">
         <v>151</v>
@@ -12351,16 +12342,16 @@
     </row>
     <row r="323" spans="1:7">
       <c r="A323" t="s">
-        <v>1223</v>
+        <v>1211</v>
       </c>
       <c r="B323" t="s">
-        <v>1224</v>
+        <v>1212</v>
       </c>
       <c r="C323" t="s">
-        <v>1225</v>
+        <v>1213</v>
       </c>
       <c r="D323" t="s">
-        <v>1226</v>
+        <v>1214</v>
       </c>
       <c r="E323">
         <v>452</v>
@@ -12374,16 +12365,16 @@
     </row>
     <row r="324" spans="1:7">
       <c r="A324" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="B324" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="C324" t="s">
-        <v>1229</v>
+        <v>1217</v>
       </c>
       <c r="D324" t="s">
-        <v>1230</v>
+        <v>1218</v>
       </c>
       <c r="E324">
         <v>160</v>
@@ -12397,16 +12388,16 @@
     </row>
     <row r="325" spans="1:7">
       <c r="A325" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="B325" t="s">
-        <v>1232</v>
+        <v>1220</v>
       </c>
       <c r="C325" t="s">
-        <v>1233</v>
+        <v>1221</v>
       </c>
       <c r="D325" t="s">
-        <v>1234</v>
+        <v>1222</v>
       </c>
       <c r="E325">
         <v>90</v>
@@ -12420,16 +12411,16 @@
     </row>
     <row r="326" spans="1:7">
       <c r="A326" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="B326" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="C326" t="s">
-        <v>1237</v>
+        <v>1225</v>
       </c>
       <c r="D326" t="s">
-        <v>1238</v>
+        <v>1226</v>
       </c>
       <c r="E326">
         <v>120</v>
@@ -12443,16 +12434,16 @@
     </row>
     <row r="327" spans="1:7">
       <c r="A327" t="s">
-        <v>1239</v>
+        <v>1227</v>
       </c>
       <c r="B327" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="C327" t="s">
-        <v>1241</v>
+        <v>1229</v>
       </c>
       <c r="D327" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="E327">
         <v>139</v>
@@ -12466,16 +12457,16 @@
     </row>
     <row r="328" spans="1:7">
       <c r="A328" t="s">
-        <v>1243</v>
+        <v>1231</v>
       </c>
       <c r="B328" t="s">
-        <v>1244</v>
+        <v>1232</v>
       </c>
       <c r="C328" t="s">
-        <v>1245</v>
+        <v>1233</v>
       </c>
       <c r="D328" t="s">
-        <v>1246</v>
+        <v>1234</v>
       </c>
       <c r="E328">
         <v>157</v>
@@ -12489,16 +12480,16 @@
     </row>
     <row r="329" spans="1:7">
       <c r="A329" t="s">
-        <v>1247</v>
+        <v>1235</v>
       </c>
       <c r="B329" t="s">
-        <v>1248</v>
+        <v>1236</v>
       </c>
       <c r="C329" t="s">
-        <v>1249</v>
+        <v>1237</v>
       </c>
       <c r="D329" t="s">
-        <v>1250</v>
+        <v>1238</v>
       </c>
       <c r="E329">
         <v>274</v>
@@ -12512,16 +12503,16 @@
     </row>
     <row r="330" spans="1:7">
       <c r="A330" t="s">
-        <v>1251</v>
+        <v>1239</v>
       </c>
       <c r="B330" t="s">
-        <v>1252</v>
+        <v>1240</v>
       </c>
       <c r="C330" t="s">
-        <v>1253</v>
+        <v>1241</v>
       </c>
       <c r="D330" t="s">
-        <v>1254</v>
+        <v>1242</v>
       </c>
       <c r="E330">
         <v>225</v>
@@ -12535,16 +12526,16 @@
     </row>
     <row r="331" spans="1:7">
       <c r="A331" t="s">
-        <v>1255</v>
+        <v>1243</v>
       </c>
       <c r="B331" t="s">
-        <v>1256</v>
+        <v>1244</v>
       </c>
       <c r="C331" t="s">
-        <v>1257</v>
+        <v>1245</v>
       </c>
       <c r="D331" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="E331">
         <v>249</v>
@@ -12558,16 +12549,16 @@
     </row>
     <row r="332" spans="1:7">
       <c r="A332" t="s">
-        <v>1259</v>
+        <v>1247</v>
       </c>
       <c r="B332" t="s">
-        <v>1260</v>
+        <v>1248</v>
       </c>
       <c r="C332" t="s">
-        <v>1261</v>
+        <v>1249</v>
       </c>
       <c r="D332" t="s">
-        <v>1262</v>
+        <v>1250</v>
       </c>
       <c r="E332">
         <v>502</v>
@@ -12581,16 +12572,16 @@
     </row>
     <row r="333" spans="1:7">
       <c r="A333" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="B333" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="C333" t="s">
-        <v>1229</v>
+        <v>1217</v>
       </c>
       <c r="D333" t="s">
-        <v>1230</v>
+        <v>1218</v>
       </c>
       <c r="E333">
         <v>112</v>
@@ -12604,16 +12595,16 @@
     </row>
     <row r="334" spans="1:7">
       <c r="A334" t="s">
-        <v>1263</v>
+        <v>1251</v>
       </c>
       <c r="B334" t="s">
-        <v>1264</v>
+        <v>1252</v>
       </c>
       <c r="C334" t="s">
-        <v>1265</v>
+        <v>1253</v>
       </c>
       <c r="D334" t="s">
-        <v>1264</v>
+        <v>1252</v>
       </c>
       <c r="E334">
         <v>108</v>
@@ -12627,16 +12618,16 @@
     </row>
     <row r="335" spans="1:7">
       <c r="A335" t="s">
-        <v>1266</v>
+        <v>1254</v>
       </c>
       <c r="B335" t="s">
-        <v>1267</v>
+        <v>1255</v>
       </c>
       <c r="C335" t="s">
-        <v>1268</v>
+        <v>1256</v>
       </c>
       <c r="D335" t="s">
-        <v>1267</v>
+        <v>1255</v>
       </c>
       <c r="E335">
         <v>126</v>
@@ -12650,16 +12641,16 @@
     </row>
     <row r="336" spans="1:7">
       <c r="A336" t="s">
-        <v>1269</v>
+        <v>1257</v>
       </c>
       <c r="B336" t="s">
-        <v>1270</v>
+        <v>1258</v>
       </c>
       <c r="C336" t="s">
-        <v>1271</v>
+        <v>1259</v>
       </c>
       <c r="D336" t="s">
-        <v>1272</v>
+        <v>1260</v>
       </c>
       <c r="E336">
         <v>1390</v>
@@ -12673,16 +12664,16 @@
     </row>
     <row r="337" spans="1:7">
       <c r="A337" t="s">
-        <v>1273</v>
+        <v>1261</v>
       </c>
       <c r="B337" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="C337" t="s">
-        <v>1275</v>
+        <v>1263</v>
       </c>
       <c r="D337" t="s">
-        <v>1276</v>
+        <v>1264</v>
       </c>
       <c r="E337">
         <v>380</v>
@@ -12696,16 +12687,16 @@
     </row>
     <row r="338" spans="1:7">
       <c r="A338" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="B338" t="s">
-        <v>1278</v>
+        <v>1266</v>
       </c>
       <c r="C338" t="s">
-        <v>1279</v>
+        <v>1267</v>
       </c>
       <c r="D338" t="s">
-        <v>1280</v>
+        <v>1268</v>
       </c>
       <c r="E338">
         <v>130</v>
@@ -12719,16 +12710,16 @@
     </row>
     <row r="339" spans="1:7">
       <c r="A339" t="s">
-        <v>1281</v>
+        <v>1269</v>
       </c>
       <c r="B339" t="s">
-        <v>1282</v>
+        <v>1270</v>
       </c>
       <c r="C339" t="s">
-        <v>1283</v>
+        <v>1271</v>
       </c>
       <c r="D339" t="s">
-        <v>1284</v>
+        <v>1272</v>
       </c>
       <c r="E339">
         <v>103</v>
@@ -12742,16 +12733,16 @@
     </row>
     <row r="340" spans="1:7">
       <c r="A340" t="s">
-        <v>1459</v>
+        <v>1434</v>
       </c>
       <c r="B340" t="s">
-        <v>1460</v>
+        <v>1435</v>
       </c>
       <c r="C340" t="s">
-        <v>1461</v>
+        <v>1436</v>
       </c>
       <c r="D340" t="s">
-        <v>1462</v>
+        <v>1437</v>
       </c>
       <c r="E340">
         <v>31</v>
@@ -12765,16 +12756,16 @@
     </row>
     <row r="341" spans="1:7">
       <c r="A341" t="s">
-        <v>1285</v>
+        <v>1273</v>
       </c>
       <c r="B341" t="s">
-        <v>1286</v>
+        <v>1274</v>
       </c>
       <c r="C341" t="s">
-        <v>1287</v>
+        <v>1275</v>
       </c>
       <c r="D341" t="s">
-        <v>1288</v>
+        <v>1276</v>
       </c>
       <c r="E341">
         <v>260</v>
@@ -12788,16 +12779,16 @@
     </row>
     <row r="342" spans="1:7">
       <c r="A342" t="s">
-        <v>1289</v>
+        <v>1277</v>
       </c>
       <c r="B342" t="s">
-        <v>1290</v>
+        <v>1278</v>
       </c>
       <c r="C342" t="s">
-        <v>1291</v>
+        <v>1279</v>
       </c>
       <c r="D342" t="s">
-        <v>1292</v>
+        <v>1280</v>
       </c>
       <c r="E342">
         <v>355</v>
@@ -12811,16 +12802,16 @@
     </row>
     <row r="343" spans="1:7">
       <c r="A343" t="s">
-        <v>1293</v>
+        <v>1281</v>
       </c>
       <c r="B343" t="s">
-        <v>1294</v>
+        <v>1282</v>
       </c>
       <c r="C343" t="s">
-        <v>1295</v>
+        <v>1283</v>
       </c>
       <c r="D343" t="s">
-        <v>1296</v>
+        <v>1284</v>
       </c>
       <c r="E343">
         <v>335</v>
@@ -12834,16 +12825,16 @@
     </row>
     <row r="344" spans="1:7">
       <c r="A344" t="s">
-        <v>1297</v>
+        <v>1285</v>
       </c>
       <c r="B344" t="s">
-        <v>1298</v>
+        <v>1286</v>
       </c>
       <c r="C344" t="s">
-        <v>1299</v>
+        <v>1287</v>
       </c>
       <c r="D344" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="E344">
         <v>300</v>
@@ -12857,16 +12848,16 @@
     </row>
     <row r="345" spans="1:7">
       <c r="A345" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="B345" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="C345" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="D345" t="s">
-        <v>1304</v>
+        <v>1292</v>
       </c>
       <c r="E345">
         <v>348</v>
@@ -12880,16 +12871,16 @@
     </row>
     <row r="346" spans="1:7">
       <c r="A346" t="s">
-        <v>1305</v>
+        <v>1293</v>
       </c>
       <c r="B346" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="C346" t="s">
-        <v>1307</v>
+        <v>1295</v>
       </c>
       <c r="D346" t="s">
-        <v>1308</v>
+        <v>1296</v>
       </c>
       <c r="E346">
         <v>219</v>
@@ -12903,16 +12894,16 @@
     </row>
     <row r="347" spans="1:7">
       <c r="A347" t="s">
-        <v>1309</v>
+        <v>1297</v>
       </c>
       <c r="B347" t="s">
-        <v>1310</v>
+        <v>1298</v>
       </c>
       <c r="C347" t="s">
-        <v>1310</v>
+        <v>1298</v>
       </c>
       <c r="D347" t="s">
-        <v>1310</v>
+        <v>1298</v>
       </c>
       <c r="E347">
         <v>32</v>
@@ -12926,16 +12917,16 @@
     </row>
     <row r="348" spans="1:7">
       <c r="A348" t="s">
-        <v>1311</v>
+        <v>1299</v>
       </c>
       <c r="B348" t="s">
-        <v>1312</v>
+        <v>1300</v>
       </c>
       <c r="C348" t="s">
-        <v>1313</v>
+        <v>1301</v>
       </c>
       <c r="D348" t="s">
-        <v>1314</v>
+        <v>1302</v>
       </c>
       <c r="E348">
         <v>70</v>
@@ -12949,16 +12940,16 @@
     </row>
     <row r="349" spans="1:7">
       <c r="A349" t="s">
-        <v>1315</v>
+        <v>1303</v>
       </c>
       <c r="B349" t="s">
-        <v>1316</v>
+        <v>1304</v>
       </c>
       <c r="C349" t="s">
-        <v>1317</v>
+        <v>1305</v>
       </c>
       <c r="D349" t="s">
-        <v>1316</v>
+        <v>1304</v>
       </c>
       <c r="E349">
         <v>70</v>
@@ -12972,16 +12963,16 @@
     </row>
     <row r="350" spans="1:7">
       <c r="A350" t="s">
-        <v>1318</v>
+        <v>1306</v>
       </c>
       <c r="B350" t="s">
-        <v>1319</v>
+        <v>1307</v>
       </c>
       <c r="C350" t="s">
-        <v>1320</v>
+        <v>1308</v>
       </c>
       <c r="D350" t="s">
-        <v>1321</v>
+        <v>1309</v>
       </c>
       <c r="E350">
         <v>160</v>
@@ -12995,16 +12986,16 @@
     </row>
     <row r="351" spans="1:7">
       <c r="A351" t="s">
-        <v>1322</v>
+        <v>1310</v>
       </c>
       <c r="B351" t="s">
-        <v>1323</v>
+        <v>1311</v>
       </c>
       <c r="C351" t="s">
-        <v>1324</v>
+        <v>1312</v>
       </c>
       <c r="D351" t="s">
-        <v>1325</v>
+        <v>1313</v>
       </c>
       <c r="E351">
         <v>120</v>
@@ -13018,16 +13009,16 @@
     </row>
     <row r="352" spans="1:7">
       <c r="A352" t="s">
-        <v>1489</v>
+        <v>1461</v>
       </c>
       <c r="B352" t="s">
-        <v>1492</v>
+        <v>1464</v>
       </c>
       <c r="C352" t="s">
-        <v>1491</v>
+        <v>1463</v>
       </c>
       <c r="D352" t="s">
-        <v>1490</v>
+        <v>1462</v>
       </c>
       <c r="E352">
         <v>100</v>
@@ -13041,16 +13032,16 @@
     </row>
     <row r="353" spans="1:7">
       <c r="A353" t="s">
-        <v>1326</v>
+        <v>1314</v>
       </c>
       <c r="B353" t="s">
-        <v>1327</v>
+        <v>1315</v>
       </c>
       <c r="C353" t="s">
-        <v>1328</v>
+        <v>1316</v>
       </c>
       <c r="D353" t="s">
-        <v>1329</v>
+        <v>1317</v>
       </c>
       <c r="E353">
         <v>220</v>
@@ -13064,16 +13055,16 @@
     </row>
     <row r="354" spans="1:7">
       <c r="A354" t="s">
-        <v>1330</v>
+        <v>1318</v>
       </c>
       <c r="B354" t="s">
-        <v>1331</v>
+        <v>1319</v>
       </c>
       <c r="C354" t="s">
-        <v>1332</v>
+        <v>1320</v>
       </c>
       <c r="D354" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
       <c r="E354">
         <v>100</v>
@@ -13087,16 +13078,16 @@
     </row>
     <row r="355" spans="1:7">
       <c r="A355" t="s">
-        <v>1334</v>
+        <v>1322</v>
       </c>
       <c r="B355" t="s">
-        <v>1335</v>
+        <v>1323</v>
       </c>
       <c r="C355" t="s">
-        <v>1336</v>
+        <v>1324</v>
       </c>
       <c r="D355" t="s">
-        <v>1337</v>
+        <v>1325</v>
       </c>
       <c r="E355">
         <v>200</v>
@@ -13110,16 +13101,16 @@
     </row>
     <row r="356" spans="1:7">
       <c r="A356" t="s">
-        <v>1338</v>
+        <v>1326</v>
       </c>
       <c r="B356" t="s">
-        <v>1339</v>
+        <v>1327</v>
       </c>
       <c r="C356" t="s">
-        <v>1340</v>
+        <v>1328</v>
       </c>
       <c r="D356" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
       <c r="E356">
         <v>150</v>
@@ -13133,16 +13124,16 @@
     </row>
     <row r="357" spans="1:7">
       <c r="A357" t="s">
-        <v>1342</v>
+        <v>1330</v>
       </c>
       <c r="B357" t="s">
-        <v>1343</v>
+        <v>1331</v>
       </c>
       <c r="C357" t="s">
-        <v>1344</v>
+        <v>1332</v>
       </c>
       <c r="D357" t="s">
-        <v>1345</v>
+        <v>1333</v>
       </c>
       <c r="E357">
         <v>100</v>
@@ -13156,16 +13147,16 @@
     </row>
     <row r="358" spans="1:7">
       <c r="A358" t="s">
-        <v>1346</v>
+        <v>1334</v>
       </c>
       <c r="B358" t="s">
-        <v>1347</v>
+        <v>1335</v>
       </c>
       <c r="C358" t="s">
-        <v>1348</v>
+        <v>1336</v>
       </c>
       <c r="D358" t="s">
-        <v>1349</v>
+        <v>1337</v>
       </c>
       <c r="E358">
         <v>100</v>
@@ -13179,16 +13170,16 @@
     </row>
     <row r="359" spans="1:7">
       <c r="A359" t="s">
-        <v>1350</v>
+        <v>1338</v>
       </c>
       <c r="B359" t="s">
-        <v>1351</v>
+        <v>1339</v>
       </c>
       <c r="C359" t="s">
-        <v>1352</v>
+        <v>1340</v>
       </c>
       <c r="D359" t="s">
-        <v>1353</v>
+        <v>1341</v>
       </c>
       <c r="E359">
         <v>145</v>
@@ -13202,16 +13193,16 @@
     </row>
     <row r="360" spans="1:7">
       <c r="A360" t="s">
-        <v>1354</v>
+        <v>1342</v>
       </c>
       <c r="B360" t="s">
-        <v>1355</v>
+        <v>1343</v>
       </c>
       <c r="C360" t="s">
-        <v>1356</v>
+        <v>1344</v>
       </c>
       <c r="D360" t="s">
-        <v>1357</v>
+        <v>1345</v>
       </c>
       <c r="E360">
         <v>338</v>
@@ -13225,16 +13216,16 @@
     </row>
     <row r="361" spans="1:7">
       <c r="A361" t="s">
-        <v>1358</v>
+        <v>1346</v>
       </c>
       <c r="B361" t="s">
-        <v>1359</v>
+        <v>1347</v>
       </c>
       <c r="C361" t="s">
-        <v>1360</v>
+        <v>1348</v>
       </c>
       <c r="D361" t="s">
-        <v>1361</v>
+        <v>1349</v>
       </c>
       <c r="E361">
         <v>209</v>
@@ -13248,16 +13239,16 @@
     </row>
     <row r="362" spans="1:7">
       <c r="A362" t="s">
-        <v>1362</v>
+        <v>1350</v>
       </c>
       <c r="B362" t="s">
-        <v>1363</v>
+        <v>1351</v>
       </c>
       <c r="C362" t="s">
-        <v>1364</v>
+        <v>1352</v>
       </c>
       <c r="D362" t="s">
-        <v>1365</v>
+        <v>1353</v>
       </c>
       <c r="E362">
         <v>131</v>
@@ -13271,16 +13262,16 @@
     </row>
     <row r="363" spans="1:7" s="2" customFormat="1" ht="17.850000000000001" customHeight="1">
       <c r="A363" s="2" t="s">
-        <v>1497</v>
+        <v>1469</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>1499</v>
+        <v>1471</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>1500</v>
+        <v>1472</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>1501</v>
+        <v>1473</v>
       </c>
       <c r="E363" s="2">
         <v>42</v>
@@ -13294,39 +13285,39 @@
     </row>
     <row r="364" spans="1:7" s="2" customFormat="1" ht="16.7" customHeight="1">
       <c r="A364" s="2" t="s">
-        <v>1520</v>
+        <v>1501</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>1503</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="E364" s="2">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="F364" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G364" s="2">
-        <v>96</v>
+        <v>192</v>
       </c>
     </row>
     <row r="365" spans="1:7" s="2" customFormat="1" ht="15.55" customHeight="1">
       <c r="A365" s="2" t="s">
-        <v>1498</v>
+        <v>1470</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>1505</v>
+        <v>1474</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>1506</v>
+        <v>1475</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>1507</v>
+        <v>1476</v>
       </c>
       <c r="E365" s="2">
         <v>77</v>
@@ -13340,16 +13331,16 @@
     </row>
     <row r="366" spans="1:7">
       <c r="A366" t="s">
-        <v>1366</v>
+        <v>1354</v>
       </c>
       <c r="B366" t="s">
-        <v>1367</v>
+        <v>1355</v>
       </c>
       <c r="C366" t="s">
-        <v>1368</v>
+        <v>1356</v>
       </c>
       <c r="D366" t="s">
-        <v>1369</v>
+        <v>1357</v>
       </c>
       <c r="E366">
         <v>1</v>
@@ -13363,16 +13354,16 @@
     </row>
     <row r="367" spans="1:7">
       <c r="A367" t="s">
-        <v>1370</v>
+        <v>1358</v>
       </c>
       <c r="B367" t="s">
-        <v>1371</v>
+        <v>1359</v>
       </c>
       <c r="C367" t="s">
-        <v>1372</v>
+        <v>1360</v>
       </c>
       <c r="D367" t="s">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="E367">
         <v>0</v>
@@ -13386,16 +13377,16 @@
     </row>
     <row r="368" spans="1:7" ht="15">
       <c r="A368" t="s">
-        <v>1493</v>
+        <v>1465</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>1494</v>
+        <v>1466</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>1495</v>
+        <v>1467</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>1496</v>
+        <v>1468</v>
       </c>
       <c r="E368">
         <v>1</v>
@@ -13409,16 +13400,16 @@
     </row>
     <row r="369" spans="1:7">
       <c r="A369" t="s">
-        <v>1374</v>
+        <v>1362</v>
       </c>
       <c r="B369" t="s">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="C369" t="s">
-        <v>1376</v>
+        <v>1364</v>
       </c>
       <c r="D369" t="s">
-        <v>1377</v>
+        <v>1365</v>
       </c>
       <c r="E369">
         <v>1</v>
@@ -13432,39 +13423,39 @@
     </row>
     <row r="370" spans="1:7">
       <c r="A370" t="s">
-        <v>1378</v>
+        <v>1506</v>
       </c>
       <c r="B370" t="s">
-        <v>1379</v>
+        <v>1508</v>
       </c>
       <c r="C370" t="s">
-        <v>1380</v>
+        <v>1510</v>
       </c>
       <c r="D370" t="s">
-        <v>1381</v>
+        <v>1512</v>
       </c>
       <c r="E370">
-        <v>10.8</v>
+        <v>4.5</v>
       </c>
       <c r="F370">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G370">
-        <v>4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="371" spans="1:7">
       <c r="A371" t="s">
-        <v>1382</v>
+        <v>1507</v>
       </c>
       <c r="B371" t="s">
-        <v>1383</v>
+        <v>1509</v>
       </c>
       <c r="C371" t="s">
-        <v>1384</v>
+        <v>1511</v>
       </c>
       <c r="D371" t="s">
-        <v>1385</v>
+        <v>1513</v>
       </c>
       <c r="E371">
         <v>0</v>
@@ -13473,21 +13464,21 @@
         <v>0</v>
       </c>
       <c r="G371">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="372" spans="1:7">
       <c r="A372" t="s">
-        <v>1386</v>
+        <v>1366</v>
       </c>
       <c r="B372" t="s">
-        <v>1387</v>
+        <v>1367</v>
       </c>
       <c r="C372" t="s">
-        <v>1388</v>
+        <v>1368</v>
       </c>
       <c r="D372" t="s">
-        <v>1389</v>
+        <v>1369</v>
       </c>
       <c r="E372">
         <v>9</v>
@@ -13501,16 +13492,16 @@
     </row>
     <row r="373" spans="1:7">
       <c r="A373" t="s">
-        <v>1482</v>
+        <v>1454</v>
       </c>
       <c r="B373" t="s">
-        <v>1483</v>
+        <v>1455</v>
       </c>
       <c r="C373" t="s">
-        <v>1484</v>
+        <v>1456</v>
       </c>
       <c r="D373" t="s">
-        <v>1485</v>
+        <v>1457</v>
       </c>
       <c r="E373">
         <v>50</v>
@@ -13524,16 +13515,16 @@
     </row>
     <row r="374" spans="1:7">
       <c r="A374" t="s">
-        <v>1390</v>
+        <v>1370</v>
       </c>
       <c r="B374" t="s">
-        <v>1391</v>
+        <v>1371</v>
       </c>
       <c r="C374" t="s">
-        <v>1392</v>
+        <v>1372</v>
       </c>
       <c r="D374" t="s">
-        <v>1393</v>
+        <v>1373</v>
       </c>
       <c r="E374">
         <v>10</v>
@@ -13547,16 +13538,16 @@
     </row>
     <row r="375" spans="1:7">
       <c r="A375" t="s">
-        <v>1394</v>
+        <v>1374</v>
       </c>
       <c r="B375" t="s">
-        <v>1395</v>
+        <v>1375</v>
       </c>
       <c r="C375" t="s">
-        <v>1396</v>
+        <v>1376</v>
       </c>
       <c r="D375" t="s">
-        <v>1397</v>
+        <v>1377</v>
       </c>
       <c r="E375">
         <v>37</v>
@@ -13570,16 +13561,16 @@
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
-        <v>1398</v>
+        <v>1378</v>
       </c>
       <c r="B376" t="s">
-        <v>1399</v>
+        <v>1379</v>
       </c>
       <c r="C376" t="s">
-        <v>1400</v>
+        <v>1380</v>
       </c>
       <c r="D376" t="s">
-        <v>1401</v>
+        <v>1381</v>
       </c>
       <c r="E376">
         <v>400</v>
@@ -13593,16 +13584,16 @@
     </row>
     <row r="377" spans="1:7">
       <c r="A377" t="s">
-        <v>1402</v>
+        <v>1382</v>
       </c>
       <c r="B377" t="s">
-        <v>1403</v>
+        <v>1383</v>
       </c>
       <c r="C377" t="s">
-        <v>1404</v>
+        <v>1384</v>
       </c>
       <c r="D377" t="s">
-        <v>1405</v>
+        <v>1385</v>
       </c>
       <c r="E377">
         <v>549</v>
@@ -13616,346 +13607,323 @@
     </row>
     <row r="378" spans="1:7">
       <c r="A378" t="s">
-        <v>1479</v>
+        <v>1514</v>
       </c>
       <c r="B378" t="s">
-        <v>1406</v>
+        <v>1515</v>
       </c>
       <c r="C378" t="s">
-        <v>1481</v>
+        <v>1516</v>
       </c>
       <c r="D378" t="s">
-        <v>1480</v>
+        <v>1517</v>
       </c>
       <c r="E378">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="F378">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="G378">
-        <v>15</v>
+        <v>150</v>
       </c>
     </row>
     <row r="379" spans="1:7">
       <c r="A379" t="s">
-        <v>1407</v>
+        <v>1386</v>
       </c>
       <c r="B379" t="s">
-        <v>1408</v>
+        <v>1387</v>
       </c>
       <c r="C379" t="s">
-        <v>1409</v>
+        <v>1388</v>
       </c>
       <c r="D379" t="s">
-        <v>1410</v>
+        <v>1389</v>
       </c>
       <c r="E379">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="F379">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="G379">
-        <v>150</v>
+        <v>2</v>
       </c>
     </row>
     <row r="380" spans="1:7">
       <c r="A380" t="s">
-        <v>1411</v>
+        <v>1390</v>
       </c>
       <c r="B380" t="s">
-        <v>1412</v>
+        <v>1391</v>
       </c>
       <c r="C380" t="s">
-        <v>1413</v>
+        <v>1392</v>
       </c>
       <c r="D380" t="s">
-        <v>1414</v>
+        <v>1393</v>
       </c>
       <c r="E380">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="F380">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G380">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="381" spans="1:7">
       <c r="A381" t="s">
-        <v>1415</v>
+        <v>1394</v>
       </c>
       <c r="B381" t="s">
-        <v>1416</v>
+        <v>1395</v>
       </c>
       <c r="C381" t="s">
-        <v>1417</v>
+        <v>1396</v>
       </c>
       <c r="D381" t="s">
-        <v>1418</v>
+        <v>1397</v>
       </c>
       <c r="E381">
+        <v>78</v>
+      </c>
+      <c r="F381">
         <v>80</v>
       </c>
-      <c r="F381">
-        <v>35</v>
-      </c>
       <c r="G381">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="382" spans="1:7">
       <c r="A382" t="s">
-        <v>1419</v>
+        <v>1398</v>
       </c>
       <c r="B382" t="s">
-        <v>1420</v>
+        <v>1399</v>
       </c>
       <c r="C382" t="s">
-        <v>1421</v>
+        <v>1400</v>
       </c>
       <c r="D382" t="s">
-        <v>1422</v>
+        <v>1401</v>
       </c>
       <c r="E382">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="F382">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G382">
-        <v>39</v>
+        <v>91</v>
       </c>
     </row>
     <row r="383" spans="1:7">
       <c r="A383" t="s">
-        <v>1423</v>
+        <v>1402</v>
       </c>
       <c r="B383" t="s">
-        <v>1424</v>
+        <v>1403</v>
       </c>
       <c r="C383" t="s">
-        <v>1425</v>
+        <v>1404</v>
       </c>
       <c r="D383" t="s">
-        <v>1426</v>
+        <v>1405</v>
       </c>
       <c r="E383">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="F383">
         <v>0</v>
       </c>
       <c r="G383">
-        <v>91</v>
+        <v>920</v>
       </c>
     </row>
     <row r="384" spans="1:7">
       <c r="A384" t="s">
-        <v>1427</v>
+        <v>1406</v>
       </c>
       <c r="B384" t="s">
-        <v>1428</v>
+        <v>1407</v>
       </c>
       <c r="C384" t="s">
-        <v>1429</v>
+        <v>1408</v>
       </c>
       <c r="D384" t="s">
-        <v>1430</v>
+        <v>1409</v>
       </c>
       <c r="E384">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="F384">
         <v>0</v>
       </c>
       <c r="G384">
-        <v>219</v>
+        <v>870</v>
       </c>
     </row>
     <row r="385" spans="1:7">
       <c r="A385" t="s">
-        <v>1431</v>
+        <v>1482</v>
       </c>
       <c r="B385" t="s">
-        <v>1432</v>
+        <v>1485</v>
       </c>
       <c r="C385" t="s">
-        <v>1433</v>
+        <v>1484</v>
       </c>
       <c r="D385" t="s">
-        <v>1434</v>
+        <v>1483</v>
       </c>
       <c r="E385">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F385">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G385">
-        <v>119</v>
+        <v>4</v>
       </c>
     </row>
     <row r="386" spans="1:7">
       <c r="A386" t="s">
-        <v>1516</v>
+        <v>1410</v>
       </c>
       <c r="B386" t="s">
-        <v>1519</v>
+        <v>1411</v>
       </c>
       <c r="C386" t="s">
-        <v>1518</v>
+        <v>1412</v>
       </c>
       <c r="D386" t="s">
-        <v>1517</v>
+        <v>1413</v>
       </c>
       <c r="E386">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F386">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G386">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="387" spans="1:7">
       <c r="A387" t="s">
-        <v>1435</v>
+        <v>1414</v>
       </c>
       <c r="B387" t="s">
-        <v>1436</v>
+        <v>1415</v>
       </c>
       <c r="C387" t="s">
-        <v>1437</v>
+        <v>1416</v>
       </c>
       <c r="D387" t="s">
-        <v>1438</v>
+        <v>1417</v>
       </c>
       <c r="E387">
+        <v>27</v>
+      </c>
+      <c r="F387">
+        <v>20</v>
+      </c>
+      <c r="G387">
         <v>10</v>
-      </c>
-      <c r="F387">
-        <v>3</v>
-      </c>
-      <c r="G387">
-        <v>14</v>
       </c>
     </row>
     <row r="388" spans="1:7">
       <c r="A388" t="s">
-        <v>1439</v>
+        <v>1418</v>
       </c>
       <c r="B388" t="s">
-        <v>1440</v>
+        <v>1419</v>
       </c>
       <c r="C388" t="s">
-        <v>1441</v>
+        <v>1420</v>
       </c>
       <c r="D388" t="s">
-        <v>1442</v>
+        <v>1421</v>
       </c>
       <c r="E388">
         <v>27</v>
       </c>
       <c r="F388">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G388">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="389" spans="1:7">
       <c r="A389" t="s">
-        <v>1443</v>
+        <v>1422</v>
       </c>
       <c r="B389" t="s">
-        <v>1444</v>
+        <v>1423</v>
       </c>
       <c r="C389" t="s">
-        <v>1445</v>
+        <v>1424</v>
       </c>
       <c r="D389" t="s">
-        <v>1446</v>
+        <v>1425</v>
       </c>
       <c r="E389">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="F389">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G389">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390" spans="1:7">
       <c r="A390" t="s">
-        <v>1447</v>
+        <v>1426</v>
       </c>
       <c r="B390" t="s">
-        <v>1448</v>
+        <v>1427</v>
       </c>
       <c r="C390" t="s">
-        <v>1449</v>
+        <v>1428</v>
       </c>
       <c r="D390" t="s">
-        <v>1450</v>
+        <v>1429</v>
       </c>
       <c r="E390">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="F390">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G390">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="391" spans="1:7">
       <c r="A391" t="s">
-        <v>1451</v>
+        <v>1430</v>
       </c>
       <c r="B391" t="s">
-        <v>1452</v>
+        <v>1431</v>
       </c>
       <c r="C391" t="s">
-        <v>1453</v>
+        <v>1432</v>
       </c>
       <c r="D391" t="s">
-        <v>1454</v>
+        <v>1433</v>
       </c>
       <c r="E391">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="F391">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G391">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="392" spans="1:7">
-      <c r="A392" t="s">
-        <v>1455</v>
-      </c>
-      <c r="B392" t="s">
-        <v>1456</v>
-      </c>
-      <c r="C392" t="s">
-        <v>1457</v>
-      </c>
-      <c r="D392" t="s">
-        <v>1458</v>
-      </c>
-      <c r="E392">
-        <v>0</v>
-      </c>
-      <c r="F392">
-        <v>0</v>
-      </c>
-      <c r="G392">
         <v>0</v>
       </c>
     </row>

--- a/KPH-AI-GLOBAL.xlsx
+++ b/KPH-AI-GLOBAL.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="1518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="1522">
   <si>
     <t>Namirnica</t>
   </si>
@@ -2947,9 +2947,6 @@
     <t>Pfirsichblüte</t>
   </si>
   <si>
-    <t>Marelica susena</t>
-  </si>
-  <si>
     <t>Dried apricot</t>
   </si>
   <si>
@@ -2959,18 +2956,6 @@
     <t>Getrocknete Aprikose</t>
   </si>
   <si>
-    <t>Marelica sveza</t>
-  </si>
-  <si>
-    <t>Apricot connection</t>
-  </si>
-  <si>
-    <t>Conexión de albaricoque</t>
-  </si>
-  <si>
-    <t>Aprikosenverbindung</t>
-  </si>
-  <si>
     <t>Sljiva suva</t>
   </si>
   <si>
@@ -3199,9 +3184,6 @@
     <t>Pfirsichsaft</t>
   </si>
   <si>
-    <t>Marelica sok</t>
-  </si>
-  <si>
     <t>Apricot juice</t>
   </si>
   <si>
@@ -3305,9 +3287,6 @@
   </si>
   <si>
     <t>Birnenkompott</t>
-  </si>
-  <si>
-    <t>Kompot Marelica</t>
   </si>
   <si>
     <t>Apricot compote</t>
@@ -4571,6 +4550,39 @@
   </si>
   <si>
     <t xml:space="preserve">Milch für Kaffee </t>
+  </si>
+  <si>
+    <t>Fresh apricot</t>
+  </si>
+  <si>
+    <t>Frische Aprikose</t>
+  </si>
+  <si>
+    <t>Albaricoque fresco</t>
+  </si>
+  <si>
+    <t>Kajsija Marelica sveza</t>
+  </si>
+  <si>
+    <t>Kajsija marelica susena</t>
+  </si>
+  <si>
+    <t>Limeta</t>
+  </si>
+  <si>
+    <t>Lime</t>
+  </si>
+  <si>
+    <t>Kalk</t>
+  </si>
+  <si>
+    <t>cal</t>
+  </si>
+  <si>
+    <t>Kajsija Marelica sok</t>
+  </si>
+  <si>
+    <t>Kompot kajsija Marelica</t>
   </si>
 </sst>
 </file>
@@ -4928,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G391"/>
+  <dimension ref="A1:G392"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="39.19921875" customWidth="1"/>
@@ -5974,16 +5986,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="B46" t="s">
-        <v>1442</v>
+        <v>1435</v>
       </c>
       <c r="C46" t="s">
-        <v>1443</v>
+        <v>1436</v>
       </c>
       <c r="D46" t="s">
-        <v>1444</v>
+        <v>1437</v>
       </c>
       <c r="E46">
         <v>173</v>
@@ -6089,16 +6101,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>1438</v>
+        <v>1431</v>
       </c>
       <c r="B51" t="s">
-        <v>1439</v>
+        <v>1432</v>
       </c>
       <c r="C51" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
       <c r="D51" t="s">
-        <v>1439</v>
+        <v>1432</v>
       </c>
       <c r="E51">
         <v>230</v>
@@ -7147,7 +7159,7 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>1445</v>
+        <v>1438</v>
       </c>
       <c r="B97" t="s">
         <v>374</v>
@@ -7561,7 +7573,7 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>1446</v>
+        <v>1439</v>
       </c>
       <c r="B115" t="s">
         <v>442</v>
@@ -8021,16 +8033,16 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>1497</v>
+        <v>1490</v>
       </c>
       <c r="B135" t="s">
-        <v>1498</v>
+        <v>1491</v>
       </c>
       <c r="C135" t="s">
-        <v>1499</v>
+        <v>1492</v>
       </c>
       <c r="D135" t="s">
-        <v>1500</v>
+        <v>1493</v>
       </c>
       <c r="E135">
         <v>250</v>
@@ -8044,7 +8056,7 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>1505</v>
+        <v>1498</v>
       </c>
       <c r="B136" t="s">
         <v>521</v>
@@ -8228,16 +8240,16 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>1477</v>
+        <v>1470</v>
       </c>
       <c r="B144" t="s">
-        <v>1478</v>
+        <v>1471</v>
       </c>
       <c r="C144" t="s">
-        <v>1479</v>
+        <v>1472</v>
       </c>
       <c r="D144" t="s">
-        <v>1480</v>
+        <v>1473</v>
       </c>
       <c r="E144">
         <v>130</v>
@@ -9585,16 +9597,16 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>1486</v>
+        <v>1479</v>
       </c>
       <c r="B203" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="C203" t="s">
-        <v>1488</v>
+        <v>1481</v>
       </c>
       <c r="D203" t="s">
-        <v>1489</v>
+        <v>1482</v>
       </c>
       <c r="E203">
         <v>84</v>
@@ -9608,16 +9620,16 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>1490</v>
+        <v>1483</v>
       </c>
       <c r="B204" t="s">
-        <v>1491</v>
+        <v>1484</v>
       </c>
       <c r="C204" t="s">
-        <v>1492</v>
+        <v>1485</v>
       </c>
       <c r="D204" t="s">
-        <v>1493</v>
+        <v>1486</v>
       </c>
       <c r="E204">
         <v>72</v>
@@ -9631,16 +9643,16 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>1496</v>
+        <v>1489</v>
       </c>
       <c r="B205" t="s">
-        <v>1481</v>
+        <v>1474</v>
       </c>
       <c r="C205" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
       <c r="D205" t="s">
-        <v>1494</v>
+        <v>1487</v>
       </c>
       <c r="E205">
         <v>8</v>
@@ -9930,16 +9942,16 @@
     </row>
     <row r="218" spans="1:7">
       <c r="A218" t="s">
-        <v>1458</v>
+        <v>1451</v>
       </c>
       <c r="B218" t="s">
-        <v>1459</v>
+        <v>1452</v>
       </c>
       <c r="C218" t="s">
-        <v>1459</v>
+        <v>1452</v>
       </c>
       <c r="D218" t="s">
-        <v>1460</v>
+        <v>1453</v>
       </c>
       <c r="E218">
         <v>320</v>
@@ -10482,16 +10494,16 @@
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
-        <v>1447</v>
+        <v>1440</v>
       </c>
       <c r="B242" t="s">
-        <v>1448</v>
+        <v>1441</v>
       </c>
       <c r="C242" t="s">
-        <v>1449</v>
+        <v>1442</v>
       </c>
       <c r="D242" t="s">
-        <v>1448</v>
+        <v>1441</v>
       </c>
       <c r="E242">
         <v>277</v>
@@ -10528,22 +10540,22 @@
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
-        <v>919</v>
+        <v>1516</v>
       </c>
       <c r="B244" t="s">
-        <v>920</v>
+        <v>1517</v>
       </c>
       <c r="C244" t="s">
-        <v>919</v>
+        <v>1518</v>
       </c>
       <c r="D244" t="s">
-        <v>921</v>
+        <v>1519</v>
       </c>
       <c r="E244">
-        <v>210</v>
+        <v>102</v>
       </c>
       <c r="F244">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G244">
         <v>2</v>
@@ -10551,68 +10563,68 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B245" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="C245" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="D245" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="E245">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="F245">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G245">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246" spans="1:7">
       <c r="A246" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B246" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="C246" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="D246" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E246">
-        <v>177</v>
+        <v>260</v>
       </c>
       <c r="F246">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G246">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="247" spans="1:7">
       <c r="A247" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B247" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="C247" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="D247" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="E247">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="F247">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G247">
         <v>1</v>
@@ -10620,68 +10632,68 @@
     </row>
     <row r="248" spans="1:7">
       <c r="A248" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B248" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C248" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="D248" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="E248">
-        <v>782</v>
+        <v>81</v>
       </c>
       <c r="F248">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="G248">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:7">
       <c r="A249" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="B249" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="C249" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="D249" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="E249">
-        <v>192</v>
+        <v>782</v>
       </c>
       <c r="F249">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="G249">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="250" spans="1:7">
       <c r="A250" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="B250" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="C250" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="D250" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="E250">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="F250">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G250">
         <v>2</v>
@@ -10689,111 +10701,111 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B251" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C251" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="D251" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="E251">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="F251">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G251">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252" spans="1:7">
       <c r="A252" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="B252" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="C252" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="D252" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="E252">
-        <v>310</v>
+        <v>170</v>
       </c>
       <c r="F252">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G252">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:7">
       <c r="A253" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B253" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="C253" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="D253" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="E253">
-        <v>238</v>
+        <v>310</v>
       </c>
       <c r="F253">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G253">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254" spans="1:7">
       <c r="A254" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="B254" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="C254" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="D254" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="E254">
-        <v>114</v>
+        <v>238</v>
+      </c>
+      <c r="F254">
+        <v>27</v>
       </c>
       <c r="G254">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:7">
       <c r="A255" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="B255" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C255" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="D255" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="E255">
-        <v>144</v>
-      </c>
-      <c r="F255">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G255">
         <v>3</v>
@@ -10801,229 +10813,229 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="B256" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="C256" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="D256" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="E256">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="F256">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G256">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257" spans="1:7">
       <c r="A257" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B257" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="C257" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="D257" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="E257">
-        <v>1340</v>
+        <v>126</v>
       </c>
       <c r="F257">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="G257">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="258" spans="1:7">
       <c r="A258" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B258" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="C258" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="D258" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="E258">
-        <v>205</v>
+        <v>1340</v>
       </c>
       <c r="F258">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="G258">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="259" spans="1:7">
       <c r="A259" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="B259" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="C259" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="D259" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="E259">
-        <v>1370</v>
+        <v>205</v>
       </c>
       <c r="F259">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="G259">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:7">
       <c r="A260" t="s">
-        <v>981</v>
+        <v>1514</v>
       </c>
       <c r="B260" t="s">
-        <v>982</v>
+        <v>1511</v>
       </c>
       <c r="C260" t="s">
-        <v>983</v>
+        <v>1512</v>
       </c>
       <c r="D260" t="s">
-        <v>984</v>
+        <v>1513</v>
       </c>
       <c r="E260">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="F260">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G260">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:7">
       <c r="A261" t="s">
-        <v>985</v>
+        <v>1515</v>
       </c>
       <c r="B261" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="C261" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="D261" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="E261">
-        <v>860</v>
+        <v>1370</v>
       </c>
       <c r="F261">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G261">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="262" spans="1:7">
       <c r="A262" t="s">
-        <v>989</v>
+        <v>980</v>
       </c>
       <c r="B262" t="s">
-        <v>990</v>
+        <v>981</v>
       </c>
       <c r="C262" t="s">
-        <v>991</v>
+        <v>982</v>
       </c>
       <c r="D262" t="s">
-        <v>992</v>
+        <v>983</v>
       </c>
       <c r="E262">
-        <v>221</v>
+        <v>860</v>
       </c>
       <c r="F262">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="G262">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="263" spans="1:7">
       <c r="A263" t="s">
-        <v>993</v>
+        <v>984</v>
       </c>
       <c r="B263" t="s">
-        <v>994</v>
+        <v>985</v>
       </c>
       <c r="C263" t="s">
-        <v>995</v>
+        <v>986</v>
       </c>
       <c r="D263" t="s">
-        <v>996</v>
+        <v>987</v>
       </c>
       <c r="E263">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="F263">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G263">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="264" spans="1:7">
       <c r="A264" t="s">
-        <v>997</v>
+        <v>988</v>
       </c>
       <c r="B264" t="s">
-        <v>998</v>
+        <v>989</v>
       </c>
       <c r="C264" t="s">
-        <v>999</v>
+        <v>990</v>
       </c>
       <c r="D264" t="s">
-        <v>1000</v>
+        <v>991</v>
       </c>
       <c r="E264">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="F264">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G264">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="265" spans="1:7">
       <c r="A265" t="s">
-        <v>1001</v>
+        <v>992</v>
       </c>
       <c r="B265" t="s">
-        <v>1002</v>
+        <v>993</v>
       </c>
       <c r="C265" t="s">
-        <v>1003</v>
+        <v>994</v>
       </c>
       <c r="D265" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="E265">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="F265">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G265">
         <v>2</v>
@@ -11031,229 +11043,229 @@
     </row>
     <row r="266" spans="1:7">
       <c r="A266" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="B266" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="C266" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="D266" t="s">
-        <v>1005</v>
+        <v>996</v>
       </c>
       <c r="E266">
-        <v>503</v>
+        <v>173</v>
       </c>
       <c r="F266">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="G266">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267" spans="1:7">
       <c r="A267" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="B267" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="C267" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="D267" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="E267">
-        <v>393</v>
+        <v>503</v>
       </c>
       <c r="F267">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G267">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268" spans="1:7">
       <c r="A268" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="B268" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="C268" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="D268" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="E268">
-        <v>295</v>
+        <v>393</v>
       </c>
       <c r="F268">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G268">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:7">
       <c r="A269" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="B269" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="C269" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="D269" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="E269">
-        <v>190</v>
+        <v>295</v>
       </c>
       <c r="F269">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G269">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="270" spans="1:7">
       <c r="A270" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="B270" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="C270" t="s">
-        <v>1015</v>
+        <v>1007</v>
       </c>
       <c r="D270" t="s">
-        <v>1016</v>
+        <v>1006</v>
       </c>
       <c r="E270">
-        <v>330</v>
+        <v>190</v>
       </c>
       <c r="F270">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G270">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="271" spans="1:7">
       <c r="A271" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
       <c r="B271" t="s">
-        <v>1018</v>
+        <v>1009</v>
       </c>
       <c r="C271" t="s">
-        <v>1019</v>
+        <v>1010</v>
       </c>
       <c r="D271" t="s">
-        <v>1020</v>
+        <v>1011</v>
       </c>
       <c r="E271">
-        <v>158</v>
+        <v>330</v>
       </c>
       <c r="F271">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G271">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="272" spans="1:7">
       <c r="A272" t="s">
-        <v>1021</v>
+        <v>1012</v>
       </c>
       <c r="B272" t="s">
-        <v>1022</v>
+        <v>1013</v>
       </c>
       <c r="C272" t="s">
-        <v>1023</v>
+        <v>1014</v>
       </c>
       <c r="D272" t="s">
-        <v>1024</v>
+        <v>1015</v>
       </c>
       <c r="E272">
-        <v>240</v>
+        <v>158</v>
       </c>
       <c r="F272">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G272">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
-        <v>1025</v>
+        <v>1016</v>
       </c>
       <c r="B273" t="s">
-        <v>1026</v>
+        <v>1017</v>
       </c>
       <c r="C273" t="s">
-        <v>1027</v>
+        <v>1018</v>
       </c>
       <c r="D273" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
       <c r="E273">
-        <v>850</v>
+        <v>240</v>
       </c>
       <c r="F273">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="G273">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>1029</v>
+        <v>1020</v>
       </c>
       <c r="B274" t="s">
-        <v>1030</v>
+        <v>1021</v>
       </c>
       <c r="C274" t="s">
-        <v>1031</v>
+        <v>1022</v>
       </c>
       <c r="D274" t="s">
-        <v>1032</v>
+        <v>1023</v>
       </c>
       <c r="E274">
-        <v>140</v>
+        <v>850</v>
       </c>
       <c r="F274">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="G274">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>1033</v>
+        <v>1024</v>
       </c>
       <c r="B275" t="s">
-        <v>1034</v>
+        <v>1025</v>
       </c>
       <c r="C275" t="s">
-        <v>1035</v>
+        <v>1026</v>
       </c>
       <c r="D275" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
       <c r="E275">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="F275">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G275">
         <v>1</v>
@@ -11261,226 +11273,226 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="B276" t="s">
-        <v>1038</v>
+        <v>1029</v>
       </c>
       <c r="C276" t="s">
-        <v>1039</v>
+        <v>1030</v>
       </c>
       <c r="D276" t="s">
-        <v>1040</v>
+        <v>1031</v>
       </c>
       <c r="E276">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F276">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G276">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>1041</v>
+        <v>1032</v>
       </c>
       <c r="B277" t="s">
-        <v>1042</v>
+        <v>1033</v>
       </c>
       <c r="C277" t="s">
-        <v>1043</v>
+        <v>1034</v>
       </c>
       <c r="D277" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="E277">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="F277">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G277">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278" spans="1:7">
       <c r="A278" t="s">
-        <v>1045</v>
+        <v>1036</v>
       </c>
       <c r="B278" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="C278" t="s">
-        <v>1047</v>
+        <v>1038</v>
       </c>
       <c r="D278" t="s">
-        <v>1048</v>
+        <v>1039</v>
       </c>
       <c r="E278">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F278">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G278">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="279" spans="1:7">
       <c r="A279" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="B279" t="s">
-        <v>1050</v>
+        <v>1041</v>
       </c>
       <c r="C279" t="s">
-        <v>1051</v>
+        <v>1042</v>
       </c>
       <c r="D279" t="s">
-        <v>1052</v>
+        <v>1043</v>
       </c>
       <c r="E279">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F279">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G279">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>1053</v>
+        <v>1044</v>
       </c>
       <c r="B280" t="s">
-        <v>1054</v>
+        <v>1045</v>
       </c>
       <c r="C280" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
       <c r="D280" t="s">
-        <v>1056</v>
+        <v>1047</v>
       </c>
       <c r="E280">
-        <v>33</v>
+        <v>200</v>
       </c>
       <c r="F280">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G280">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>1057</v>
+        <v>1048</v>
       </c>
       <c r="B281" t="s">
-        <v>1058</v>
+        <v>1049</v>
       </c>
       <c r="C281" t="s">
-        <v>1059</v>
+        <v>1050</v>
       </c>
       <c r="D281" t="s">
-        <v>1060</v>
+        <v>1051</v>
       </c>
       <c r="E281">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="F281">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G281">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>1061</v>
+        <v>1052</v>
       </c>
       <c r="B282" t="s">
-        <v>1062</v>
+        <v>1053</v>
       </c>
       <c r="C282" t="s">
-        <v>1063</v>
+        <v>1054</v>
       </c>
       <c r="D282" t="s">
-        <v>1064</v>
+        <v>1055</v>
       </c>
       <c r="E282">
-        <v>362</v>
+        <v>78</v>
       </c>
       <c r="F282">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G282">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>1065</v>
+        <v>1520</v>
       </c>
       <c r="B283" t="s">
-        <v>1066</v>
+        <v>1056</v>
       </c>
       <c r="C283" t="s">
-        <v>1067</v>
+        <v>1057</v>
       </c>
       <c r="D283" t="s">
-        <v>1068</v>
+        <v>1058</v>
       </c>
       <c r="E283">
-        <v>50</v>
+        <v>362</v>
       </c>
       <c r="F283">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G283">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>1069</v>
+        <v>1059</v>
       </c>
       <c r="B284" t="s">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="C284" t="s">
-        <v>1071</v>
+        <v>1061</v>
       </c>
       <c r="D284" t="s">
-        <v>1072</v>
+        <v>1062</v>
       </c>
       <c r="E284">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F284">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G284">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>1073</v>
+        <v>1063</v>
       </c>
       <c r="B285" t="s">
-        <v>1074</v>
+        <v>1064</v>
       </c>
       <c r="C285" t="s">
-        <v>1075</v>
+        <v>1065</v>
       </c>
       <c r="D285" t="s">
-        <v>1076</v>
+        <v>1066</v>
       </c>
       <c r="E285">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F285">
         <v>10</v>
@@ -11491,22 +11503,22 @@
     </row>
     <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>1077</v>
+        <v>1067</v>
       </c>
       <c r="B286" t="s">
-        <v>1078</v>
+        <v>1068</v>
       </c>
       <c r="C286" t="s">
-        <v>1079</v>
+        <v>1069</v>
       </c>
       <c r="D286" t="s">
-        <v>1080</v>
+        <v>1070</v>
       </c>
       <c r="E286">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F286">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G286">
         <v>1</v>
@@ -11514,22 +11526,22 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" t="s">
-        <v>1081</v>
+        <v>1071</v>
       </c>
       <c r="B287" t="s">
-        <v>1082</v>
+        <v>1072</v>
       </c>
       <c r="C287" t="s">
-        <v>1083</v>
+        <v>1073</v>
       </c>
       <c r="D287" t="s">
-        <v>1084</v>
+        <v>1074</v>
       </c>
       <c r="E287">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="F287">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G287">
         <v>1</v>
@@ -11537,22 +11549,22 @@
     </row>
     <row r="288" spans="1:7">
       <c r="A288" t="s">
-        <v>1085</v>
+        <v>1075</v>
       </c>
       <c r="B288" t="s">
-        <v>1086</v>
+        <v>1076</v>
       </c>
       <c r="C288" t="s">
-        <v>1087</v>
+        <v>1077</v>
       </c>
       <c r="D288" t="s">
-        <v>1088</v>
+        <v>1078</v>
       </c>
       <c r="E288">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="F288">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G288">
         <v>1</v>
@@ -11560,22 +11572,22 @@
     </row>
     <row r="289" spans="1:7">
       <c r="A289" t="s">
-        <v>1089</v>
+        <v>1079</v>
       </c>
       <c r="B289" t="s">
-        <v>1090</v>
+        <v>1080</v>
       </c>
       <c r="C289" t="s">
-        <v>1091</v>
+        <v>1081</v>
       </c>
       <c r="D289" t="s">
-        <v>1092</v>
+        <v>1082</v>
       </c>
       <c r="E289">
-        <v>150</v>
+        <v>94</v>
       </c>
       <c r="F289">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G289">
         <v>1</v>
@@ -11583,22 +11595,22 @@
     </row>
     <row r="290" spans="1:7">
       <c r="A290" t="s">
-        <v>1093</v>
+        <v>1083</v>
       </c>
       <c r="B290" t="s">
-        <v>1094</v>
+        <v>1084</v>
       </c>
       <c r="C290" t="s">
-        <v>1095</v>
+        <v>1085</v>
       </c>
       <c r="D290" t="s">
-        <v>1096</v>
+        <v>1086</v>
       </c>
       <c r="E290">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="F290">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G290">
         <v>1</v>
@@ -11606,22 +11618,22 @@
     </row>
     <row r="291" spans="1:7">
       <c r="A291" t="s">
-        <v>1097</v>
+        <v>1087</v>
       </c>
       <c r="B291" t="s">
-        <v>1098</v>
+        <v>1088</v>
       </c>
       <c r="C291" t="s">
-        <v>1099</v>
+        <v>1089</v>
       </c>
       <c r="D291" t="s">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="E291">
-        <v>260</v>
+        <v>90</v>
       </c>
       <c r="F291">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G291">
         <v>1</v>
@@ -11629,114 +11641,114 @@
     </row>
     <row r="292" spans="1:7">
       <c r="A292" t="s">
-        <v>1101</v>
+        <v>1521</v>
       </c>
       <c r="B292" t="s">
-        <v>1102</v>
+        <v>1091</v>
       </c>
       <c r="C292" t="s">
-        <v>1103</v>
+        <v>1092</v>
       </c>
       <c r="D292" t="s">
-        <v>1104</v>
+        <v>1093</v>
       </c>
       <c r="E292">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="F292">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G292">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293" spans="1:7">
       <c r="A293" t="s">
-        <v>1105</v>
+        <v>1094</v>
       </c>
       <c r="B293" t="s">
-        <v>1106</v>
+        <v>1095</v>
       </c>
       <c r="C293" t="s">
-        <v>1107</v>
+        <v>1096</v>
       </c>
       <c r="D293" t="s">
-        <v>1108</v>
+        <v>1097</v>
       </c>
       <c r="E293">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="F293">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G293">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:7">
       <c r="A294" t="s">
-        <v>1109</v>
+        <v>1098</v>
       </c>
       <c r="B294" t="s">
-        <v>1110</v>
+        <v>1099</v>
       </c>
       <c r="C294" t="s">
-        <v>1111</v>
+        <v>1100</v>
       </c>
       <c r="D294" t="s">
-        <v>1112</v>
+        <v>1101</v>
       </c>
       <c r="E294">
-        <v>407</v>
+        <v>125</v>
       </c>
       <c r="F294">
-        <v>152</v>
+        <v>15</v>
       </c>
       <c r="G294">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="295" spans="1:7">
       <c r="A295" t="s">
-        <v>1113</v>
+        <v>1102</v>
       </c>
       <c r="B295" t="s">
-        <v>1114</v>
+        <v>1103</v>
       </c>
       <c r="C295" t="s">
-        <v>1115</v>
+        <v>1104</v>
       </c>
       <c r="D295" t="s">
-        <v>1116</v>
+        <v>1105</v>
       </c>
       <c r="E295">
-        <v>45</v>
+        <v>407</v>
       </c>
       <c r="F295">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="G295">
-        <v>50</v>
+        <v>107</v>
       </c>
     </row>
     <row r="296" spans="1:7">
       <c r="A296" t="s">
-        <v>1117</v>
+        <v>1106</v>
       </c>
       <c r="B296" t="s">
-        <v>942</v>
+        <v>1107</v>
       </c>
       <c r="C296" t="s">
-        <v>943</v>
+        <v>1108</v>
       </c>
       <c r="D296" t="s">
-        <v>944</v>
+        <v>1109</v>
       </c>
       <c r="E296">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="F296">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G296">
         <v>50</v>
@@ -11744,275 +11756,275 @@
     </row>
     <row r="297" spans="1:7">
       <c r="A297" t="s">
-        <v>1118</v>
+        <v>1110</v>
       </c>
       <c r="B297" t="s">
-        <v>1119</v>
+        <v>942</v>
       </c>
       <c r="C297" t="s">
-        <v>1120</v>
+        <v>943</v>
       </c>
       <c r="D297" t="s">
-        <v>1121</v>
+        <v>944</v>
       </c>
       <c r="E297">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F297">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G297">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="298" spans="1:7">
       <c r="A298" t="s">
-        <v>1122</v>
+        <v>1111</v>
       </c>
       <c r="B298" t="s">
-        <v>1123</v>
+        <v>1112</v>
       </c>
       <c r="C298" t="s">
-        <v>1124</v>
+        <v>1113</v>
       </c>
       <c r="D298" t="s">
-        <v>1125</v>
+        <v>1114</v>
       </c>
       <c r="E298">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F298">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G298">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>1126</v>
+        <v>1115</v>
       </c>
       <c r="B299" t="s">
-        <v>1127</v>
+        <v>1116</v>
       </c>
       <c r="C299" t="s">
-        <v>1128</v>
+        <v>1117</v>
       </c>
       <c r="D299" t="s">
-        <v>1129</v>
+        <v>1118</v>
       </c>
       <c r="E299">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="F299">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G299">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="300" spans="1:7">
       <c r="A300" t="s">
-        <v>1130</v>
+        <v>1119</v>
       </c>
       <c r="B300" t="s">
-        <v>1131</v>
+        <v>1120</v>
       </c>
       <c r="C300" t="s">
-        <v>1132</v>
+        <v>1121</v>
       </c>
       <c r="D300" t="s">
-        <v>1133</v>
+        <v>1122</v>
       </c>
       <c r="E300">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="F300">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G300">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="301" spans="1:7">
       <c r="A301" t="s">
-        <v>1134</v>
+        <v>1123</v>
       </c>
       <c r="B301" t="s">
-        <v>1135</v>
+        <v>1124</v>
       </c>
       <c r="C301" t="s">
-        <v>1136</v>
+        <v>1125</v>
       </c>
       <c r="D301" t="s">
-        <v>1137</v>
+        <v>1126</v>
       </c>
       <c r="E301">
-        <v>705</v>
+        <v>44</v>
       </c>
       <c r="F301">
-        <v>481</v>
+        <v>13</v>
       </c>
       <c r="G301">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="302" spans="1:7">
       <c r="A302" t="s">
-        <v>1138</v>
+        <v>1127</v>
       </c>
       <c r="B302" t="s">
-        <v>1139</v>
+        <v>1128</v>
       </c>
       <c r="C302" t="s">
-        <v>1140</v>
+        <v>1129</v>
       </c>
       <c r="D302" t="s">
-        <v>1141</v>
+        <v>1130</v>
       </c>
       <c r="E302">
-        <v>592</v>
+        <v>705</v>
       </c>
       <c r="F302">
-        <v>107</v>
+        <v>481</v>
       </c>
       <c r="G302">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="303" spans="1:7">
       <c r="A303" t="s">
-        <v>1142</v>
+        <v>1131</v>
       </c>
       <c r="B303" t="s">
-        <v>1143</v>
+        <v>1132</v>
       </c>
       <c r="C303" t="s">
-        <v>1144</v>
+        <v>1133</v>
       </c>
       <c r="D303" t="s">
-        <v>1145</v>
+        <v>1134</v>
       </c>
       <c r="E303">
-        <v>500</v>
+        <v>592</v>
       </c>
       <c r="F303">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="G303">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304" t="s">
-        <v>1146</v>
+        <v>1135</v>
       </c>
       <c r="B304" t="s">
-        <v>1147</v>
+        <v>1136</v>
       </c>
       <c r="C304" t="s">
-        <v>1148</v>
+        <v>1137</v>
       </c>
       <c r="D304" t="s">
-        <v>1149</v>
+        <v>1138</v>
       </c>
       <c r="E304">
-        <v>777</v>
+        <v>500</v>
       </c>
       <c r="F304">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="G304">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="305" spans="1:7">
       <c r="A305" t="s">
-        <v>1150</v>
+        <v>1139</v>
       </c>
       <c r="B305" t="s">
-        <v>1151</v>
+        <v>1140</v>
       </c>
       <c r="C305" t="s">
-        <v>1152</v>
+        <v>1141</v>
       </c>
       <c r="D305" t="s">
-        <v>1153</v>
+        <v>1142</v>
       </c>
       <c r="E305">
-        <v>786</v>
+        <v>777</v>
       </c>
       <c r="F305">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G305">
-        <v>420</v>
+        <v>6</v>
       </c>
     </row>
     <row r="306" spans="1:7">
       <c r="A306" t="s">
-        <v>1154</v>
+        <v>1143</v>
       </c>
       <c r="B306" t="s">
-        <v>1155</v>
+        <v>1144</v>
       </c>
       <c r="C306" t="s">
-        <v>1156</v>
+        <v>1145</v>
       </c>
       <c r="D306" t="s">
-        <v>1157</v>
+        <v>1146</v>
       </c>
       <c r="E306">
-        <v>379</v>
+        <v>786</v>
       </c>
       <c r="F306">
-        <v>94</v>
+        <v>410</v>
       </c>
       <c r="G306">
-        <v>35</v>
+        <v>420</v>
       </c>
     </row>
     <row r="307" spans="1:7">
       <c r="A307" t="s">
-        <v>1158</v>
+        <v>1147</v>
       </c>
       <c r="B307" t="s">
-        <v>1159</v>
+        <v>1148</v>
       </c>
       <c r="C307" t="s">
-        <v>1160</v>
+        <v>1149</v>
       </c>
       <c r="D307" t="s">
-        <v>1161</v>
+        <v>1150</v>
       </c>
       <c r="E307">
-        <v>704</v>
+        <v>379</v>
       </c>
       <c r="F307">
-        <v>333</v>
+        <v>94</v>
       </c>
       <c r="G307">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="308" spans="1:7">
       <c r="A308" t="s">
-        <v>1162</v>
+        <v>1151</v>
       </c>
       <c r="B308" t="s">
-        <v>1163</v>
+        <v>1152</v>
       </c>
       <c r="C308" t="s">
-        <v>1164</v>
+        <v>1153</v>
       </c>
       <c r="D308" t="s">
-        <v>1165</v>
+        <v>1154</v>
       </c>
       <c r="E308">
-        <v>544</v>
+        <v>704</v>
       </c>
       <c r="F308">
-        <v>409</v>
+        <v>333</v>
       </c>
       <c r="G308">
         <v>2</v>
@@ -12020,936 +12032,936 @@
     </row>
     <row r="309" spans="1:7">
       <c r="A309" t="s">
-        <v>1166</v>
+        <v>1155</v>
       </c>
       <c r="B309" t="s">
-        <v>1167</v>
+        <v>1156</v>
       </c>
       <c r="C309" t="s">
-        <v>1168</v>
+        <v>1157</v>
       </c>
       <c r="D309" t="s">
-        <v>1169</v>
+        <v>1158</v>
       </c>
       <c r="E309">
-        <v>818</v>
+        <v>544</v>
       </c>
       <c r="F309">
-        <v>1144</v>
+        <v>409</v>
       </c>
       <c r="G309">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310" spans="1:7">
       <c r="A310" t="s">
-        <v>1170</v>
+        <v>1159</v>
       </c>
       <c r="B310" t="s">
-        <v>1171</v>
+        <v>1160</v>
       </c>
       <c r="C310" t="s">
-        <v>1172</v>
+        <v>1161</v>
       </c>
       <c r="D310" t="s">
-        <v>1173</v>
+        <v>1162</v>
       </c>
       <c r="E310">
-        <v>705</v>
+        <v>818</v>
       </c>
       <c r="F310">
-        <v>854</v>
+        <v>1144</v>
       </c>
       <c r="G310">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="311" spans="1:7">
       <c r="A311" t="s">
-        <v>1174</v>
+        <v>1163</v>
       </c>
       <c r="B311" t="s">
-        <v>1175</v>
+        <v>1164</v>
       </c>
       <c r="C311" t="s">
-        <v>1176</v>
+        <v>1165</v>
       </c>
       <c r="D311" t="s">
-        <v>1177</v>
+        <v>1166</v>
       </c>
       <c r="E311">
-        <v>458</v>
+        <v>705</v>
       </c>
       <c r="F311">
-        <v>607</v>
+        <v>854</v>
       </c>
       <c r="G311">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="312" spans="1:7">
       <c r="A312" t="s">
-        <v>1178</v>
+        <v>1167</v>
       </c>
       <c r="B312" t="s">
-        <v>1179</v>
+        <v>1168</v>
       </c>
       <c r="C312" t="s">
-        <v>1180</v>
+        <v>1169</v>
       </c>
       <c r="D312" t="s">
-        <v>1181</v>
+        <v>1170</v>
       </c>
       <c r="E312">
-        <v>690</v>
+        <v>458</v>
       </c>
       <c r="F312">
-        <v>100</v>
+        <v>607</v>
       </c>
       <c r="G312">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="313" spans="1:7">
       <c r="A313" t="s">
-        <v>1182</v>
+        <v>1171</v>
       </c>
       <c r="B313" t="s">
-        <v>1183</v>
+        <v>1172</v>
       </c>
       <c r="C313" t="s">
-        <v>1184</v>
+        <v>1173</v>
       </c>
       <c r="D313" t="s">
-        <v>1185</v>
+        <v>1174</v>
       </c>
       <c r="E313">
-        <v>100</v>
+        <v>690</v>
       </c>
       <c r="F313">
         <v>100</v>
       </c>
       <c r="G313">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314" spans="1:7">
       <c r="A314" t="s">
-        <v>1186</v>
+        <v>1175</v>
       </c>
       <c r="B314" t="s">
-        <v>1187</v>
+        <v>1176</v>
       </c>
       <c r="C314" t="s">
-        <v>1187</v>
+        <v>1177</v>
       </c>
       <c r="D314" t="s">
-        <v>1187</v>
+        <v>1178</v>
       </c>
       <c r="E314">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F314">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G314">
-        <v>250</v>
+        <v>40</v>
       </c>
     </row>
     <row r="315" spans="1:7">
       <c r="A315" t="s">
-        <v>1188</v>
+        <v>1179</v>
       </c>
       <c r="B315" t="s">
-        <v>1189</v>
+        <v>1180</v>
       </c>
       <c r="C315" t="s">
-        <v>1190</v>
+        <v>1180</v>
       </c>
       <c r="D315" t="s">
-        <v>1191</v>
+        <v>1180</v>
       </c>
       <c r="E315">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F315">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G315">
-        <v>360</v>
+        <v>250</v>
       </c>
     </row>
     <row r="316" spans="1:7">
       <c r="A316" t="s">
-        <v>1192</v>
+        <v>1181</v>
       </c>
       <c r="B316" t="s">
-        <v>1193</v>
+        <v>1182</v>
       </c>
       <c r="C316" t="s">
-        <v>1194</v>
+        <v>1183</v>
       </c>
       <c r="D316" t="s">
-        <v>1195</v>
+        <v>1184</v>
       </c>
       <c r="E316">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="F316">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G316">
-        <v>1000</v>
+        <v>360</v>
       </c>
     </row>
     <row r="317" spans="1:7">
       <c r="A317" t="s">
-        <v>1196</v>
+        <v>1185</v>
       </c>
       <c r="B317" t="s">
-        <v>1196</v>
+        <v>1186</v>
       </c>
       <c r="C317" t="s">
-        <v>1197</v>
+        <v>1187</v>
       </c>
       <c r="D317" t="s">
-        <v>1196</v>
+        <v>1188</v>
       </c>
       <c r="E317">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="F317">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="G317">
-        <v>10</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="318" spans="1:7">
       <c r="A318" t="s">
-        <v>1198</v>
+        <v>1189</v>
       </c>
       <c r="B318" t="s">
-        <v>1199</v>
+        <v>1189</v>
       </c>
       <c r="C318" t="s">
-        <v>1200</v>
+        <v>1190</v>
       </c>
       <c r="D318" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="E318">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F318">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G318">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="319" spans="1:7">
       <c r="A319" t="s">
-        <v>1202</v>
+        <v>1191</v>
       </c>
       <c r="B319" t="s">
-        <v>1203</v>
+        <v>1192</v>
       </c>
       <c r="C319" t="s">
-        <v>1204</v>
+        <v>1193</v>
       </c>
       <c r="D319" t="s">
-        <v>1205</v>
+        <v>1194</v>
       </c>
       <c r="E319">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F319">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G319">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320" spans="1:7">
       <c r="A320" t="s">
-        <v>1450</v>
+        <v>1195</v>
       </c>
       <c r="B320" t="s">
-        <v>1451</v>
+        <v>1196</v>
       </c>
       <c r="C320" t="s">
-        <v>1452</v>
+        <v>1197</v>
       </c>
       <c r="D320" t="s">
-        <v>1453</v>
+        <v>1198</v>
       </c>
       <c r="E320">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F320">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G320">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="321" spans="1:7">
       <c r="A321" t="s">
-        <v>1206</v>
+        <v>1443</v>
       </c>
       <c r="B321" t="s">
-        <v>502</v>
+        <v>1444</v>
       </c>
       <c r="C321" t="s">
-        <v>503</v>
+        <v>1445</v>
       </c>
       <c r="D321" t="s">
-        <v>504</v>
+        <v>1446</v>
       </c>
       <c r="E321">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="F321">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="G321">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="322" spans="1:7">
       <c r="A322" t="s">
-        <v>1207</v>
+        <v>1199</v>
       </c>
       <c r="B322" t="s">
-        <v>1208</v>
+        <v>502</v>
       </c>
       <c r="C322" t="s">
-        <v>1209</v>
+        <v>503</v>
       </c>
       <c r="D322" t="s">
-        <v>1210</v>
+        <v>504</v>
       </c>
       <c r="E322">
-        <v>151</v>
+        <v>400</v>
       </c>
       <c r="F322">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="G322">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="323" spans="1:7">
       <c r="A323" t="s">
-        <v>1211</v>
+        <v>1200</v>
       </c>
       <c r="B323" t="s">
-        <v>1212</v>
+        <v>1201</v>
       </c>
       <c r="C323" t="s">
-        <v>1213</v>
+        <v>1202</v>
       </c>
       <c r="D323" t="s">
-        <v>1214</v>
+        <v>1203</v>
       </c>
       <c r="E323">
-        <v>452</v>
+        <v>151</v>
       </c>
       <c r="F323">
-        <v>264</v>
+        <v>117</v>
       </c>
       <c r="G323">
-        <v>12</v>
+        <v>90</v>
       </c>
     </row>
     <row r="324" spans="1:7">
       <c r="A324" t="s">
-        <v>1215</v>
+        <v>1204</v>
       </c>
       <c r="B324" t="s">
-        <v>1216</v>
+        <v>1205</v>
       </c>
       <c r="C324" t="s">
-        <v>1217</v>
+        <v>1206</v>
       </c>
       <c r="D324" t="s">
-        <v>1218</v>
+        <v>1207</v>
       </c>
       <c r="E324">
-        <v>160</v>
+        <v>452</v>
       </c>
       <c r="F324">
-        <v>189</v>
+        <v>264</v>
       </c>
       <c r="G324">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="325" spans="1:7">
       <c r="A325" t="s">
-        <v>1219</v>
+        <v>1208</v>
       </c>
       <c r="B325" t="s">
-        <v>1220</v>
+        <v>1209</v>
       </c>
       <c r="C325" t="s">
-        <v>1221</v>
+        <v>1210</v>
       </c>
       <c r="D325" t="s">
-        <v>1222</v>
+        <v>1211</v>
       </c>
       <c r="E325">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="F325">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="G325">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="326" spans="1:7">
       <c r="A326" t="s">
-        <v>1223</v>
+        <v>1212</v>
       </c>
       <c r="B326" t="s">
-        <v>1224</v>
+        <v>1213</v>
       </c>
       <c r="C326" t="s">
-        <v>1225</v>
+        <v>1214</v>
       </c>
       <c r="D326" t="s">
-        <v>1226</v>
+        <v>1215</v>
       </c>
       <c r="E326">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="F326">
-        <v>256</v>
+        <v>115</v>
       </c>
       <c r="G326">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="327" spans="1:7">
       <c r="A327" t="s">
-        <v>1227</v>
+        <v>1216</v>
       </c>
       <c r="B327" t="s">
-        <v>1228</v>
+        <v>1217</v>
       </c>
       <c r="C327" t="s">
-        <v>1229</v>
+        <v>1218</v>
       </c>
       <c r="D327" t="s">
-        <v>1230</v>
+        <v>1219</v>
       </c>
       <c r="E327">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="F327">
-        <v>59</v>
+        <v>256</v>
       </c>
       <c r="G327">
-        <v>910</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328" spans="1:7">
       <c r="A328" t="s">
-        <v>1231</v>
+        <v>1220</v>
       </c>
       <c r="B328" t="s">
-        <v>1232</v>
+        <v>1221</v>
       </c>
       <c r="C328" t="s">
-        <v>1233</v>
+        <v>1222</v>
       </c>
       <c r="D328" t="s">
-        <v>1234</v>
+        <v>1223</v>
       </c>
       <c r="E328">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="F328">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="G328">
-        <v>1</v>
+        <v>910</v>
       </c>
     </row>
     <row r="329" spans="1:7">
       <c r="A329" t="s">
-        <v>1235</v>
+        <v>1224</v>
       </c>
       <c r="B329" t="s">
-        <v>1236</v>
+        <v>1225</v>
       </c>
       <c r="C329" t="s">
-        <v>1237</v>
+        <v>1226</v>
       </c>
       <c r="D329" t="s">
-        <v>1238</v>
+        <v>1227</v>
       </c>
       <c r="E329">
-        <v>274</v>
+        <v>157</v>
       </c>
       <c r="F329">
-        <v>300</v>
+        <v>73</v>
       </c>
       <c r="G329">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330" spans="1:7">
       <c r="A330" t="s">
-        <v>1239</v>
+        <v>1228</v>
       </c>
       <c r="B330" t="s">
-        <v>1240</v>
+        <v>1229</v>
       </c>
       <c r="C330" t="s">
-        <v>1241</v>
+        <v>1230</v>
       </c>
       <c r="D330" t="s">
-        <v>1242</v>
+        <v>1231</v>
       </c>
       <c r="E330">
-        <v>225</v>
+        <v>274</v>
       </c>
       <c r="F330">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G330">
-        <v>600</v>
+        <v>4</v>
       </c>
     </row>
     <row r="331" spans="1:7">
       <c r="A331" t="s">
-        <v>1243</v>
+        <v>1232</v>
       </c>
       <c r="B331" t="s">
-        <v>1244</v>
+        <v>1233</v>
       </c>
       <c r="C331" t="s">
-        <v>1245</v>
+        <v>1234</v>
       </c>
       <c r="D331" t="s">
-        <v>1246</v>
+        <v>1235</v>
       </c>
       <c r="E331">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="F331">
-        <v>103</v>
+        <v>250</v>
       </c>
       <c r="G331">
-        <v>17</v>
+        <v>600</v>
       </c>
     </row>
     <row r="332" spans="1:7">
       <c r="A332" t="s">
-        <v>1247</v>
+        <v>1236</v>
       </c>
       <c r="B332" t="s">
-        <v>1248</v>
+        <v>1237</v>
       </c>
       <c r="C332" t="s">
-        <v>1249</v>
+        <v>1238</v>
       </c>
       <c r="D332" t="s">
-        <v>1250</v>
+        <v>1239</v>
       </c>
       <c r="E332">
-        <v>502</v>
+        <v>249</v>
       </c>
       <c r="F332">
-        <v>344</v>
+        <v>103</v>
       </c>
       <c r="G332">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="333" spans="1:7">
       <c r="A333" t="s">
-        <v>1215</v>
+        <v>1240</v>
       </c>
       <c r="B333" t="s">
-        <v>1216</v>
+        <v>1241</v>
       </c>
       <c r="C333" t="s">
-        <v>1217</v>
+        <v>1242</v>
       </c>
       <c r="D333" t="s">
-        <v>1218</v>
+        <v>1243</v>
       </c>
       <c r="E333">
-        <v>112</v>
+        <v>502</v>
       </c>
       <c r="F333">
-        <v>75</v>
+        <v>344</v>
       </c>
       <c r="G333">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="334" spans="1:7">
       <c r="A334" t="s">
-        <v>1251</v>
+        <v>1208</v>
       </c>
       <c r="B334" t="s">
-        <v>1252</v>
+        <v>1209</v>
       </c>
       <c r="C334" t="s">
-        <v>1253</v>
+        <v>1210</v>
       </c>
       <c r="D334" t="s">
-        <v>1252</v>
+        <v>1211</v>
       </c>
       <c r="E334">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F334">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G334">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335" spans="1:7">
       <c r="A335" t="s">
-        <v>1254</v>
+        <v>1244</v>
       </c>
       <c r="B335" t="s">
-        <v>1255</v>
+        <v>1245</v>
       </c>
       <c r="C335" t="s">
-        <v>1256</v>
+        <v>1246</v>
       </c>
       <c r="D335" t="s">
-        <v>1255</v>
+        <v>1245</v>
       </c>
       <c r="E335">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F335">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="G335">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336" spans="1:7">
       <c r="A336" t="s">
-        <v>1257</v>
+        <v>1247</v>
       </c>
       <c r="B336" t="s">
-        <v>1258</v>
+        <v>1248</v>
       </c>
       <c r="C336" t="s">
-        <v>1259</v>
+        <v>1249</v>
       </c>
       <c r="D336" t="s">
-        <v>1260</v>
+        <v>1248</v>
       </c>
       <c r="E336">
-        <v>1390</v>
+        <v>126</v>
       </c>
       <c r="F336">
-        <v>1280</v>
+        <v>113</v>
       </c>
       <c r="G336">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="337" spans="1:7">
       <c r="A337" t="s">
-        <v>1261</v>
+        <v>1250</v>
       </c>
       <c r="B337" t="s">
-        <v>1262</v>
+        <v>1251</v>
       </c>
       <c r="C337" t="s">
-        <v>1263</v>
+        <v>1252</v>
       </c>
       <c r="D337" t="s">
-        <v>1264</v>
+        <v>1253</v>
       </c>
       <c r="E337">
-        <v>380</v>
+        <v>1390</v>
       </c>
       <c r="F337">
-        <v>350</v>
+        <v>1280</v>
       </c>
       <c r="G337">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="338" spans="1:7">
       <c r="A338" t="s">
-        <v>1265</v>
+        <v>1254</v>
       </c>
       <c r="B338" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="C338" t="s">
-        <v>1267</v>
+        <v>1256</v>
       </c>
       <c r="D338" t="s">
-        <v>1268</v>
+        <v>1257</v>
       </c>
       <c r="E338">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="F338">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="G338">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="339" spans="1:7">
       <c r="A339" t="s">
-        <v>1269</v>
+        <v>1258</v>
       </c>
       <c r="B339" t="s">
-        <v>1270</v>
+        <v>1259</v>
       </c>
       <c r="C339" t="s">
-        <v>1271</v>
+        <v>1260</v>
       </c>
       <c r="D339" t="s">
-        <v>1272</v>
+        <v>1261</v>
       </c>
       <c r="E339">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="F339">
-        <v>120</v>
+        <v>325</v>
       </c>
       <c r="G339">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="340" spans="1:7">
       <c r="A340" t="s">
-        <v>1434</v>
+        <v>1262</v>
       </c>
       <c r="B340" t="s">
-        <v>1435</v>
+        <v>1263</v>
       </c>
       <c r="C340" t="s">
-        <v>1436</v>
+        <v>1264</v>
       </c>
       <c r="D340" t="s">
-        <v>1437</v>
+        <v>1265</v>
       </c>
       <c r="E340">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="F340">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="G340">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="341" spans="1:7">
       <c r="A341" t="s">
-        <v>1273</v>
+        <v>1427</v>
       </c>
       <c r="B341" t="s">
-        <v>1274</v>
+        <v>1428</v>
       </c>
       <c r="C341" t="s">
-        <v>1275</v>
+        <v>1429</v>
       </c>
       <c r="D341" t="s">
-        <v>1276</v>
+        <v>1430</v>
       </c>
       <c r="E341">
-        <v>260</v>
+        <v>31</v>
       </c>
       <c r="F341">
-        <v>250</v>
+        <v>36</v>
       </c>
       <c r="G341">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342" spans="1:7">
       <c r="A342" t="s">
-        <v>1277</v>
+        <v>1266</v>
       </c>
       <c r="B342" t="s">
-        <v>1278</v>
+        <v>1267</v>
       </c>
       <c r="C342" t="s">
-        <v>1279</v>
+        <v>1268</v>
       </c>
       <c r="D342" t="s">
-        <v>1280</v>
+        <v>1269</v>
       </c>
       <c r="E342">
-        <v>355</v>
+        <v>260</v>
       </c>
       <c r="F342">
-        <v>342</v>
+        <v>250</v>
       </c>
       <c r="G342">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="343" spans="1:7">
       <c r="A343" t="s">
-        <v>1281</v>
+        <v>1270</v>
       </c>
       <c r="B343" t="s">
-        <v>1282</v>
+        <v>1271</v>
       </c>
       <c r="C343" t="s">
-        <v>1283</v>
+        <v>1272</v>
       </c>
       <c r="D343" t="s">
-        <v>1284</v>
+        <v>1273</v>
       </c>
       <c r="E343">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="F343">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="G343">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="344" spans="1:7">
       <c r="A344" t="s">
-        <v>1285</v>
+        <v>1274</v>
       </c>
       <c r="B344" t="s">
-        <v>1286</v>
+        <v>1275</v>
       </c>
       <c r="C344" t="s">
-        <v>1287</v>
+        <v>1276</v>
       </c>
       <c r="D344" t="s">
-        <v>1288</v>
+        <v>1277</v>
       </c>
       <c r="E344">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="F344">
-        <v>98</v>
+        <v>391</v>
       </c>
       <c r="G344">
-        <v>390</v>
+        <v>5</v>
       </c>
     </row>
     <row r="345" spans="1:7">
       <c r="A345" t="s">
-        <v>1289</v>
+        <v>1278</v>
       </c>
       <c r="B345" t="s">
-        <v>1290</v>
+        <v>1279</v>
       </c>
       <c r="C345" t="s">
-        <v>1291</v>
+        <v>1280</v>
       </c>
       <c r="D345" t="s">
-        <v>1292</v>
+        <v>1281</v>
       </c>
       <c r="E345">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="F345">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="G345">
-        <v>564</v>
+        <v>390</v>
       </c>
     </row>
     <row r="346" spans="1:7">
       <c r="A346" t="s">
-        <v>1293</v>
+        <v>1282</v>
       </c>
       <c r="B346" t="s">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="C346" t="s">
-        <v>1295</v>
+        <v>1284</v>
       </c>
       <c r="D346" t="s">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="E346">
-        <v>219</v>
+        <v>348</v>
       </c>
       <c r="F346">
-        <v>140</v>
+        <v>298</v>
       </c>
       <c r="G346">
-        <v>281</v>
+        <v>564</v>
       </c>
     </row>
     <row r="347" spans="1:7">
       <c r="A347" t="s">
-        <v>1297</v>
+        <v>1286</v>
       </c>
       <c r="B347" t="s">
-        <v>1298</v>
+        <v>1287</v>
       </c>
       <c r="C347" t="s">
-        <v>1298</v>
+        <v>1288</v>
       </c>
       <c r="D347" t="s">
-        <v>1298</v>
+        <v>1289</v>
       </c>
       <c r="E347">
-        <v>32</v>
+        <v>219</v>
       </c>
       <c r="F347">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="G347">
-        <v>400</v>
+        <v>281</v>
       </c>
     </row>
     <row r="348" spans="1:7">
       <c r="A348" t="s">
-        <v>1299</v>
+        <v>1290</v>
       </c>
       <c r="B348" t="s">
-        <v>1300</v>
+        <v>1291</v>
       </c>
       <c r="C348" t="s">
-        <v>1301</v>
+        <v>1291</v>
       </c>
       <c r="D348" t="s">
-        <v>1302</v>
+        <v>1291</v>
       </c>
       <c r="E348">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F348">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="G348">
-        <v>1</v>
+        <v>400</v>
       </c>
     </row>
     <row r="349" spans="1:7">
       <c r="A349" t="s">
-        <v>1303</v>
+        <v>1292</v>
       </c>
       <c r="B349" t="s">
-        <v>1304</v>
+        <v>1293</v>
       </c>
       <c r="C349" t="s">
-        <v>1305</v>
+        <v>1294</v>
       </c>
       <c r="D349" t="s">
-        <v>1304</v>
+        <v>1295</v>
       </c>
       <c r="E349">
         <v>70</v>
@@ -12963,183 +12975,183 @@
     </row>
     <row r="350" spans="1:7">
       <c r="A350" t="s">
-        <v>1306</v>
+        <v>1296</v>
       </c>
       <c r="B350" t="s">
-        <v>1307</v>
+        <v>1297</v>
       </c>
       <c r="C350" t="s">
-        <v>1308</v>
+        <v>1298</v>
       </c>
       <c r="D350" t="s">
-        <v>1309</v>
+        <v>1297</v>
       </c>
       <c r="E350">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="F350">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="G350">
-        <v>400</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351" spans="1:7">
       <c r="A351" t="s">
-        <v>1310</v>
+        <v>1299</v>
       </c>
       <c r="B351" t="s">
-        <v>1311</v>
+        <v>1300</v>
       </c>
       <c r="C351" t="s">
-        <v>1312</v>
+        <v>1301</v>
       </c>
       <c r="D351" t="s">
-        <v>1313</v>
+        <v>1302</v>
       </c>
       <c r="E351">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="F351">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G351">
-        <v>150</v>
+        <v>400</v>
       </c>
     </row>
     <row r="352" spans="1:7">
       <c r="A352" t="s">
-        <v>1461</v>
+        <v>1303</v>
       </c>
       <c r="B352" t="s">
-        <v>1464</v>
+        <v>1304</v>
       </c>
       <c r="C352" t="s">
-        <v>1463</v>
+        <v>1305</v>
       </c>
       <c r="D352" t="s">
-        <v>1462</v>
+        <v>1306</v>
       </c>
       <c r="E352">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F352">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="G352">
-        <v>180</v>
+        <v>150</v>
       </c>
     </row>
     <row r="353" spans="1:7">
       <c r="A353" t="s">
-        <v>1314</v>
+        <v>1454</v>
       </c>
       <c r="B353" t="s">
-        <v>1315</v>
+        <v>1457</v>
       </c>
       <c r="C353" t="s">
-        <v>1316</v>
+        <v>1456</v>
       </c>
       <c r="D353" t="s">
-        <v>1317</v>
+        <v>1455</v>
       </c>
       <c r="E353">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="F353">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="G353">
-        <v>450</v>
+        <v>180</v>
       </c>
     </row>
     <row r="354" spans="1:7">
       <c r="A354" t="s">
-        <v>1318</v>
+        <v>1307</v>
       </c>
       <c r="B354" t="s">
-        <v>1319</v>
+        <v>1308</v>
       </c>
       <c r="C354" t="s">
-        <v>1320</v>
+        <v>1309</v>
       </c>
       <c r="D354" t="s">
-        <v>1321</v>
+        <v>1310</v>
       </c>
       <c r="E354">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="F354">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="G354">
-        <v>100</v>
+        <v>450</v>
       </c>
     </row>
     <row r="355" spans="1:7">
       <c r="A355" t="s">
-        <v>1322</v>
+        <v>1311</v>
       </c>
       <c r="B355" t="s">
-        <v>1323</v>
+        <v>1312</v>
       </c>
       <c r="C355" t="s">
-        <v>1324</v>
+        <v>1313</v>
       </c>
       <c r="D355" t="s">
-        <v>1325</v>
+        <v>1314</v>
       </c>
       <c r="E355">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F355">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="G355">
-        <v>350</v>
+        <v>100</v>
       </c>
     </row>
     <row r="356" spans="1:7">
       <c r="A356" t="s">
-        <v>1326</v>
+        <v>1315</v>
       </c>
       <c r="B356" t="s">
-        <v>1327</v>
+        <v>1316</v>
       </c>
       <c r="C356" t="s">
-        <v>1328</v>
+        <v>1317</v>
       </c>
       <c r="D356" t="s">
-        <v>1329</v>
+        <v>1318</v>
       </c>
       <c r="E356">
+        <v>200</v>
+      </c>
+      <c r="F356">
         <v>150</v>
       </c>
-      <c r="F356">
-        <v>110</v>
-      </c>
       <c r="G356">
-        <v>500</v>
+        <v>350</v>
       </c>
     </row>
     <row r="357" spans="1:7">
       <c r="A357" t="s">
-        <v>1330</v>
+        <v>1319</v>
       </c>
       <c r="B357" t="s">
-        <v>1331</v>
+        <v>1320</v>
       </c>
       <c r="C357" t="s">
-        <v>1332</v>
+        <v>1321</v>
       </c>
       <c r="D357" t="s">
-        <v>1333</v>
+        <v>1322</v>
       </c>
       <c r="E357">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F357">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="G357">
         <v>500</v>
@@ -13147,16 +13159,16 @@
     </row>
     <row r="358" spans="1:7">
       <c r="A358" t="s">
-        <v>1334</v>
+        <v>1323</v>
       </c>
       <c r="B358" t="s">
-        <v>1335</v>
+        <v>1324</v>
       </c>
       <c r="C358" t="s">
-        <v>1336</v>
+        <v>1325</v>
       </c>
       <c r="D358" t="s">
-        <v>1337</v>
+        <v>1326</v>
       </c>
       <c r="E358">
         <v>100</v>
@@ -13170,22 +13182,22 @@
     </row>
     <row r="359" spans="1:7">
       <c r="A359" t="s">
-        <v>1338</v>
+        <v>1327</v>
       </c>
       <c r="B359" t="s">
-        <v>1339</v>
+        <v>1328</v>
       </c>
       <c r="C359" t="s">
-        <v>1340</v>
+        <v>1329</v>
       </c>
       <c r="D359" t="s">
-        <v>1341</v>
+        <v>1330</v>
       </c>
       <c r="E359">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="F359">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="G359">
         <v>500</v>
@@ -13193,45 +13205,45 @@
     </row>
     <row r="360" spans="1:7">
       <c r="A360" t="s">
-        <v>1342</v>
+        <v>1331</v>
       </c>
       <c r="B360" t="s">
-        <v>1343</v>
+        <v>1332</v>
       </c>
       <c r="C360" t="s">
-        <v>1344</v>
+        <v>1333</v>
       </c>
       <c r="D360" t="s">
-        <v>1345</v>
+        <v>1334</v>
       </c>
       <c r="E360">
-        <v>338</v>
+        <v>145</v>
       </c>
       <c r="F360">
-        <v>347</v>
+        <v>135</v>
       </c>
       <c r="G360">
-        <v>370</v>
+        <v>500</v>
       </c>
     </row>
     <row r="361" spans="1:7">
       <c r="A361" t="s">
-        <v>1346</v>
+        <v>1335</v>
       </c>
       <c r="B361" t="s">
-        <v>1347</v>
+        <v>1336</v>
       </c>
       <c r="C361" t="s">
-        <v>1348</v>
+        <v>1337</v>
       </c>
       <c r="D361" t="s">
-        <v>1349</v>
+        <v>1338</v>
       </c>
       <c r="E361">
-        <v>209</v>
+        <v>338</v>
       </c>
       <c r="F361">
-        <v>244</v>
+        <v>347</v>
       </c>
       <c r="G361">
         <v>370</v>
@@ -13239,691 +13251,714 @@
     </row>
     <row r="362" spans="1:7">
       <c r="A362" t="s">
-        <v>1350</v>
+        <v>1339</v>
       </c>
       <c r="B362" t="s">
-        <v>1351</v>
+        <v>1340</v>
       </c>
       <c r="C362" t="s">
-        <v>1352</v>
+        <v>1341</v>
       </c>
       <c r="D362" t="s">
-        <v>1353</v>
+        <v>1342</v>
       </c>
       <c r="E362">
+        <v>209</v>
+      </c>
+      <c r="F362">
+        <v>244</v>
+      </c>
+      <c r="G362">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7">
+      <c r="A363" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B363" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C363" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D363" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E363">
         <v>131</v>
       </c>
-      <c r="F362">
+      <c r="F363">
         <v>120</v>
       </c>
-      <c r="G362">
+      <c r="G363">
         <v>635</v>
       </c>
     </row>
-    <row r="363" spans="1:7" s="2" customFormat="1" ht="17.850000000000001" customHeight="1">
-      <c r="A363" s="2" t="s">
+    <row r="364" spans="1:7" s="2" customFormat="1" ht="17.850000000000001" customHeight="1">
+      <c r="A364" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D364" s="3" t="s">
+        <v>1466</v>
+      </c>
+      <c r="E364" s="2">
+        <v>42</v>
+      </c>
+      <c r="F364" s="2">
+        <v>14</v>
+      </c>
+      <c r="G364" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" s="2" customFormat="1" ht="16.7" customHeight="1">
+      <c r="A365" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B365" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D365" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E365" s="2">
+        <v>106</v>
+      </c>
+      <c r="F365" s="2">
+        <v>18</v>
+      </c>
+      <c r="G365" s="2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" s="2" customFormat="1" ht="15.55" customHeight="1">
+      <c r="A366" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C366" s="3" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D366" s="4" t="s">
         <v>1469</v>
       </c>
-      <c r="B363" s="2" t="s">
-        <v>1471</v>
-      </c>
-      <c r="C363" s="2" t="s">
-        <v>1472</v>
-      </c>
-      <c r="D363" s="3" t="s">
-        <v>1473</v>
-      </c>
-      <c r="E363" s="2">
-        <v>42</v>
-      </c>
-      <c r="F363" s="2">
-        <v>14</v>
-      </c>
-      <c r="G363" s="2">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="364" spans="1:7" s="2" customFormat="1" ht="16.7" customHeight="1">
-      <c r="A364" s="2" t="s">
-        <v>1501</v>
-      </c>
-      <c r="B364" s="3" t="s">
-        <v>1502</v>
-      </c>
-      <c r="C364" s="2" t="s">
-        <v>1503</v>
-      </c>
-      <c r="D364" s="2" t="s">
-        <v>1504</v>
-      </c>
-      <c r="E364" s="2">
-        <v>106</v>
-      </c>
-      <c r="F364" s="2">
-        <v>18</v>
-      </c>
-      <c r="G364" s="2">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="365" spans="1:7" s="2" customFormat="1" ht="15.55" customHeight="1">
-      <c r="A365" s="2" t="s">
-        <v>1470</v>
-      </c>
-      <c r="B365" s="2" t="s">
-        <v>1474</v>
-      </c>
-      <c r="C365" s="3" t="s">
-        <v>1475</v>
-      </c>
-      <c r="D365" s="4" t="s">
-        <v>1476</v>
-      </c>
-      <c r="E365" s="2">
+      <c r="E366" s="2">
         <v>77</v>
       </c>
-      <c r="F365" s="2">
+      <c r="F366" s="2">
         <v>47</v>
       </c>
-      <c r="G365" s="2">
+      <c r="G366" s="2">
         <v>223</v>
-      </c>
-    </row>
-    <row r="366" spans="1:7">
-      <c r="A366" t="s">
-        <v>1354</v>
-      </c>
-      <c r="B366" t="s">
-        <v>1355</v>
-      </c>
-      <c r="C366" t="s">
-        <v>1356</v>
-      </c>
-      <c r="D366" t="s">
-        <v>1357</v>
-      </c>
-      <c r="E366">
-        <v>1</v>
-      </c>
-      <c r="F366">
-        <v>1</v>
-      </c>
-      <c r="G366">
-        <v>10</v>
       </c>
     </row>
     <row r="367" spans="1:7">
       <c r="A367" t="s">
-        <v>1358</v>
+        <v>1347</v>
       </c>
       <c r="B367" t="s">
-        <v>1359</v>
+        <v>1348</v>
       </c>
       <c r="C367" t="s">
-        <v>1360</v>
+        <v>1349</v>
       </c>
       <c r="D367" t="s">
-        <v>1361</v>
+        <v>1350</v>
       </c>
       <c r="E367">
+        <v>1</v>
+      </c>
+      <c r="F367">
+        <v>1</v>
+      </c>
+      <c r="G367">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7">
+      <c r="A368" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B368" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C368" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D368" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E368">
         <v>0</v>
-      </c>
-      <c r="F367">
-        <v>0</v>
-      </c>
-      <c r="G367">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="368" spans="1:7" ht="15">
-      <c r="A368" t="s">
-        <v>1465</v>
-      </c>
-      <c r="B368" s="1" t="s">
-        <v>1466</v>
-      </c>
-      <c r="C368" s="1" t="s">
-        <v>1467</v>
-      </c>
-      <c r="D368" s="1" t="s">
-        <v>1468</v>
-      </c>
-      <c r="E368">
-        <v>1</v>
       </c>
       <c r="F368">
         <v>0</v>
       </c>
       <c r="G368">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="369" spans="1:7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" ht="15">
       <c r="A369" t="s">
-        <v>1362</v>
-      </c>
-      <c r="B369" t="s">
-        <v>1363</v>
-      </c>
-      <c r="C369" t="s">
-        <v>1364</v>
-      </c>
-      <c r="D369" t="s">
-        <v>1365</v>
+        <v>1458</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>1461</v>
       </c>
       <c r="E369">
         <v>1</v>
       </c>
       <c r="F369">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G369">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="370" spans="1:7">
       <c r="A370" t="s">
-        <v>1506</v>
+        <v>1355</v>
       </c>
       <c r="B370" t="s">
-        <v>1508</v>
+        <v>1356</v>
       </c>
       <c r="C370" t="s">
-        <v>1510</v>
+        <v>1357</v>
       </c>
       <c r="D370" t="s">
-        <v>1512</v>
+        <v>1358</v>
       </c>
       <c r="E370">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="F370">
-        <v>0.5</v>
+        <v>12</v>
       </c>
       <c r="G370">
-        <v>1.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="371" spans="1:7">
       <c r="A371" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="B371" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
       <c r="C371" t="s">
-        <v>1511</v>
+        <v>1503</v>
       </c>
       <c r="D371" t="s">
-        <v>1513</v>
+        <v>1505</v>
       </c>
       <c r="E371">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F371">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G371">
-        <v>15</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="372" spans="1:7">
       <c r="A372" t="s">
-        <v>1366</v>
+        <v>1500</v>
       </c>
       <c r="B372" t="s">
-        <v>1367</v>
+        <v>1502</v>
       </c>
       <c r="C372" t="s">
-        <v>1368</v>
+        <v>1504</v>
       </c>
       <c r="D372" t="s">
-        <v>1369</v>
+        <v>1506</v>
       </c>
       <c r="E372">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F372">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G372">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="373" spans="1:7">
       <c r="A373" t="s">
-        <v>1454</v>
+        <v>1359</v>
       </c>
       <c r="B373" t="s">
-        <v>1455</v>
+        <v>1360</v>
       </c>
       <c r="C373" t="s">
-        <v>1456</v>
+        <v>1361</v>
       </c>
       <c r="D373" t="s">
-        <v>1457</v>
+        <v>1362</v>
       </c>
       <c r="E373">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F373">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="G373">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374" spans="1:7">
       <c r="A374" t="s">
-        <v>1370</v>
+        <v>1447</v>
       </c>
       <c r="B374" t="s">
-        <v>1371</v>
+        <v>1448</v>
       </c>
       <c r="C374" t="s">
-        <v>1372</v>
+        <v>1449</v>
       </c>
       <c r="D374" t="s">
-        <v>1373</v>
+        <v>1450</v>
       </c>
       <c r="E374">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F374">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G374">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="375" spans="1:7">
       <c r="A375" t="s">
-        <v>1374</v>
+        <v>1363</v>
       </c>
       <c r="B375" t="s">
-        <v>1375</v>
+        <v>1364</v>
       </c>
       <c r="C375" t="s">
-        <v>1376</v>
+        <v>1365</v>
       </c>
       <c r="D375" t="s">
-        <v>1377</v>
+        <v>1366</v>
       </c>
       <c r="E375">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F375">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G375">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
-        <v>1378</v>
+        <v>1367</v>
       </c>
       <c r="B376" t="s">
-        <v>1379</v>
+        <v>1368</v>
       </c>
       <c r="C376" t="s">
-        <v>1380</v>
+        <v>1369</v>
       </c>
       <c r="D376" t="s">
-        <v>1381</v>
+        <v>1370</v>
       </c>
       <c r="E376">
-        <v>400</v>
+        <v>37</v>
       </c>
       <c r="F376">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G376">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="377" spans="1:7">
       <c r="A377" t="s">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="B377" t="s">
-        <v>1383</v>
+        <v>1372</v>
       </c>
       <c r="C377" t="s">
-        <v>1384</v>
+        <v>1373</v>
       </c>
       <c r="D377" t="s">
-        <v>1385</v>
+        <v>1374</v>
       </c>
       <c r="E377">
-        <v>549</v>
+        <v>400</v>
       </c>
       <c r="F377">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c r="G377">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="378" spans="1:7">
       <c r="A378" t="s">
-        <v>1514</v>
+        <v>1375</v>
       </c>
       <c r="B378" t="s">
-        <v>1515</v>
+        <v>1376</v>
       </c>
       <c r="C378" t="s">
-        <v>1516</v>
+        <v>1377</v>
       </c>
       <c r="D378" t="s">
-        <v>1517</v>
+        <v>1378</v>
       </c>
       <c r="E378">
-        <v>150</v>
+        <v>549</v>
       </c>
       <c r="F378">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="G378">
-        <v>150</v>
+        <v>26</v>
       </c>
     </row>
     <row r="379" spans="1:7">
       <c r="A379" t="s">
-        <v>1386</v>
+        <v>1507</v>
       </c>
       <c r="B379" t="s">
-        <v>1387</v>
+        <v>1508</v>
       </c>
       <c r="C379" t="s">
-        <v>1388</v>
+        <v>1509</v>
       </c>
       <c r="D379" t="s">
-        <v>1389</v>
+        <v>1510</v>
       </c>
       <c r="E379">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="F379">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="G379">
-        <v>2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="380" spans="1:7">
       <c r="A380" t="s">
-        <v>1390</v>
+        <v>1379</v>
       </c>
       <c r="B380" t="s">
-        <v>1391</v>
+        <v>1380</v>
       </c>
       <c r="C380" t="s">
-        <v>1392</v>
+        <v>1381</v>
       </c>
       <c r="D380" t="s">
-        <v>1393</v>
+        <v>1382</v>
       </c>
       <c r="E380">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="F380">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G380">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="381" spans="1:7">
       <c r="A381" t="s">
-        <v>1394</v>
+        <v>1383</v>
       </c>
       <c r="B381" t="s">
-        <v>1395</v>
+        <v>1384</v>
       </c>
       <c r="C381" t="s">
-        <v>1396</v>
+        <v>1385</v>
       </c>
       <c r="D381" t="s">
-        <v>1397</v>
+        <v>1386</v>
       </c>
       <c r="E381">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F381">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="G381">
-        <v>39</v>
+        <v>4</v>
       </c>
     </row>
     <row r="382" spans="1:7">
       <c r="A382" t="s">
-        <v>1398</v>
+        <v>1387</v>
       </c>
       <c r="B382" t="s">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="C382" t="s">
-        <v>1400</v>
+        <v>1389</v>
       </c>
       <c r="D382" t="s">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="E382">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="F382">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G382">
-        <v>91</v>
+        <v>39</v>
       </c>
     </row>
     <row r="383" spans="1:7">
       <c r="A383" t="s">
-        <v>1402</v>
+        <v>1391</v>
       </c>
       <c r="B383" t="s">
-        <v>1403</v>
+        <v>1392</v>
       </c>
       <c r="C383" t="s">
-        <v>1404</v>
+        <v>1393</v>
       </c>
       <c r="D383" t="s">
-        <v>1405</v>
+        <v>1394</v>
       </c>
       <c r="E383">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="F383">
         <v>0</v>
       </c>
       <c r="G383">
-        <v>920</v>
+        <v>91</v>
       </c>
     </row>
     <row r="384" spans="1:7">
       <c r="A384" t="s">
-        <v>1406</v>
+        <v>1395</v>
       </c>
       <c r="B384" t="s">
-        <v>1407</v>
+        <v>1396</v>
       </c>
       <c r="C384" t="s">
-        <v>1408</v>
+        <v>1397</v>
       </c>
       <c r="D384" t="s">
-        <v>1409</v>
+        <v>1398</v>
       </c>
       <c r="E384">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="F384">
         <v>0</v>
       </c>
       <c r="G384">
-        <v>870</v>
+        <v>920</v>
       </c>
     </row>
     <row r="385" spans="1:7">
       <c r="A385" t="s">
-        <v>1482</v>
+        <v>1399</v>
       </c>
       <c r="B385" t="s">
-        <v>1485</v>
+        <v>1400</v>
       </c>
       <c r="C385" t="s">
-        <v>1484</v>
+        <v>1401</v>
       </c>
       <c r="D385" t="s">
-        <v>1483</v>
+        <v>1402</v>
       </c>
       <c r="E385">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F385">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G385">
-        <v>4</v>
+        <v>870</v>
       </c>
     </row>
     <row r="386" spans="1:7">
       <c r="A386" t="s">
-        <v>1410</v>
+        <v>1475</v>
       </c>
       <c r="B386" t="s">
-        <v>1411</v>
+        <v>1478</v>
       </c>
       <c r="C386" t="s">
-        <v>1412</v>
+        <v>1477</v>
       </c>
       <c r="D386" t="s">
-        <v>1413</v>
+        <v>1476</v>
       </c>
       <c r="E386">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F386">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G386">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="387" spans="1:7">
       <c r="A387" t="s">
-        <v>1414</v>
+        <v>1403</v>
       </c>
       <c r="B387" t="s">
-        <v>1415</v>
+        <v>1404</v>
       </c>
       <c r="C387" t="s">
-        <v>1416</v>
+        <v>1405</v>
       </c>
       <c r="D387" t="s">
-        <v>1417</v>
+        <v>1406</v>
       </c>
       <c r="E387">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F387">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G387">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="388" spans="1:7">
       <c r="A388" t="s">
-        <v>1418</v>
+        <v>1407</v>
       </c>
       <c r="B388" t="s">
-        <v>1419</v>
+        <v>1408</v>
       </c>
       <c r="C388" t="s">
-        <v>1420</v>
+        <v>1409</v>
       </c>
       <c r="D388" t="s">
-        <v>1421</v>
+        <v>1410</v>
       </c>
       <c r="E388">
         <v>27</v>
       </c>
       <c r="F388">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G388">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="389" spans="1:7">
       <c r="A389" t="s">
-        <v>1422</v>
+        <v>1411</v>
       </c>
       <c r="B389" t="s">
-        <v>1423</v>
+        <v>1412</v>
       </c>
       <c r="C389" t="s">
-        <v>1424</v>
+        <v>1413</v>
       </c>
       <c r="D389" t="s">
-        <v>1425</v>
+        <v>1414</v>
       </c>
       <c r="E389">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="F389">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G389">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="390" spans="1:7">
       <c r="A390" t="s">
-        <v>1426</v>
+        <v>1415</v>
       </c>
       <c r="B390" t="s">
-        <v>1427</v>
+        <v>1416</v>
       </c>
       <c r="C390" t="s">
-        <v>1428</v>
+        <v>1417</v>
       </c>
       <c r="D390" t="s">
-        <v>1429</v>
+        <v>1418</v>
       </c>
       <c r="E390">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="F390">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G390">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391" spans="1:7">
       <c r="A391" t="s">
-        <v>1430</v>
+        <v>1419</v>
       </c>
       <c r="B391" t="s">
-        <v>1431</v>
+        <v>1420</v>
       </c>
       <c r="C391" t="s">
-        <v>1432</v>
+        <v>1421</v>
       </c>
       <c r="D391" t="s">
-        <v>1433</v>
+        <v>1422</v>
       </c>
       <c r="E391">
+        <v>102</v>
+      </c>
+      <c r="F391">
+        <v>10</v>
+      </c>
+      <c r="G391">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7">
+      <c r="A392" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B392" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C392" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D392" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E392">
         <v>0</v>
       </c>
-      <c r="F391">
+      <c r="F392">
         <v>0</v>
       </c>
-      <c r="G391">
+      <c r="G392">
         <v>0</v>
       </c>
     </row>
